--- a/2020.HK.xlsx
+++ b/2020.HK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82AE3255-1257-41D6-B6B1-5F451925B081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3593EE31-E3BC-4011-B7D0-8A3D5BEE431C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{A24C8550-AABC-4E33-81F8-E1B227287154}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{A24C8550-AABC-4E33-81F8-E1B227287154}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="91">
   <si>
     <t>Anta Sports Prouducts</t>
   </si>
@@ -303,7 +303,13 @@
     <t>FY25</t>
   </si>
   <si>
-    <t>Q425</t>
+    <t>H126</t>
+  </si>
+  <si>
+    <t>H226</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
@@ -315,13 +321,19 @@
     <numFmt numFmtId="165" formatCode="#,##0;\(#,##0\)"/>
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -509,41 +521,44 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -907,7 +922,7 @@
         <v>78</v>
       </c>
       <c r="H2" s="3">
-        <v>80.55</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -916,7 +931,7 @@
       </c>
       <c r="H3" s="3">
         <f>+H2*H10</f>
-        <v>74.911500000000004</v>
+        <v>73.237499999999997</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -924,10 +939,10 @@
         <v>1</v>
       </c>
       <c r="H4" s="4">
-        <v>2780.4319999999998</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>88</v>
+        <v>2770.7</v>
+      </c>
+      <c r="I4" s="30" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -939,7 +954,7 @@
       </c>
       <c r="H5" s="3">
         <f>+H3*H4</f>
-        <v>208286.331768</v>
+        <v>202919.14124999999</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -950,11 +965,11 @@
         <v>3</v>
       </c>
       <c r="H6" s="3">
-        <f>12181+24275</f>
-        <v>36456</v>
-      </c>
-      <c r="I6" s="29" t="s">
-        <v>88</v>
+        <f>16994+26403</f>
+        <v>43397</v>
+      </c>
+      <c r="I6" s="30" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -962,11 +977,11 @@
         <v>4</v>
       </c>
       <c r="H7" s="3">
-        <f>11532+11770</f>
-        <v>23302</v>
-      </c>
-      <c r="I7" s="29" t="s">
-        <v>88</v>
+        <f>12849+10639</f>
+        <v>23488</v>
+      </c>
+      <c r="I7" s="30" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -986,7 +1001,7 @@
       </c>
       <c r="H8" s="3">
         <f>+H5-H6+H7</f>
-        <v>195132.331768</v>
+        <v>183010.14124999999</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -1072,7 +1087,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E54530EA-0C07-4ABC-B674-B68D4026A86E}">
-  <dimension ref="A1:CB301"/>
+  <dimension ref="A1:CD301"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
@@ -1080,12 +1095,12 @@
     <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:82" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:82" x14ac:dyDescent="0.2">
       <c r="C2" s="5" t="s">
         <v>16</v>
       </c>
@@ -1110,29 +1125,35 @@
       <c r="J2" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="K2" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="L2" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="N2" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="5" t="s">
+      <c r="O2" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="5" t="s">
+      <c r="P2" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="5" t="s">
+      <c r="Q2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="5" t="s">
+      <c r="R2" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="Q2" s="5" t="s">
+      <c r="S2" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="R2" s="29" t="s">
+      <c r="T2" s="29" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="3" spans="1:80" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>22</v>
       </c>
@@ -1160,26 +1181,28 @@
       <c r="J3" s="4">
         <v>7203</v>
       </c>
-      <c r="K3" s="4"/>
+      <c r="K3" s="4">
+        <v>7122</v>
+      </c>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
-      <c r="N3" s="4">
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="4">
         <v>6832</v>
       </c>
-      <c r="O3" s="4">
+      <c r="Q3" s="4">
         <v>6924</v>
       </c>
-      <c r="P3" s="4">
+      <c r="R3" s="4">
         <v>7053</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="S3" s="4">
         <v>7135</v>
       </c>
-      <c r="R3" s="4">
+      <c r="T3" s="4">
         <v>7203</v>
       </c>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
       <c r="U3" s="4"/>
       <c r="V3" s="4"/>
       <c r="W3" s="4"/>
@@ -1208,8 +1231,8 @@
       <c r="AT3" s="4"/>
       <c r="AU3" s="4"/>
       <c r="AV3" s="4"/>
-      <c r="AW3" s="3"/>
-      <c r="AX3" s="3"/>
+      <c r="AW3" s="4"/>
+      <c r="AX3" s="4"/>
       <c r="AY3" s="3"/>
       <c r="AZ3" s="3"/>
       <c r="BA3" s="3"/>
@@ -1240,8 +1263,10 @@
       <c r="BZ3" s="3"/>
       <c r="CA3" s="3"/>
       <c r="CB3" s="3"/>
-    </row>
-    <row r="4" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC3" s="3"/>
+      <c r="CD3" s="3"/>
+    </row>
+    <row r="4" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1269,26 +1294,28 @@
       <c r="J4" s="4">
         <v>2652</v>
       </c>
-      <c r="K4" s="4"/>
+      <c r="K4" s="4">
+        <v>2560</v>
+      </c>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
-      <c r="N4" s="4">
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="4">
         <v>2571</v>
       </c>
-      <c r="O4" s="4">
+      <c r="Q4" s="4">
         <v>2679</v>
       </c>
-      <c r="P4" s="4">
+      <c r="R4" s="4">
         <v>2778</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="S4" s="4">
         <v>2784</v>
       </c>
-      <c r="R4" s="4">
+      <c r="T4" s="4">
         <v>2652</v>
       </c>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
       <c r="U4" s="4"/>
       <c r="V4" s="4"/>
       <c r="W4" s="4"/>
@@ -1317,8 +1344,8 @@
       <c r="AT4" s="4"/>
       <c r="AU4" s="4"/>
       <c r="AV4" s="4"/>
-      <c r="AW4" s="3"/>
-      <c r="AX4" s="3"/>
+      <c r="AW4" s="4"/>
+      <c r="AX4" s="4"/>
       <c r="AY4" s="3"/>
       <c r="AZ4" s="3"/>
       <c r="BA4" s="3"/>
@@ -1349,8 +1376,10 @@
       <c r="BZ4" s="3"/>
       <c r="CA4" s="3"/>
       <c r="CB4" s="3"/>
-    </row>
-    <row r="5" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC4" s="3"/>
+      <c r="CD4" s="3"/>
+    </row>
+    <row r="5" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B5" s="2" t="s">
         <v>24</v>
       </c>
@@ -1380,29 +1409,32 @@
         <f>1273+578+189</f>
         <v>2040</v>
       </c>
-      <c r="K5" s="4"/>
+      <c r="K5" s="4">
+        <f>1230+548+176</f>
+        <v>1954</v>
+      </c>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="4">
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="4">
         <v>2054</v>
       </c>
-      <c r="O5" s="4">
+      <c r="Q5" s="4">
         <v>1984</v>
       </c>
-      <c r="P5" s="4">
+      <c r="R5" s="4">
         <f>1179+582+211</f>
         <v>1972</v>
       </c>
-      <c r="Q5" s="4">
+      <c r="S5" s="4">
         <f>1264+590+206</f>
         <v>2060</v>
       </c>
-      <c r="R5" s="4">
+      <c r="T5" s="4">
         <f>1273+578+189</f>
         <v>2040</v>
       </c>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
       <c r="U5" s="4"/>
       <c r="V5" s="4"/>
       <c r="W5" s="4"/>
@@ -1431,8 +1463,8 @@
       <c r="AT5" s="4"/>
       <c r="AU5" s="4"/>
       <c r="AV5" s="4"/>
-      <c r="AW5" s="3"/>
-      <c r="AX5" s="3"/>
+      <c r="AW5" s="4"/>
+      <c r="AX5" s="4"/>
       <c r="AY5" s="3"/>
       <c r="AZ5" s="3"/>
       <c r="BA5" s="3"/>
@@ -1463,8 +1495,10 @@
       <c r="BZ5" s="3"/>
       <c r="CA5" s="3"/>
       <c r="CB5" s="3"/>
-    </row>
-    <row r="6" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC5" s="3"/>
+      <c r="CD5" s="3"/>
+    </row>
+    <row r="6" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
         <v>25</v>
       </c>
@@ -1492,26 +1526,28 @@
       <c r="J6" s="4">
         <v>256</v>
       </c>
-      <c r="K6" s="4"/>
+      <c r="K6" s="4">
+        <v>261</v>
+      </c>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="4">
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="4">
         <v>182</v>
       </c>
-      <c r="O6" s="4">
+      <c r="Q6" s="4">
         <v>191</v>
       </c>
-      <c r="P6" s="4">
+      <c r="R6" s="4">
         <v>187</v>
       </c>
-      <c r="Q6" s="4">
+      <c r="S6" s="4">
         <v>226</v>
       </c>
-      <c r="R6" s="4">
+      <c r="T6" s="4">
         <v>256</v>
       </c>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
       <c r="U6" s="4"/>
       <c r="V6" s="4"/>
       <c r="W6" s="4"/>
@@ -1540,8 +1576,8 @@
       <c r="AT6" s="4"/>
       <c r="AU6" s="4"/>
       <c r="AV6" s="4"/>
-      <c r="AW6" s="3"/>
-      <c r="AX6" s="3"/>
+      <c r="AW6" s="4"/>
+      <c r="AX6" s="4"/>
       <c r="AY6" s="3"/>
       <c r="AZ6" s="3"/>
       <c r="BA6" s="3"/>
@@ -1572,8 +1608,10 @@
       <c r="BZ6" s="3"/>
       <c r="CA6" s="3"/>
       <c r="CB6" s="3"/>
-    </row>
-    <row r="7" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC6" s="3"/>
+      <c r="CD6" s="3"/>
+    </row>
+    <row r="7" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B7" s="2" t="s">
         <v>26</v>
       </c>
@@ -1601,26 +1639,28 @@
       <c r="J7" s="4">
         <v>191</v>
       </c>
-      <c r="K7" s="4"/>
+      <c r="K7" s="4">
+        <v>212</v>
+      </c>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
-      <c r="N7" s="4">
+      <c r="N7" s="4"/>
+      <c r="O7" s="4"/>
+      <c r="P7" s="4">
         <v>155</v>
       </c>
-      <c r="O7" s="4">
+      <c r="Q7" s="4">
         <v>161</v>
       </c>
-      <c r="P7" s="4">
+      <c r="R7" s="4">
         <v>164</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="S7" s="4">
         <v>191</v>
       </c>
-      <c r="R7" s="4">
+      <c r="T7" s="4">
         <v>191</v>
       </c>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
       <c r="U7" s="4"/>
       <c r="V7" s="4"/>
       <c r="W7" s="4"/>
@@ -1649,8 +1689,8 @@
       <c r="AT7" s="4"/>
       <c r="AU7" s="4"/>
       <c r="AV7" s="4"/>
-      <c r="AW7" s="3"/>
-      <c r="AX7" s="3"/>
+      <c r="AW7" s="4"/>
+      <c r="AX7" s="4"/>
       <c r="AY7" s="3"/>
       <c r="AZ7" s="3"/>
       <c r="BA7" s="3"/>
@@ -1681,8 +1721,10 @@
       <c r="BZ7" s="3"/>
       <c r="CA7" s="3"/>
       <c r="CB7" s="3"/>
-    </row>
-    <row r="8" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC7" s="3"/>
+      <c r="CD7" s="3"/>
+    </row>
+    <row r="8" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B8" s="2" t="s">
         <v>85</v>
       </c>
@@ -1700,26 +1742,28 @@
       <c r="J8" s="4">
         <v>52</v>
       </c>
-      <c r="K8" s="4"/>
+      <c r="K8" s="4">
+        <v>53</v>
+      </c>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
-      <c r="N8" s="4">
-        <v>0</v>
-      </c>
-      <c r="O8" s="4">
-        <v>0</v>
-      </c>
+      <c r="N8" s="4"/>
+      <c r="O8" s="4"/>
       <c r="P8" s="4">
         <v>0</v>
       </c>
       <c r="Q8" s="4">
+        <v>0</v>
+      </c>
+      <c r="R8" s="4">
+        <v>0</v>
+      </c>
+      <c r="S8" s="4">
         <v>47</v>
       </c>
-      <c r="R8" s="4">
+      <c r="T8" s="4">
         <v>52</v>
       </c>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
       <c r="U8" s="4"/>
       <c r="V8" s="4"/>
       <c r="W8" s="4"/>
@@ -1748,8 +1792,8 @@
       <c r="AT8" s="4"/>
       <c r="AU8" s="4"/>
       <c r="AV8" s="4"/>
-      <c r="AW8" s="3"/>
-      <c r="AX8" s="3"/>
+      <c r="AW8" s="4"/>
+      <c r="AX8" s="4"/>
       <c r="AY8" s="3"/>
       <c r="AZ8" s="3"/>
       <c r="BA8" s="3"/>
@@ -1780,8 +1824,10 @@
       <c r="BZ8" s="3"/>
       <c r="CA8" s="3"/>
       <c r="CB8" s="3"/>
-    </row>
-    <row r="9" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC8" s="3"/>
+      <c r="CD8" s="3"/>
+    </row>
+    <row r="9" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>27</v>
       </c>
@@ -1814,40 +1860,43 @@
         <v>12453</v>
       </c>
       <c r="J9" s="25">
-        <f t="shared" ref="J9" si="1">+SUM(J3:J7)</f>
+        <f t="shared" ref="J9:K9" si="1">+SUM(J3:J7)</f>
         <v>12342</v>
       </c>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25">
-        <f t="shared" ref="L9:R9" si="2">+SUM(L3:L7)</f>
+      <c r="K9" s="25">
+        <f t="shared" si="1"/>
+        <v>12109</v>
+      </c>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25">
+        <f t="shared" ref="N9:T9" si="2">+SUM(N3:N7)</f>
         <v>0</v>
       </c>
-      <c r="M9" s="25">
+      <c r="O9" s="25">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="N9" s="25">
+      <c r="P9" s="25">
         <f t="shared" si="2"/>
         <v>11794</v>
       </c>
-      <c r="O9" s="25">
+      <c r="Q9" s="25">
         <f t="shared" si="2"/>
         <v>11939</v>
       </c>
-      <c r="P9" s="25">
+      <c r="R9" s="25">
         <f t="shared" si="2"/>
         <v>12154</v>
       </c>
-      <c r="Q9" s="25">
+      <c r="S9" s="25">
         <f t="shared" si="2"/>
         <v>12396</v>
       </c>
-      <c r="R9" s="25">
+      <c r="T9" s="25">
         <f t="shared" si="2"/>
         <v>12342</v>
       </c>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
       <c r="U9" s="4"/>
       <c r="V9" s="4"/>
       <c r="W9" s="4"/>
@@ -1876,8 +1925,8 @@
       <c r="AT9" s="4"/>
       <c r="AU9" s="4"/>
       <c r="AV9" s="4"/>
-      <c r="AW9" s="3"/>
-      <c r="AX9" s="3"/>
+      <c r="AW9" s="4"/>
+      <c r="AX9" s="4"/>
       <c r="AY9" s="3"/>
       <c r="AZ9" s="3"/>
       <c r="BA9" s="3"/>
@@ -1908,8 +1957,10 @@
       <c r="BZ9" s="3"/>
       <c r="CA9" s="3"/>
       <c r="CB9" s="3"/>
-    </row>
-    <row r="10" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC9" s="3"/>
+      <c r="CD9" s="3"/>
+    </row>
+    <row r="10" spans="1:82" x14ac:dyDescent="0.2">
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -1988,8 +2039,10 @@
       <c r="BZ10" s="3"/>
       <c r="CA10" s="3"/>
       <c r="CB10" s="3"/>
-    </row>
-    <row r="11" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC10" s="3"/>
+      <c r="CD10" s="3"/>
+    </row>
+    <row r="11" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B11" s="2" t="s">
         <v>32</v>
       </c>
@@ -1997,50 +2050,52 @@
         <v>11111</v>
       </c>
       <c r="D11" s="3">
-        <f>+O11-C11</f>
+        <f>+Q11-C11</f>
         <v>11360</v>
       </c>
       <c r="E11" s="3">
         <v>12407</v>
       </c>
       <c r="F11" s="3">
-        <f>+P11-E11</f>
+        <f>+R11-E11</f>
         <v>12925</v>
       </c>
       <c r="G11" s="3">
         <v>14635</v>
       </c>
       <c r="H11" s="3">
-        <f>+Q11-G11</f>
+        <f>+S11-G11</f>
         <v>14567</v>
       </c>
       <c r="I11" s="3">
         <v>16390</v>
       </c>
       <c r="J11" s="3">
-        <f t="shared" ref="J11:J21" si="3">+R11-I11</f>
+        <f t="shared" ref="J11:J21" si="3">+T11-I11</f>
         <v>15059</v>
       </c>
-      <c r="K11" s="3"/>
+      <c r="K11" s="3">
+        <v>17158</v>
+      </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="3">
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="P11" s="3">
         <v>19139</v>
       </c>
-      <c r="O11" s="3">
+      <c r="Q11" s="3">
         <v>22471</v>
       </c>
-      <c r="P11" s="3">
+      <c r="R11" s="3">
         <v>25332</v>
       </c>
-      <c r="Q11" s="3">
+      <c r="S11" s="3">
         <v>29202</v>
       </c>
-      <c r="R11" s="3">
+      <c r="T11" s="3">
         <v>31449</v>
       </c>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -2101,8 +2156,10 @@
       <c r="BZ11" s="3"/>
       <c r="CA11" s="3"/>
       <c r="CB11" s="3"/>
-    </row>
-    <row r="12" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC11" s="3"/>
+      <c r="CD11" s="3"/>
+    </row>
+    <row r="12" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B12" s="2" t="s">
         <v>33</v>
       </c>
@@ -2110,21 +2167,21 @@
         <v>14036</v>
       </c>
       <c r="D12" s="3">
-        <f t="shared" ref="D12:D33" si="4">+O12-C12</f>
+        <f t="shared" ref="D12:D33" si="4">+Q12-C12</f>
         <v>15487</v>
       </c>
       <c r="E12" s="4">
         <v>16313</v>
       </c>
       <c r="F12" s="4">
-        <f t="shared" ref="F12:F33" si="5">+P12-E12</f>
+        <f t="shared" ref="F12:F33" si="5">+R12-E12</f>
         <v>18754</v>
       </c>
       <c r="G12" s="4">
         <v>18082</v>
       </c>
       <c r="H12" s="4">
-        <f t="shared" ref="H12:H33" si="6">+Q12-G12</f>
+        <f t="shared" ref="H12:H33" si="6">+S12-G12</f>
         <v>21303</v>
       </c>
       <c r="I12" s="4">
@@ -2134,26 +2191,28 @@
         <f t="shared" si="3"/>
         <v>24928</v>
       </c>
-      <c r="K12" s="4"/>
-      <c r="L12" s="4"/>
+      <c r="K12" s="3">
+        <v>24861</v>
+      </c>
+      <c r="L12" s="3"/>
       <c r="M12" s="4"/>
-      <c r="N12" s="4">
+      <c r="N12" s="4"/>
+      <c r="O12" s="4"/>
+      <c r="P12" s="4">
         <v>28632</v>
       </c>
-      <c r="O12" s="4">
+      <c r="Q12" s="4">
         <v>29523</v>
       </c>
-      <c r="P12" s="4">
+      <c r="R12" s="4">
         <v>35067</v>
       </c>
-      <c r="Q12" s="4">
+      <c r="S12" s="4">
         <v>39385</v>
       </c>
-      <c r="R12" s="4">
+      <c r="T12" s="4">
         <v>45814</v>
       </c>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
       <c r="U12" s="4"/>
       <c r="V12" s="4"/>
       <c r="W12" s="4"/>
@@ -2182,8 +2241,8 @@
       <c r="AT12" s="4"/>
       <c r="AU12" s="4"/>
       <c r="AV12" s="4"/>
-      <c r="AW12" s="3"/>
-      <c r="AX12" s="3"/>
+      <c r="AW12" s="4"/>
+      <c r="AX12" s="4"/>
       <c r="AY12" s="3"/>
       <c r="AZ12" s="3"/>
       <c r="BA12" s="3"/>
@@ -2214,8 +2273,10 @@
       <c r="BZ12" s="3"/>
       <c r="CA12" s="3"/>
       <c r="CB12" s="3"/>
-    </row>
-    <row r="13" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC12" s="3"/>
+      <c r="CD12" s="3"/>
+    </row>
+    <row r="13" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B13" s="2" t="s">
         <v>34</v>
       </c>
@@ -2247,26 +2308,28 @@
         <f t="shared" si="3"/>
         <v>1638</v>
       </c>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
+      <c r="K13" s="3">
+        <v>1488</v>
+      </c>
+      <c r="L13" s="3"/>
       <c r="M13" s="4"/>
-      <c r="N13" s="4">
+      <c r="N13" s="4"/>
+      <c r="O13" s="4"/>
+      <c r="P13" s="4">
         <v>1557</v>
       </c>
-      <c r="O13" s="4">
+      <c r="Q13" s="4">
         <v>1657</v>
       </c>
-      <c r="P13" s="4">
+      <c r="R13" s="4">
         <v>1957</v>
       </c>
-      <c r="Q13" s="4">
+      <c r="S13" s="4">
         <v>2239</v>
       </c>
-      <c r="R13" s="4">
+      <c r="T13" s="4">
         <v>2906</v>
       </c>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
       <c r="U13" s="4"/>
       <c r="V13" s="4"/>
       <c r="W13" s="4"/>
@@ -2295,8 +2358,8 @@
       <c r="AT13" s="4"/>
       <c r="AU13" s="4"/>
       <c r="AV13" s="4"/>
-      <c r="AW13" s="3"/>
-      <c r="AX13" s="3"/>
+      <c r="AW13" s="4"/>
+      <c r="AX13" s="4"/>
       <c r="AY13" s="3"/>
       <c r="AZ13" s="3"/>
       <c r="BA13" s="3"/>
@@ -2327,8 +2390,10 @@
       <c r="BZ13" s="3"/>
       <c r="CA13" s="3"/>
       <c r="CB13" s="3"/>
-    </row>
-    <row r="14" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC13" s="3"/>
+      <c r="CD13" s="3"/>
+    </row>
+    <row r="14" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B14" s="2" t="s">
         <v>35</v>
       </c>
@@ -2360,26 +2425,28 @@
         <f t="shared" si="3"/>
         <v>17804</v>
       </c>
-      <c r="K14" s="4"/>
-      <c r="L14" s="4"/>
+      <c r="K14" s="3">
+        <v>17751</v>
+      </c>
+      <c r="L14" s="3"/>
       <c r="M14" s="4"/>
-      <c r="N14" s="4">
+      <c r="N14" s="4"/>
+      <c r="O14" s="4"/>
+      <c r="P14" s="4">
         <v>24012</v>
       </c>
-      <c r="O14" s="4">
+      <c r="Q14" s="4">
         <v>27723</v>
       </c>
-      <c r="P14" s="4">
+      <c r="R14" s="4">
         <v>30306</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="S14" s="4">
         <v>33522</v>
       </c>
-      <c r="R14" s="4">
+      <c r="T14" s="4">
         <v>34754</v>
       </c>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
       <c r="U14" s="4"/>
       <c r="V14" s="4"/>
       <c r="W14" s="4"/>
@@ -2408,8 +2475,8 @@
       <c r="AT14" s="4"/>
       <c r="AU14" s="4"/>
       <c r="AV14" s="4"/>
-      <c r="AW14" s="3"/>
-      <c r="AX14" s="3"/>
+      <c r="AW14" s="4"/>
+      <c r="AX14" s="4"/>
       <c r="AY14" s="3"/>
       <c r="AZ14" s="3"/>
       <c r="BA14" s="3"/>
@@ -2440,8 +2507,10 @@
       <c r="BZ14" s="3"/>
       <c r="CA14" s="3"/>
       <c r="CB14" s="3"/>
-    </row>
-    <row r="15" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC14" s="3"/>
+      <c r="CD14" s="3"/>
+    </row>
+    <row r="15" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B15" s="2" t="s">
         <v>36</v>
       </c>
@@ -2473,26 +2542,28 @@
         <f t="shared" si="3"/>
         <v>14287</v>
       </c>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
+      <c r="K15" s="3">
+        <v>15045</v>
+      </c>
+      <c r="L15" s="3"/>
       <c r="M15" s="4"/>
-      <c r="N15" s="4">
+      <c r="N15" s="4"/>
+      <c r="O15" s="4"/>
+      <c r="P15" s="4">
         <v>21822</v>
       </c>
-      <c r="O15" s="4">
+      <c r="Q15" s="4">
         <v>21523</v>
       </c>
-      <c r="P15" s="4">
+      <c r="R15" s="4">
         <v>25103</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="S15" s="4">
         <v>26626</v>
       </c>
-      <c r="R15" s="4">
+      <c r="T15" s="4">
         <v>28469</v>
       </c>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
       <c r="U15" s="4"/>
       <c r="V15" s="4"/>
       <c r="W15" s="4"/>
@@ -2521,8 +2592,8 @@
       <c r="AT15" s="4"/>
       <c r="AU15" s="4"/>
       <c r="AV15" s="4"/>
-      <c r="AW15" s="3"/>
-      <c r="AX15" s="3"/>
+      <c r="AW15" s="4"/>
+      <c r="AX15" s="4"/>
       <c r="AY15" s="3"/>
       <c r="AZ15" s="3"/>
       <c r="BA15" s="3"/>
@@ -2553,8 +2624,10 @@
       <c r="BZ15" s="3"/>
       <c r="CA15" s="3"/>
       <c r="CB15" s="3"/>
-    </row>
-    <row r="16" spans="1:80" x14ac:dyDescent="0.2">
+      <c r="CC15" s="3"/>
+      <c r="CD15" s="3"/>
+    </row>
+    <row r="16" spans="1:82" x14ac:dyDescent="0.2">
       <c r="B16" s="2" t="s">
         <v>37</v>
       </c>
@@ -2586,26 +2659,28 @@
         <f t="shared" si="3"/>
         <v>9584</v>
       </c>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
+      <c r="K16" s="3">
+        <v>7815</v>
+      </c>
+      <c r="L16" s="3"/>
       <c r="M16" s="4"/>
-      <c r="N16" s="4">
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="4">
         <v>3494</v>
       </c>
-      <c r="O16" s="4">
+      <c r="Q16" s="4">
         <v>4405</v>
       </c>
-      <c r="P16" s="4">
+      <c r="R16" s="4">
         <v>6947</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="S16" s="4">
         <v>10678</v>
       </c>
-      <c r="R16" s="4">
+      <c r="T16" s="4">
         <v>16996</v>
       </c>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
       <c r="U16" s="4"/>
       <c r="V16" s="4"/>
       <c r="W16" s="4"/>
@@ -2634,8 +2709,8 @@
       <c r="AT16" s="4"/>
       <c r="AU16" s="4"/>
       <c r="AV16" s="4"/>
-      <c r="AW16" s="3"/>
-      <c r="AX16" s="3"/>
+      <c r="AW16" s="4"/>
+      <c r="AX16" s="4"/>
       <c r="AY16" s="3"/>
       <c r="AZ16" s="3"/>
       <c r="BA16" s="3"/>
@@ -2666,8 +2741,10 @@
       <c r="BZ16" s="3"/>
       <c r="CA16" s="3"/>
       <c r="CB16" s="3"/>
-    </row>
-    <row r="17" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC16" s="3"/>
+      <c r="CD16" s="3"/>
+    </row>
+    <row r="17" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B17" s="2" t="s">
         <v>39</v>
       </c>
@@ -2699,27 +2776,29 @@
         <f t="shared" si="3"/>
         <v>9292</v>
       </c>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
+      <c r="K17" s="3">
+        <v>6560</v>
+      </c>
+      <c r="L17" s="3"/>
       <c r="M17" s="4"/>
-      <c r="N17" s="4">
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4">
         <v>8554</v>
       </c>
-      <c r="O17" s="4">
+      <c r="Q17" s="4">
         <v>13687</v>
       </c>
-      <c r="P17" s="4">
+      <c r="R17" s="4">
         <v>17005</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="S17" s="4">
         <v>18238</v>
       </c>
-      <c r="R17" s="4">
+      <c r="T17" s="4">
         <f>12310+6395</f>
         <v>18705</v>
       </c>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
       <c r="U17" s="4"/>
       <c r="V17" s="4"/>
       <c r="W17" s="4"/>
@@ -2748,8 +2827,8 @@
       <c r="AT17" s="4"/>
       <c r="AU17" s="4"/>
       <c r="AV17" s="4"/>
-      <c r="AW17" s="3"/>
-      <c r="AX17" s="3"/>
+      <c r="AW17" s="4"/>
+      <c r="AX17" s="4"/>
       <c r="AY17" s="3"/>
       <c r="AZ17" s="3"/>
       <c r="BA17" s="3"/>
@@ -2780,8 +2859,10 @@
       <c r="BZ17" s="3"/>
       <c r="CA17" s="3"/>
       <c r="CB17" s="3"/>
-    </row>
-    <row r="18" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC17" s="3"/>
+      <c r="CD17" s="3"/>
+    </row>
+    <row r="18" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B18" s="2" t="s">
         <v>40</v>
       </c>
@@ -2813,26 +2894,28 @@
         <f t="shared" si="3"/>
         <v>6732</v>
       </c>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
+      <c r="K18" s="3">
+        <v>6949</v>
+      </c>
+      <c r="L18" s="3"/>
       <c r="M18" s="4"/>
-      <c r="N18" s="4">
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="4">
         <v>8221</v>
       </c>
-      <c r="O18" s="4">
+      <c r="Q18" s="4">
         <v>8677</v>
       </c>
-      <c r="P18" s="4">
+      <c r="R18" s="4">
         <v>9931</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="S18" s="4">
         <v>11985</v>
       </c>
-      <c r="R18" s="4">
+      <c r="T18" s="4">
         <v>12863</v>
       </c>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
       <c r="U18" s="4"/>
       <c r="V18" s="4"/>
       <c r="W18" s="4"/>
@@ -2861,8 +2944,8 @@
       <c r="AT18" s="4"/>
       <c r="AU18" s="4"/>
       <c r="AV18" s="4"/>
-      <c r="AW18" s="3"/>
-      <c r="AX18" s="3"/>
+      <c r="AW18" s="4"/>
+      <c r="AX18" s="4"/>
       <c r="AY18" s="3"/>
       <c r="AZ18" s="3"/>
       <c r="BA18" s="3"/>
@@ -2893,8 +2976,10 @@
       <c r="BZ18" s="3"/>
       <c r="CA18" s="3"/>
       <c r="CB18" s="3"/>
-    </row>
-    <row r="19" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC18" s="3"/>
+      <c r="CD18" s="3"/>
+    </row>
+    <row r="19" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B19" s="2" t="s">
         <v>41</v>
       </c>
@@ -2926,26 +3011,28 @@
         <f t="shared" si="3"/>
         <v>1780</v>
       </c>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
+      <c r="K19" s="3">
+        <v>4262</v>
+      </c>
+      <c r="L19" s="3"/>
       <c r="M19" s="4"/>
-      <c r="N19" s="4">
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="4">
         <v>7237</v>
       </c>
-      <c r="O19" s="4">
+      <c r="Q19" s="4">
         <v>4359</v>
       </c>
-      <c r="P19" s="4">
+      <c r="R19" s="4">
         <v>3370</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="S19" s="4">
         <v>3299</v>
       </c>
-      <c r="R19" s="4">
+      <c r="T19" s="4">
         <v>3186</v>
       </c>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4"/>
       <c r="U19" s="4"/>
       <c r="V19" s="4"/>
       <c r="W19" s="4"/>
@@ -2974,8 +3061,8 @@
       <c r="AT19" s="4"/>
       <c r="AU19" s="4"/>
       <c r="AV19" s="4"/>
-      <c r="AW19" s="3"/>
-      <c r="AX19" s="3"/>
+      <c r="AW19" s="4"/>
+      <c r="AX19" s="4"/>
       <c r="AY19" s="3"/>
       <c r="AZ19" s="3"/>
       <c r="BA19" s="3"/>
@@ -3006,8 +3093,10 @@
       <c r="BZ19" s="3"/>
       <c r="CA19" s="3"/>
       <c r="CB19" s="3"/>
-    </row>
-    <row r="20" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC19" s="3"/>
+      <c r="CD19" s="3"/>
+    </row>
+    <row r="20" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B20" s="1" t="s">
         <v>42</v>
       </c>
@@ -3015,7 +3104,7 @@
         <v>25965</v>
       </c>
       <c r="D20" s="24">
-        <f>+O20-C20</f>
+        <f>+Q20-C20</f>
         <v>27686</v>
       </c>
       <c r="E20" s="25">
@@ -3039,34 +3128,36 @@
         <f t="shared" si="3"/>
         <v>41675</v>
       </c>
-      <c r="K20" s="25"/>
-      <c r="L20" s="25"/>
-      <c r="M20" s="25">
+      <c r="K20" s="24">
+        <v>43507</v>
+      </c>
+      <c r="L20" s="24"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25">
         <v>35512</v>
       </c>
-      <c r="N20" s="25">
+      <c r="P20" s="25">
         <v>49328</v>
       </c>
-      <c r="O20" s="25">
+      <c r="Q20" s="25">
         <v>53651</v>
       </c>
-      <c r="P20" s="25">
+      <c r="R20" s="25">
         <v>62356</v>
       </c>
-      <c r="Q20" s="25">
+      <c r="S20" s="25">
         <v>70826</v>
       </c>
-      <c r="R20" s="25">
+      <c r="T20" s="25">
         <v>80219</v>
       </c>
-      <c r="S20" s="25"/>
-      <c r="T20" s="25"/>
       <c r="U20" s="25"/>
       <c r="V20" s="25"/>
       <c r="W20" s="25"/>
       <c r="X20" s="25"/>
-      <c r="Y20" s="4"/>
-      <c r="Z20" s="4"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
       <c r="AA20" s="4"/>
       <c r="AB20" s="4"/>
       <c r="AC20" s="4"/>
@@ -3089,8 +3180,8 @@
       <c r="AT20" s="4"/>
       <c r="AU20" s="4"/>
       <c r="AV20" s="4"/>
-      <c r="AW20" s="3"/>
-      <c r="AX20" s="3"/>
+      <c r="AW20" s="4"/>
+      <c r="AX20" s="4"/>
       <c r="AY20" s="3"/>
       <c r="AZ20" s="3"/>
       <c r="BA20" s="3"/>
@@ -3121,8 +3212,10 @@
       <c r="BZ20" s="3"/>
       <c r="CA20" s="3"/>
       <c r="CB20" s="3"/>
-    </row>
-    <row r="21" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC20" s="3"/>
+      <c r="CD20" s="3"/>
+    </row>
+    <row r="21" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B21" s="2" t="s">
         <v>43</v>
       </c>
@@ -3154,26 +3247,28 @@
         <f t="shared" si="3"/>
         <v>16366</v>
       </c>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
+      <c r="K21" s="3">
+        <v>15715</v>
+      </c>
+      <c r="L21" s="3"/>
       <c r="M21" s="4"/>
-      <c r="N21" s="4">
+      <c r="N21" s="4"/>
+      <c r="O21" s="4"/>
+      <c r="P21" s="4">
         <v>18924</v>
       </c>
-      <c r="O21" s="4">
+      <c r="Q21" s="4">
         <v>21333</v>
       </c>
-      <c r="P21" s="4">
+      <c r="R21" s="4">
         <v>23328</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="S21" s="4">
         <v>26794</v>
       </c>
-      <c r="R21" s="4">
+      <c r="T21" s="4">
         <v>30485</v>
       </c>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
       <c r="W21" s="4"/>
@@ -3202,8 +3297,8 @@
       <c r="AT21" s="4"/>
       <c r="AU21" s="4"/>
       <c r="AV21" s="4"/>
-      <c r="AW21" s="3"/>
-      <c r="AX21" s="3"/>
+      <c r="AW21" s="4"/>
+      <c r="AX21" s="4"/>
       <c r="AY21" s="3"/>
       <c r="AZ21" s="3"/>
       <c r="BA21" s="3"/>
@@ -3234,8 +3329,10 @@
       <c r="BZ21" s="3"/>
       <c r="CA21" s="3"/>
       <c r="CB21" s="3"/>
-    </row>
-    <row r="22" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC21" s="3"/>
+      <c r="CD21" s="3"/>
+    </row>
+    <row r="22" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B22" s="2" t="s">
         <v>44</v>
       </c>
@@ -3252,7 +3349,7 @@
         <v>18755</v>
       </c>
       <c r="F22" s="4">
-        <f t="shared" ref="F22:J22" si="8">+F20-F21</f>
+        <f t="shared" ref="F22:K22" si="8">+F20-F21</f>
         <v>20273</v>
       </c>
       <c r="G22" s="4">
@@ -3271,37 +3368,40 @@
         <f t="shared" si="8"/>
         <v>25309</v>
       </c>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4">
-        <f t="shared" ref="L22:P22" si="9">+L20-L21</f>
+      <c r="K22" s="4">
+        <f t="shared" si="8"/>
+        <v>27792</v>
+      </c>
+      <c r="L22" s="4"/>
+      <c r="M22" s="4"/>
+      <c r="N22" s="4">
+        <f t="shared" ref="N22:R22" si="9">+N20-N21</f>
         <v>0</v>
       </c>
-      <c r="M22" s="4">
+      <c r="O22" s="4">
         <f t="shared" si="9"/>
         <v>35512</v>
       </c>
-      <c r="N22" s="4">
+      <c r="P22" s="4">
         <f t="shared" si="9"/>
         <v>30404</v>
       </c>
-      <c r="O22" s="4">
+      <c r="Q22" s="4">
         <f t="shared" si="9"/>
         <v>32318</v>
       </c>
-      <c r="P22" s="4">
+      <c r="R22" s="4">
         <f t="shared" si="9"/>
         <v>39028</v>
       </c>
-      <c r="Q22" s="4">
-        <f>+Q20-Q21</f>
+      <c r="S22" s="4">
+        <f>+S20-S21</f>
         <v>44032</v>
       </c>
-      <c r="R22" s="4">
-        <f>+R20-R21</f>
+      <c r="T22" s="4">
+        <f>+T20-T21</f>
         <v>49734</v>
       </c>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
       <c r="U22" s="4"/>
       <c r="V22" s="4"/>
       <c r="W22" s="4"/>
@@ -3330,8 +3430,8 @@
       <c r="AT22" s="4"/>
       <c r="AU22" s="4"/>
       <c r="AV22" s="4"/>
-      <c r="AW22" s="3"/>
-      <c r="AX22" s="3"/>
+      <c r="AW22" s="4"/>
+      <c r="AX22" s="4"/>
       <c r="AY22" s="3"/>
       <c r="AZ22" s="3"/>
       <c r="BA22" s="3"/>
@@ -3362,8 +3462,10 @@
       <c r="BZ22" s="3"/>
       <c r="CA22" s="3"/>
       <c r="CB22" s="3"/>
-    </row>
-    <row r="23" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC22" s="3"/>
+      <c r="CD22" s="3"/>
+    </row>
+    <row r="23" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
@@ -3392,29 +3494,31 @@
         <v>1315</v>
       </c>
       <c r="J23" s="3">
-        <f>+R23-I23</f>
+        <f>+T23-I23</f>
         <v>1684</v>
       </c>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
+      <c r="K23" s="3">
+        <v>1608</v>
+      </c>
+      <c r="L23" s="3"/>
       <c r="M23" s="4"/>
-      <c r="N23" s="4">
+      <c r="N23" s="4"/>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4">
         <v>1266</v>
       </c>
-      <c r="O23" s="4">
+      <c r="Q23" s="4">
         <v>2128</v>
       </c>
-      <c r="P23" s="4">
+      <c r="R23" s="4">
         <v>1705</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="S23" s="4">
         <v>2408</v>
       </c>
-      <c r="R23" s="4">
+      <c r="T23" s="4">
         <v>2999</v>
       </c>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
       <c r="W23" s="4"/>
@@ -3443,8 +3547,8 @@
       <c r="AT23" s="4"/>
       <c r="AU23" s="4"/>
       <c r="AV23" s="4"/>
-      <c r="AW23" s="3"/>
-      <c r="AX23" s="3"/>
+      <c r="AW23" s="4"/>
+      <c r="AX23" s="4"/>
       <c r="AY23" s="3"/>
       <c r="AZ23" s="3"/>
       <c r="BA23" s="3"/>
@@ -3475,8 +3579,10 @@
       <c r="BZ23" s="3"/>
       <c r="CA23" s="3"/>
       <c r="CB23" s="3"/>
-    </row>
-    <row r="24" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC23" s="3"/>
+      <c r="CD23" s="3"/>
+    </row>
+    <row r="24" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B24" s="2" t="s">
         <v>46</v>
       </c>
@@ -3505,29 +3611,31 @@
         <v>13272</v>
       </c>
       <c r="J24" s="3">
-        <f>+R24-I24</f>
+        <f>+T24-I24</f>
         <v>15184</v>
       </c>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
+      <c r="K24" s="3">
+        <v>15099</v>
+      </c>
+      <c r="L24" s="3"/>
       <c r="M24" s="4"/>
-      <c r="N24" s="4">
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4">
         <v>17753</v>
       </c>
-      <c r="O24" s="4">
+      <c r="Q24" s="4">
         <v>19629</v>
       </c>
-      <c r="P24" s="4">
+      <c r="R24" s="4">
         <v>21673</v>
       </c>
-      <c r="Q24" s="4">
+      <c r="S24" s="4">
         <v>25647</v>
       </c>
-      <c r="R24" s="4">
+      <c r="T24" s="4">
         <v>28456</v>
       </c>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
       <c r="U24" s="4"/>
       <c r="V24" s="4"/>
       <c r="W24" s="4"/>
@@ -3556,8 +3664,8 @@
       <c r="AT24" s="4"/>
       <c r="AU24" s="4"/>
       <c r="AV24" s="4"/>
-      <c r="AW24" s="3"/>
-      <c r="AX24" s="3"/>
+      <c r="AW24" s="4"/>
+      <c r="AX24" s="4"/>
       <c r="AY24" s="3"/>
       <c r="AZ24" s="3"/>
       <c r="BA24" s="3"/>
@@ -3588,8 +3696,10 @@
       <c r="BZ24" s="3"/>
       <c r="CA24" s="3"/>
       <c r="CB24" s="3"/>
-    </row>
-    <row r="25" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC24" s="3"/>
+      <c r="CD24" s="3"/>
+    </row>
+    <row r="25" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B25" s="2" t="s">
         <v>47</v>
       </c>
@@ -3618,29 +3728,31 @@
         <v>2337</v>
       </c>
       <c r="J25" s="3">
-        <f>+R25-I25</f>
+        <f>+T25-I25</f>
         <v>2849</v>
       </c>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
+      <c r="K25" s="3">
+        <v>2541</v>
+      </c>
+      <c r="L25" s="3"/>
       <c r="M25" s="4"/>
-      <c r="N25" s="4">
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
+      <c r="P25" s="4">
         <v>2928</v>
       </c>
-      <c r="O25" s="4">
+      <c r="Q25" s="4">
         <v>3587</v>
       </c>
-      <c r="P25" s="4">
+      <c r="R25" s="4">
         <v>3693</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="S25" s="4">
         <v>4198</v>
       </c>
-      <c r="R25" s="4">
+      <c r="T25" s="4">
         <v>5186</v>
       </c>
-      <c r="S25" s="4"/>
-      <c r="T25" s="4"/>
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
       <c r="W25" s="4"/>
@@ -3669,8 +3781,8 @@
       <c r="AT25" s="4"/>
       <c r="AU25" s="4"/>
       <c r="AV25" s="4"/>
-      <c r="AW25" s="3"/>
-      <c r="AX25" s="3"/>
+      <c r="AW25" s="4"/>
+      <c r="AX25" s="4"/>
       <c r="AY25" s="3"/>
       <c r="AZ25" s="3"/>
       <c r="BA25" s="3"/>
@@ -3701,8 +3813,10 @@
       <c r="BZ25" s="3"/>
       <c r="CA25" s="3"/>
       <c r="CB25" s="3"/>
-    </row>
-    <row r="26" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC25" s="3"/>
+      <c r="CD25" s="3"/>
+    </row>
+    <row r="26" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B26" s="2" t="s">
         <v>48</v>
       </c>
@@ -3727,7 +3841,7 @@
         <v>8660</v>
       </c>
       <c r="H26" s="4">
-        <f t="shared" ref="H26:R26" si="11">+H22+H23-SUM(H24:H25)</f>
+        <f t="shared" ref="H26:T26" si="11">+H22+H23-SUM(H24:H25)</f>
         <v>7935</v>
       </c>
       <c r="I26" s="4">
@@ -3738,37 +3852,40 @@
         <f t="shared" si="11"/>
         <v>8960</v>
       </c>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4">
+      <c r="K26" s="4">
+        <f t="shared" si="11"/>
+        <v>11760</v>
+      </c>
+      <c r="L26" s="4"/>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="M26" s="4">
+      <c r="O26" s="4">
         <f t="shared" si="11"/>
         <v>35512</v>
       </c>
-      <c r="N26" s="4">
+      <c r="P26" s="4">
         <f t="shared" si="11"/>
         <v>10989</v>
       </c>
-      <c r="O26" s="4">
+      <c r="Q26" s="4">
         <f t="shared" si="11"/>
         <v>11230</v>
       </c>
-      <c r="P26" s="4">
+      <c r="R26" s="4">
         <f t="shared" si="11"/>
         <v>15367</v>
       </c>
-      <c r="Q26" s="4">
+      <c r="S26" s="4">
         <f t="shared" si="11"/>
         <v>16595</v>
       </c>
-      <c r="R26" s="4">
+      <c r="T26" s="4">
         <f t="shared" si="11"/>
         <v>19091</v>
       </c>
-      <c r="S26" s="4"/>
-      <c r="T26" s="4"/>
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
       <c r="W26" s="4"/>
@@ -3797,8 +3914,8 @@
       <c r="AT26" s="4"/>
       <c r="AU26" s="4"/>
       <c r="AV26" s="4"/>
-      <c r="AW26" s="3"/>
-      <c r="AX26" s="3"/>
+      <c r="AW26" s="4"/>
+      <c r="AX26" s="4"/>
       <c r="AY26" s="3"/>
       <c r="AZ26" s="3"/>
       <c r="BA26" s="3"/>
@@ -3829,8 +3946,10 @@
       <c r="BZ26" s="3"/>
       <c r="CA26" s="3"/>
       <c r="CB26" s="3"/>
-    </row>
-    <row r="27" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC26" s="3"/>
+      <c r="CD26" s="3"/>
+    </row>
+    <row r="27" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B27" s="2" t="s">
         <v>49</v>
       </c>
@@ -3859,29 +3978,31 @@
         <v>596</v>
       </c>
       <c r="J27" s="3">
-        <f>+R27-I27</f>
+        <f>+T27-I27</f>
         <v>555</v>
       </c>
-      <c r="K27" s="4"/>
-      <c r="L27" s="4"/>
+      <c r="K27" s="3">
+        <v>507</v>
+      </c>
+      <c r="L27" s="3"/>
       <c r="M27" s="4"/>
-      <c r="N27" s="4">
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
+      <c r="P27" s="4">
         <v>332</v>
       </c>
-      <c r="O27" s="4">
+      <c r="Q27" s="4">
         <v>97</v>
       </c>
-      <c r="P27" s="4">
+      <c r="R27" s="4">
         <v>991</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="S27" s="4">
         <v>1388</v>
       </c>
-      <c r="R27" s="4">
+      <c r="T27" s="4">
         <v>1151</v>
       </c>
-      <c r="S27" s="4"/>
-      <c r="T27" s="4"/>
       <c r="U27" s="4"/>
       <c r="V27" s="4"/>
       <c r="W27" s="4"/>
@@ -3910,8 +4031,8 @@
       <c r="AT27" s="4"/>
       <c r="AU27" s="4"/>
       <c r="AV27" s="4"/>
-      <c r="AW27" s="3"/>
-      <c r="AX27" s="3"/>
+      <c r="AW27" s="4"/>
+      <c r="AX27" s="4"/>
       <c r="AY27" s="3"/>
       <c r="AZ27" s="3"/>
       <c r="BA27" s="3"/>
@@ -3942,8 +4063,10 @@
       <c r="BZ27" s="3"/>
       <c r="CA27" s="3"/>
       <c r="CB27" s="3"/>
-    </row>
-    <row r="28" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC27" s="3"/>
+      <c r="CD27" s="3"/>
+    </row>
+    <row r="28" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B28" s="2" t="s">
         <v>50</v>
       </c>
@@ -3972,29 +4095,31 @@
         <v>434</v>
       </c>
       <c r="J28" s="3">
-        <f>+R28-I28</f>
+        <f>+T28-I28</f>
         <v>769</v>
       </c>
-      <c r="K28" s="4"/>
-      <c r="L28" s="4"/>
+      <c r="K28" s="3">
+        <v>708</v>
+      </c>
+      <c r="L28" s="3"/>
       <c r="M28" s="4"/>
-      <c r="N28" s="4">
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
+      <c r="P28" s="4">
         <v>-81</v>
       </c>
-      <c r="O28" s="4">
+      <c r="Q28" s="4">
         <v>28</v>
       </c>
-      <c r="P28" s="4">
+      <c r="R28" s="4">
         <v>-718</v>
       </c>
-      <c r="Q28" s="4">
+      <c r="S28" s="4">
         <v>198</v>
       </c>
-      <c r="R28" s="4">
+      <c r="T28" s="4">
         <v>1203</v>
       </c>
-      <c r="S28" s="4"/>
-      <c r="T28" s="4"/>
       <c r="U28" s="4"/>
       <c r="V28" s="4"/>
       <c r="W28" s="4"/>
@@ -4023,8 +4148,8 @@
       <c r="AT28" s="4"/>
       <c r="AU28" s="4"/>
       <c r="AV28" s="4"/>
-      <c r="AW28" s="3"/>
-      <c r="AX28" s="3"/>
+      <c r="AW28" s="4"/>
+      <c r="AX28" s="4"/>
       <c r="AY28" s="3"/>
       <c r="AZ28" s="3"/>
       <c r="BA28" s="3"/>
@@ -4055,8 +4180,10 @@
       <c r="BZ28" s="3"/>
       <c r="CA28" s="3"/>
       <c r="CB28" s="3"/>
-    </row>
-    <row r="29" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC28" s="3"/>
+      <c r="CD28" s="3"/>
+    </row>
+    <row r="29" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B29" s="2" t="s">
         <v>51</v>
       </c>
@@ -4085,30 +4212,32 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
-        <f>+R29-I29</f>
+        <f>+T29-I29</f>
         <v>1</v>
       </c>
-      <c r="K29" s="4"/>
-      <c r="L29" s="4"/>
+      <c r="K29" s="3">
+        <v>1549</v>
+      </c>
+      <c r="L29" s="3"/>
       <c r="M29" s="4"/>
-      <c r="N29" s="4">
-        <v>0</v>
-      </c>
-      <c r="O29" s="4">
-        <v>0</v>
-      </c>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
       <c r="P29" s="4">
         <v>0</v>
       </c>
       <c r="Q29" s="4">
+        <v>0</v>
+      </c>
+      <c r="R29" s="4">
+        <v>0</v>
+      </c>
+      <c r="S29" s="4">
         <f>1579+2090+34</f>
         <v>3703</v>
       </c>
-      <c r="R29" s="4">
+      <c r="T29" s="4">
         <v>1</v>
       </c>
-      <c r="S29" s="4"/>
-      <c r="T29" s="4"/>
       <c r="U29" s="4"/>
       <c r="V29" s="4"/>
       <c r="W29" s="4"/>
@@ -4137,8 +4266,8 @@
       <c r="AT29" s="4"/>
       <c r="AU29" s="4"/>
       <c r="AV29" s="4"/>
-      <c r="AW29" s="3"/>
-      <c r="AX29" s="3"/>
+      <c r="AW29" s="4"/>
+      <c r="AX29" s="4"/>
       <c r="AY29" s="3"/>
       <c r="AZ29" s="3"/>
       <c r="BA29" s="3"/>
@@ -4169,8 +4298,10 @@
       <c r="BZ29" s="3"/>
       <c r="CA29" s="3"/>
       <c r="CB29" s="3"/>
-    </row>
-    <row r="30" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC29" s="3"/>
+      <c r="CD29" s="3"/>
+    </row>
+    <row r="30" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B30" s="2" t="s">
         <v>52</v>
       </c>
@@ -4195,7 +4326,7 @@
         <v>10930</v>
       </c>
       <c r="H30" s="4">
-        <f t="shared" ref="H30:R30" si="13">+H26+SUM(H27:H29)</f>
+        <f t="shared" ref="H30:T30" si="13">+H26+SUM(H27:H29)</f>
         <v>10954</v>
       </c>
       <c r="I30" s="4">
@@ -4206,37 +4337,40 @@
         <f t="shared" si="13"/>
         <v>10285</v>
       </c>
-      <c r="K30" s="4"/>
-      <c r="L30" s="4">
+      <c r="K30" s="4">
+        <f t="shared" si="13"/>
+        <v>14524</v>
+      </c>
+      <c r="L30" s="4"/>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="M30" s="4">
+      <c r="O30" s="4">
         <f t="shared" si="13"/>
         <v>35512</v>
       </c>
-      <c r="N30" s="4">
+      <c r="P30" s="4">
         <f t="shared" si="13"/>
         <v>11240</v>
       </c>
-      <c r="O30" s="4">
+      <c r="Q30" s="4">
         <f t="shared" si="13"/>
         <v>11355</v>
       </c>
-      <c r="P30" s="4">
+      <c r="R30" s="4">
         <f t="shared" si="13"/>
         <v>15640</v>
       </c>
-      <c r="Q30" s="4">
+      <c r="S30" s="4">
         <f t="shared" si="13"/>
         <v>21884</v>
       </c>
-      <c r="R30" s="4">
+      <c r="T30" s="4">
         <f t="shared" si="13"/>
         <v>21446</v>
       </c>
-      <c r="S30" s="4"/>
-      <c r="T30" s="4"/>
       <c r="U30" s="4"/>
       <c r="V30" s="4"/>
       <c r="W30" s="4"/>
@@ -4265,8 +4399,8 @@
       <c r="AT30" s="4"/>
       <c r="AU30" s="4"/>
       <c r="AV30" s="4"/>
-      <c r="AW30" s="3"/>
-      <c r="AX30" s="3"/>
+      <c r="AW30" s="4"/>
+      <c r="AX30" s="4"/>
       <c r="AY30" s="3"/>
       <c r="AZ30" s="3"/>
       <c r="BA30" s="3"/>
@@ -4297,8 +4431,10 @@
       <c r="BZ30" s="3"/>
       <c r="CA30" s="3"/>
       <c r="CB30" s="3"/>
-    </row>
-    <row r="31" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC30" s="3"/>
+      <c r="CD30" s="3"/>
+    </row>
+    <row r="31" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B31" s="2" t="s">
         <v>53</v>
       </c>
@@ -4327,29 +4463,31 @@
         <v>3050</v>
       </c>
       <c r="J31" s="3">
-        <f>+R31-I31</f>
+        <f>+T31-I31</f>
         <v>2734</v>
       </c>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
+      <c r="K31" s="3">
+        <v>3605</v>
+      </c>
+      <c r="L31" s="3"/>
       <c r="M31" s="4"/>
-      <c r="N31" s="4">
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
+      <c r="P31" s="4">
         <v>3021</v>
       </c>
-      <c r="O31" s="4">
+      <c r="Q31" s="4">
         <v>3110</v>
       </c>
-      <c r="P31" s="4">
+      <c r="R31" s="4">
         <v>4363</v>
       </c>
-      <c r="Q31" s="4">
+      <c r="S31" s="4">
         <v>4895</v>
       </c>
-      <c r="R31" s="4">
+      <c r="T31" s="4">
         <v>5784</v>
       </c>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
       <c r="U31" s="4"/>
       <c r="V31" s="4"/>
       <c r="W31" s="4"/>
@@ -4378,8 +4516,8 @@
       <c r="AT31" s="4"/>
       <c r="AU31" s="4"/>
       <c r="AV31" s="4"/>
-      <c r="AW31" s="3"/>
-      <c r="AX31" s="3"/>
+      <c r="AW31" s="4"/>
+      <c r="AX31" s="4"/>
       <c r="AY31" s="3"/>
       <c r="AZ31" s="3"/>
       <c r="BA31" s="3"/>
@@ -4410,8 +4548,10 @@
       <c r="BZ31" s="3"/>
       <c r="CA31" s="3"/>
       <c r="CB31" s="3"/>
-    </row>
-    <row r="32" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC31" s="3"/>
+      <c r="CD31" s="3"/>
+    </row>
+    <row r="32" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B32" s="2" t="s">
         <v>54</v>
       </c>
@@ -4436,7 +4576,7 @@
         <v>8419</v>
       </c>
       <c r="H32" s="4">
-        <f t="shared" ref="H32:J32" si="15">+H30-H31</f>
+        <f t="shared" ref="H32:K32" si="15">+H30-H31</f>
         <v>8570</v>
       </c>
       <c r="I32" s="4">
@@ -4447,37 +4587,40 @@
         <f t="shared" si="15"/>
         <v>7551</v>
       </c>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4">
-        <f t="shared" ref="L32:P32" si="16">+L30-L31</f>
+      <c r="K32" s="4">
+        <f t="shared" si="15"/>
+        <v>10919</v>
+      </c>
+      <c r="L32" s="4"/>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4">
+        <f t="shared" ref="N32:R32" si="16">+N30-N31</f>
         <v>0</v>
       </c>
-      <c r="M32" s="4">
+      <c r="O32" s="4">
         <f t="shared" si="16"/>
         <v>35512</v>
       </c>
-      <c r="N32" s="4">
+      <c r="P32" s="4">
         <f t="shared" si="16"/>
         <v>8219</v>
       </c>
-      <c r="O32" s="4">
+      <c r="Q32" s="4">
         <f t="shared" si="16"/>
         <v>8245</v>
       </c>
-      <c r="P32" s="4">
+      <c r="R32" s="4">
         <f t="shared" si="16"/>
         <v>11277</v>
       </c>
-      <c r="Q32" s="4">
-        <f>+Q30-Q31</f>
+      <c r="S32" s="4">
+        <f>+S30-S31</f>
         <v>16989</v>
       </c>
-      <c r="R32" s="4">
-        <f>+R30-R31</f>
+      <c r="T32" s="4">
+        <f>+T30-T31</f>
         <v>15662</v>
       </c>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
       <c r="W32" s="4"/>
@@ -4506,8 +4649,8 @@
       <c r="AT32" s="4"/>
       <c r="AU32" s="4"/>
       <c r="AV32" s="4"/>
-      <c r="AW32" s="3"/>
-      <c r="AX32" s="3"/>
+      <c r="AW32" s="4"/>
+      <c r="AX32" s="4"/>
       <c r="AY32" s="3"/>
       <c r="AZ32" s="3"/>
       <c r="BA32" s="3"/>
@@ -4538,8 +4681,10 @@
       <c r="BZ32" s="3"/>
       <c r="CA32" s="3"/>
       <c r="CB32" s="3"/>
-    </row>
-    <row r="33" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC32" s="3"/>
+      <c r="CD32" s="3"/>
+    </row>
+    <row r="33" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B33" s="2" t="s">
         <v>55</v>
       </c>
@@ -4568,29 +4713,31 @@
         <v>1080</v>
       </c>
       <c r="J33" s="3">
-        <f>+R33-I33</f>
+        <f>+T33-I33</f>
         <v>994</v>
       </c>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
+      <c r="K33" s="3">
+        <v>1432</v>
+      </c>
+      <c r="L33" s="3"/>
       <c r="M33" s="4"/>
-      <c r="N33" s="4">
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
+      <c r="P33" s="4">
         <v>499</v>
       </c>
-      <c r="O33" s="4">
+      <c r="Q33" s="4">
         <v>655</v>
       </c>
-      <c r="P33" s="4">
+      <c r="R33" s="4">
         <v>1041</v>
       </c>
-      <c r="Q33" s="4">
+      <c r="S33" s="4">
         <v>1393</v>
       </c>
-      <c r="R33" s="4">
+      <c r="T33" s="4">
         <v>2074</v>
       </c>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
       <c r="U33" s="4"/>
       <c r="V33" s="4"/>
       <c r="W33" s="4"/>
@@ -4619,8 +4766,8 @@
       <c r="AT33" s="4"/>
       <c r="AU33" s="4"/>
       <c r="AV33" s="4"/>
-      <c r="AW33" s="3"/>
-      <c r="AX33" s="3"/>
+      <c r="AW33" s="4"/>
+      <c r="AX33" s="4"/>
       <c r="AY33" s="3"/>
       <c r="AZ33" s="3"/>
       <c r="BA33" s="3"/>
@@ -4651,8 +4798,10 @@
       <c r="BZ33" s="3"/>
       <c r="CA33" s="3"/>
       <c r="CB33" s="3"/>
-    </row>
-    <row r="34" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC33" s="3"/>
+      <c r="CD33" s="3"/>
+    </row>
+    <row r="34" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B34" s="2" t="s">
         <v>56</v>
       </c>
@@ -4677,7 +4826,7 @@
         <v>7721</v>
       </c>
       <c r="H34" s="4">
-        <f t="shared" ref="H34:J34" si="18">+H32-H33</f>
+        <f t="shared" ref="H34:K34" si="18">+H32-H33</f>
         <v>7875</v>
       </c>
       <c r="I34" s="4">
@@ -4688,37 +4837,40 @@
         <f t="shared" si="18"/>
         <v>6557</v>
       </c>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4">
-        <f t="shared" ref="L34:P34" si="19">+L32-L33</f>
+      <c r="K34" s="4">
+        <f t="shared" si="18"/>
+        <v>9487</v>
+      </c>
+      <c r="L34" s="4"/>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4">
+        <f t="shared" ref="N34:R34" si="19">+N32-N33</f>
         <v>0</v>
       </c>
-      <c r="M34" s="4">
+      <c r="O34" s="4">
         <f t="shared" si="19"/>
         <v>35512</v>
       </c>
-      <c r="N34" s="4">
+      <c r="P34" s="4">
         <f t="shared" si="19"/>
         <v>7720</v>
       </c>
-      <c r="O34" s="4">
+      <c r="Q34" s="4">
         <f t="shared" si="19"/>
         <v>7590</v>
       </c>
-      <c r="P34" s="4">
+      <c r="R34" s="4">
         <f t="shared" si="19"/>
         <v>10236</v>
       </c>
-      <c r="Q34" s="4">
-        <f>+Q32-Q33</f>
+      <c r="S34" s="4">
+        <f>+S32-S33</f>
         <v>15596</v>
       </c>
-      <c r="R34" s="4">
-        <f>+R32-R33</f>
+      <c r="T34" s="4">
+        <f>+T32-T33</f>
         <v>13588</v>
       </c>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
       <c r="U34" s="4"/>
       <c r="V34" s="4"/>
       <c r="W34" s="4"/>
@@ -4747,8 +4899,8 @@
       <c r="AT34" s="4"/>
       <c r="AU34" s="4"/>
       <c r="AV34" s="4"/>
-      <c r="AW34" s="3"/>
-      <c r="AX34" s="3"/>
+      <c r="AW34" s="4"/>
+      <c r="AX34" s="4"/>
       <c r="AY34" s="3"/>
       <c r="AZ34" s="3"/>
       <c r="BA34" s="3"/>
@@ -4779,8 +4931,10 @@
       <c r="BZ34" s="3"/>
       <c r="CA34" s="3"/>
       <c r="CB34" s="3"/>
-    </row>
-    <row r="35" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC34" s="3"/>
+      <c r="CD34" s="3"/>
+    </row>
+    <row r="35" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="4"/>
@@ -4827,8 +4981,8 @@
       <c r="AT35" s="4"/>
       <c r="AU35" s="4"/>
       <c r="AV35" s="4"/>
-      <c r="AW35" s="3"/>
-      <c r="AX35" s="3"/>
+      <c r="AW35" s="4"/>
+      <c r="AX35" s="4"/>
       <c r="AY35" s="3"/>
       <c r="AZ35" s="3"/>
       <c r="BA35" s="3"/>
@@ -4859,8 +5013,10 @@
       <c r="BZ35" s="3"/>
       <c r="CA35" s="3"/>
       <c r="CB35" s="3"/>
-    </row>
-    <row r="36" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC35" s="3"/>
+      <c r="CD35" s="3"/>
+    </row>
+    <row r="36" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B36" s="2" t="s">
         <v>57</v>
       </c>
@@ -4877,7 +5033,7 @@
         <v>1.7353820197902265</v>
       </c>
       <c r="F36" s="26">
-        <f t="shared" ref="F36:J36" si="21">+F34/F37</f>
+        <f t="shared" ref="F36:K36" si="21">+F34/F37</f>
         <v>1.9778394050624473</v>
       </c>
       <c r="G36" s="26">
@@ -4896,37 +5052,40 @@
         <f t="shared" si="21"/>
         <v>2.3582666290705907</v>
       </c>
-      <c r="K36" s="4"/>
-      <c r="L36" s="26" t="e">
-        <f t="shared" ref="L36:P36" si="22">+L34/L37</f>
+      <c r="K36" s="26">
+        <f t="shared" si="21"/>
+        <v>3.4240444652975786</v>
+      </c>
+      <c r="L36" s="26"/>
+      <c r="M36" s="4"/>
+      <c r="N36" s="26" t="e">
+        <f t="shared" ref="N36:R36" si="22">+N34/N37</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="M36" s="26" t="e">
+      <c r="O36" s="26" t="e">
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N36" s="26">
+      <c r="P36" s="26">
         <f t="shared" si="22"/>
         <v>2.8695321844796968</v>
       </c>
-      <c r="O36" s="26">
+      <c r="Q36" s="26">
         <f t="shared" si="22"/>
         <v>2.8192053629531899</v>
       </c>
-      <c r="P36" s="26">
+      <c r="R36" s="26">
         <f t="shared" si="22"/>
         <v>3.6889876367017513</v>
       </c>
-      <c r="Q36" s="26">
-        <f>+Q34/Q37</f>
+      <c r="S36" s="26">
+        <f>+S34/S37</f>
         <v>5.5533854607127182</v>
       </c>
-      <c r="R36" s="26">
-        <f>+R34/R37</f>
+      <c r="T36" s="26">
+        <f>+T34/T37</f>
         <v>4.8870103638571276</v>
       </c>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
       <c r="U36" s="4"/>
       <c r="V36" s="4"/>
       <c r="W36" s="4"/>
@@ -4955,8 +5114,8 @@
       <c r="AT36" s="4"/>
       <c r="AU36" s="4"/>
       <c r="AV36" s="4"/>
-      <c r="AW36" s="3"/>
-      <c r="AX36" s="3"/>
+      <c r="AW36" s="4"/>
+      <c r="AX36" s="4"/>
       <c r="AY36" s="3"/>
       <c r="AZ36" s="3"/>
       <c r="BA36" s="3"/>
@@ -4987,8 +5146,10 @@
       <c r="BZ36" s="3"/>
       <c r="CA36" s="3"/>
       <c r="CB36" s="3"/>
-    </row>
-    <row r="37" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC36" s="3"/>
+      <c r="CD36" s="3"/>
+    </row>
+    <row r="37" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B37" s="2" t="s">
         <v>1</v>
       </c>
@@ -4996,21 +5157,21 @@
         <v>2691.614</v>
       </c>
       <c r="D37" s="3">
-        <f>+O37</f>
+        <f>+Q37</f>
         <v>2692.248</v>
       </c>
       <c r="E37" s="4">
         <v>2735.9969999999998</v>
       </c>
       <c r="F37" s="4">
-        <f>+P37</f>
+        <f>+R37</f>
         <v>2774.7449999999999</v>
       </c>
       <c r="G37" s="4">
         <v>2811.5770000000002</v>
       </c>
       <c r="H37" s="4">
-        <f>+Q37</f>
+        <f>+S37</f>
         <v>2808.377</v>
       </c>
       <c r="I37" s="4">
@@ -5019,26 +5180,28 @@
       <c r="J37" s="4">
         <v>2780.4319999999998</v>
       </c>
-      <c r="K37" s="4"/>
+      <c r="K37" s="4">
+        <v>2770.7</v>
+      </c>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
-      <c r="N37" s="4">
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
+      <c r="P37" s="4">
         <v>2690.3339999999998</v>
       </c>
-      <c r="O37" s="4">
+      <c r="Q37" s="4">
         <v>2692.248</v>
       </c>
-      <c r="P37" s="4">
+      <c r="R37" s="4">
         <v>2774.7449999999999</v>
       </c>
-      <c r="Q37" s="4">
+      <c r="S37" s="4">
         <v>2808.377</v>
       </c>
-      <c r="R37" s="4">
+      <c r="T37" s="4">
         <v>2780.4319999999998</v>
       </c>
-      <c r="S37" s="4"/>
-      <c r="T37" s="4"/>
       <c r="U37" s="4"/>
       <c r="V37" s="4"/>
       <c r="W37" s="4"/>
@@ -5067,8 +5230,8 @@
       <c r="AT37" s="4"/>
       <c r="AU37" s="4"/>
       <c r="AV37" s="4"/>
-      <c r="AW37" s="3"/>
-      <c r="AX37" s="3"/>
+      <c r="AW37" s="4"/>
+      <c r="AX37" s="4"/>
       <c r="AY37" s="3"/>
       <c r="AZ37" s="3"/>
       <c r="BA37" s="3"/>
@@ -5099,8 +5262,10 @@
       <c r="BZ37" s="3"/>
       <c r="CA37" s="3"/>
       <c r="CB37" s="3"/>
-    </row>
-    <row r="38" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC37" s="3"/>
+      <c r="CD37" s="3"/>
+    </row>
+    <row r="38" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="4"/>
@@ -5147,8 +5312,8 @@
       <c r="AT38" s="4"/>
       <c r="AU38" s="4"/>
       <c r="AV38" s="4"/>
-      <c r="AW38" s="3"/>
-      <c r="AX38" s="3"/>
+      <c r="AW38" s="4"/>
+      <c r="AX38" s="4"/>
       <c r="AY38" s="3"/>
       <c r="AZ38" s="3"/>
       <c r="BA38" s="3"/>
@@ -5179,15 +5344,17 @@
       <c r="BZ38" s="3"/>
       <c r="CA38" s="3"/>
       <c r="CB38" s="3"/>
-    </row>
-    <row r="39" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC38" s="3"/>
+      <c r="CD38" s="3"/>
+    </row>
+    <row r="39" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B39" s="2" t="s">
         <v>58</v>
       </c>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="27">
-        <f t="shared" ref="E39:J39" si="23">+E9/C9-1</f>
+        <f t="shared" ref="E39:K39" si="23">+E9/C9-1</f>
         <v>2.927713964936518E-2</v>
       </c>
       <c r="F39" s="27">
@@ -5210,34 +5377,37 @@
         <f t="shared" si="23"/>
         <v>-8.1170135819336187E-3</v>
       </c>
-      <c r="K39" s="4"/>
-      <c r="L39" s="4"/>
-      <c r="M39" s="27" t="e">
-        <f t="shared" ref="M39:R39" si="24">+M9/L9-1</f>
+      <c r="K39" s="27">
+        <f t="shared" si="23"/>
+        <v>-2.7623865735164177E-2</v>
+      </c>
+      <c r="L39" s="27"/>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="27" t="e">
+        <f t="shared" ref="O39:T39" si="24">+O9/N9-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N39" s="27" t="e">
+      <c r="P39" s="27" t="e">
         <f t="shared" si="24"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O39" s="27">
+      <c r="Q39" s="27">
         <f t="shared" si="24"/>
         <v>1.2294386976428706E-2</v>
       </c>
-      <c r="P39" s="27">
+      <c r="R39" s="27">
         <f t="shared" si="24"/>
         <v>1.8008208392662706E-2</v>
       </c>
-      <c r="Q39" s="27">
+      <c r="S39" s="27">
         <f t="shared" si="24"/>
         <v>1.991114036531183E-2</v>
       </c>
-      <c r="R39" s="27">
+      <c r="T39" s="27">
         <f t="shared" si="24"/>
         <v>-4.3562439496611649E-3</v>
       </c>
-      <c r="S39" s="4"/>
-      <c r="T39" s="4"/>
       <c r="U39" s="4"/>
       <c r="V39" s="4"/>
       <c r="W39" s="4"/>
@@ -5266,8 +5436,8 @@
       <c r="AT39" s="4"/>
       <c r="AU39" s="4"/>
       <c r="AV39" s="4"/>
-      <c r="AW39" s="3"/>
-      <c r="AX39" s="3"/>
+      <c r="AW39" s="4"/>
+      <c r="AX39" s="4"/>
       <c r="AY39" s="3"/>
       <c r="AZ39" s="3"/>
       <c r="BA39" s="3"/>
@@ -5298,8 +5468,10 @@
       <c r="BZ39" s="3"/>
       <c r="CA39" s="3"/>
       <c r="CB39" s="3"/>
-    </row>
-    <row r="40" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC39" s="3"/>
+      <c r="CD39" s="3"/>
+    </row>
+    <row r="40" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B40" s="2" t="s">
         <v>59</v>
       </c>
@@ -5318,7 +5490,7 @@
         <v>0.17957604578060771</v>
       </c>
       <c r="H40" s="27">
-        <f t="shared" ref="H40:J49" si="26">+H11/F11-1</f>
+        <f t="shared" ref="H40:K49" si="26">+H11/F11-1</f>
         <v>0.12704061895551266</v>
       </c>
       <c r="I40" s="27">
@@ -5329,34 +5501,37 @@
         <f t="shared" si="26"/>
         <v>3.3774970824466344E-2</v>
       </c>
-      <c r="K40" s="4"/>
-      <c r="L40" s="4"/>
-      <c r="M40" s="27" t="e">
-        <f t="shared" ref="M40:P49" si="27">+M11/L11-1</f>
+      <c r="K40" s="27">
+        <f t="shared" si="26"/>
+        <v>4.6857840146430796E-2</v>
+      </c>
+      <c r="L40" s="27"/>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="27" t="e">
+        <f t="shared" ref="O40:R49" si="27">+O11/N11-1</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N40" s="27" t="e">
+      <c r="P40" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O40" s="27">
+      <c r="Q40" s="27">
         <f t="shared" si="27"/>
         <v>0.17409478029155134</v>
       </c>
-      <c r="P40" s="27">
+      <c r="R40" s="27">
         <f t="shared" si="27"/>
         <v>0.12731965644608612</v>
       </c>
-      <c r="Q40" s="27">
-        <f>+Q11/P11-1</f>
+      <c r="S40" s="27">
+        <f>+S11/R11-1</f>
         <v>0.15277119848413068</v>
       </c>
-      <c r="R40" s="27">
-        <f>+R11/Q11-1</f>
+      <c r="T40" s="27">
+        <f>+T11/S11-1</f>
         <v>7.6946784466817242E-2</v>
       </c>
-      <c r="S40" s="4"/>
-      <c r="T40" s="4"/>
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
       <c r="W40" s="4"/>
@@ -5385,8 +5560,8 @@
       <c r="AT40" s="4"/>
       <c r="AU40" s="4"/>
       <c r="AV40" s="4"/>
-      <c r="AW40" s="3"/>
-      <c r="AX40" s="3"/>
+      <c r="AW40" s="4"/>
+      <c r="AX40" s="4"/>
       <c r="AY40" s="3"/>
       <c r="AZ40" s="3"/>
       <c r="BA40" s="3"/>
@@ -5417,8 +5592,10 @@
       <c r="BZ40" s="3"/>
       <c r="CA40" s="3"/>
       <c r="CB40" s="3"/>
-    </row>
-    <row r="41" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC40" s="3"/>
+      <c r="CD40" s="3"/>
+    </row>
+    <row r="41" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B41" s="2" t="s">
         <v>60</v>
       </c>
@@ -5448,34 +5625,37 @@
         <f t="shared" si="26"/>
         <v>0.17016382669107633</v>
       </c>
-      <c r="K41" s="4"/>
-      <c r="L41" s="4"/>
-      <c r="M41" s="27" t="e">
+      <c r="K41" s="27">
+        <f t="shared" si="26"/>
+        <v>0.19031887388681423</v>
+      </c>
+      <c r="L41" s="27"/>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N41" s="27" t="e">
+      <c r="P41" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O41" s="27">
+      <c r="Q41" s="27">
         <f t="shared" si="27"/>
         <v>3.111902766135799E-2</v>
       </c>
-      <c r="P41" s="27">
+      <c r="R41" s="27">
         <f t="shared" si="27"/>
         <v>0.18778579412661323</v>
       </c>
-      <c r="Q41" s="27">
-        <f t="shared" ref="Q41:R49" si="29">+Q12/P12-1</f>
+      <c r="S41" s="27">
+        <f t="shared" ref="S41:T49" si="29">+S12/R12-1</f>
         <v>0.12313571163772208</v>
       </c>
-      <c r="R41" s="27">
+      <c r="T41" s="27">
         <f t="shared" si="29"/>
         <v>0.16323473403580047</v>
       </c>
-      <c r="S41" s="4"/>
-      <c r="T41" s="4"/>
       <c r="U41" s="4"/>
       <c r="V41" s="4"/>
       <c r="W41" s="4"/>
@@ -5504,8 +5684,8 @@
       <c r="AT41" s="4"/>
       <c r="AU41" s="4"/>
       <c r="AV41" s="4"/>
-      <c r="AW41" s="3"/>
-      <c r="AX41" s="3"/>
+      <c r="AW41" s="4"/>
+      <c r="AX41" s="4"/>
       <c r="AY41" s="3"/>
       <c r="AZ41" s="3"/>
       <c r="BA41" s="3"/>
@@ -5536,8 +5716,10 @@
       <c r="BZ41" s="3"/>
       <c r="CA41" s="3"/>
       <c r="CB41" s="3"/>
-    </row>
-    <row r="42" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC41" s="3"/>
+      <c r="CD41" s="3"/>
+    </row>
+    <row r="42" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B42" s="2" t="s">
         <v>61</v>
       </c>
@@ -5567,34 +5749,37 @@
         <f t="shared" si="26"/>
         <v>0.34152334152334163</v>
       </c>
-      <c r="K42" s="4"/>
-      <c r="L42" s="4"/>
-      <c r="M42" s="27" t="e">
+      <c r="K42" s="27">
+        <f t="shared" si="26"/>
+        <v>0.17350157728706628</v>
+      </c>
+      <c r="L42" s="27"/>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N42" s="27" t="e">
+      <c r="P42" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O42" s="27">
+      <c r="Q42" s="27">
         <f t="shared" si="27"/>
         <v>6.4226075786769421E-2</v>
       </c>
-      <c r="P42" s="27">
+      <c r="R42" s="27">
         <f t="shared" si="27"/>
         <v>0.18105009052504517</v>
       </c>
-      <c r="Q42" s="27">
+      <c r="S42" s="27">
         <f t="shared" si="29"/>
         <v>0.14409810935104761</v>
       </c>
-      <c r="R42" s="27">
+      <c r="T42" s="27">
         <f t="shared" si="29"/>
         <v>0.29790084859312183</v>
       </c>
-      <c r="S42" s="4"/>
-      <c r="T42" s="4"/>
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
       <c r="W42" s="4"/>
@@ -5623,8 +5808,8 @@
       <c r="AT42" s="4"/>
       <c r="AU42" s="4"/>
       <c r="AV42" s="4"/>
-      <c r="AW42" s="3"/>
-      <c r="AX42" s="3"/>
+      <c r="AW42" s="4"/>
+      <c r="AX42" s="4"/>
       <c r="AY42" s="3"/>
       <c r="AZ42" s="3"/>
       <c r="BA42" s="3"/>
@@ -5655,8 +5840,10 @@
       <c r="BZ42" s="3"/>
       <c r="CA42" s="3"/>
       <c r="CB42" s="3"/>
-    </row>
-    <row r="43" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC42" s="3"/>
+      <c r="CD42" s="3"/>
+    </row>
+    <row r="43" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B43" s="2" t="s">
         <v>62</v>
       </c>
@@ -5686,34 +5873,37 @@
         <f t="shared" si="26"/>
         <v>2.0578962453424943E-2</v>
       </c>
-      <c r="K43" s="4"/>
-      <c r="L43" s="4"/>
-      <c r="M43" s="27" t="e">
+      <c r="K43" s="27">
+        <f t="shared" si="26"/>
+        <v>4.7256637168141546E-2</v>
+      </c>
+      <c r="L43" s="27"/>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N43" s="27" t="e">
+      <c r="P43" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O43" s="27">
+      <c r="Q43" s="27">
         <f t="shared" si="27"/>
         <v>0.15454772613693146</v>
       </c>
-      <c r="P43" s="27">
+      <c r="R43" s="27">
         <f t="shared" si="27"/>
         <v>9.3171734660751016E-2</v>
       </c>
-      <c r="Q43" s="27">
+      <c r="S43" s="27">
         <f t="shared" si="29"/>
         <v>0.1061176004751534</v>
       </c>
-      <c r="R43" s="27">
+      <c r="T43" s="27">
         <f t="shared" si="29"/>
         <v>3.6751983771851293E-2</v>
       </c>
-      <c r="S43" s="4"/>
-      <c r="T43" s="4"/>
       <c r="U43" s="4"/>
       <c r="V43" s="4"/>
       <c r="W43" s="4"/>
@@ -5742,8 +5932,8 @@
       <c r="AT43" s="4"/>
       <c r="AU43" s="4"/>
       <c r="AV43" s="4"/>
-      <c r="AW43" s="3"/>
-      <c r="AX43" s="3"/>
+      <c r="AW43" s="4"/>
+      <c r="AX43" s="4"/>
       <c r="AY43" s="3"/>
       <c r="AZ43" s="3"/>
       <c r="BA43" s="3"/>
@@ -5774,8 +5964,10 @@
       <c r="BZ43" s="3"/>
       <c r="CA43" s="3"/>
       <c r="CB43" s="3"/>
-    </row>
-    <row r="44" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC43" s="3"/>
+      <c r="CD43" s="3"/>
+    </row>
+    <row r="44" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B44" s="2" t="s">
         <v>63</v>
       </c>
@@ -5805,34 +5997,37 @@
         <f t="shared" si="26"/>
         <v>5.2837140751658129E-2</v>
       </c>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
-      <c r="M44" s="27" t="e">
+      <c r="K44" s="27">
+        <f t="shared" si="26"/>
+        <v>6.0851783951487715E-2</v>
+      </c>
+      <c r="L44" s="27"/>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N44" s="27" t="e">
+      <c r="P44" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O44" s="27">
+      <c r="Q44" s="27">
         <f t="shared" si="27"/>
         <v>-1.3701768857116714E-2</v>
       </c>
-      <c r="P44" s="27">
+      <c r="R44" s="27">
         <f t="shared" si="27"/>
         <v>0.16633368954142091</v>
       </c>
-      <c r="Q44" s="27">
+      <c r="S44" s="27">
         <f t="shared" si="29"/>
         <v>6.0670039437517476E-2</v>
       </c>
-      <c r="R44" s="27">
+      <c r="T44" s="27">
         <f t="shared" si="29"/>
         <v>6.9218057537745015E-2</v>
       </c>
-      <c r="S44" s="4"/>
-      <c r="T44" s="4"/>
       <c r="U44" s="4"/>
       <c r="V44" s="4"/>
       <c r="W44" s="4"/>
@@ -5861,8 +6056,8 @@
       <c r="AT44" s="4"/>
       <c r="AU44" s="4"/>
       <c r="AV44" s="4"/>
-      <c r="AW44" s="3"/>
-      <c r="AX44" s="3"/>
+      <c r="AW44" s="4"/>
+      <c r="AX44" s="4"/>
       <c r="AY44" s="3"/>
       <c r="AZ44" s="3"/>
       <c r="BA44" s="3"/>
@@ -5893,8 +6088,10 @@
       <c r="BZ44" s="3"/>
       <c r="CA44" s="3"/>
       <c r="CB44" s="3"/>
-    </row>
-    <row r="45" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC44" s="3"/>
+      <c r="CD44" s="3"/>
+    </row>
+    <row r="45" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B45" s="2" t="s">
         <v>64</v>
       </c>
@@ -5924,34 +6121,37 @@
         <f t="shared" si="26"/>
         <v>0.57735352205398294</v>
       </c>
-      <c r="K45" s="4"/>
-      <c r="L45" s="4"/>
-      <c r="M45" s="27" t="e">
+      <c r="K45" s="27">
+        <f t="shared" si="26"/>
+        <v>5.4371289800323908E-2</v>
+      </c>
+      <c r="L45" s="27"/>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N45" s="27" t="e">
+      <c r="P45" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O45" s="27">
+      <c r="Q45" s="27">
         <f t="shared" si="27"/>
         <v>0.26073268460217514</v>
       </c>
-      <c r="P45" s="27">
+      <c r="R45" s="27">
         <f t="shared" si="27"/>
         <v>0.57707150964812715</v>
       </c>
-      <c r="Q45" s="27">
+      <c r="S45" s="27">
         <f t="shared" si="29"/>
         <v>0.53706635957967475</v>
       </c>
-      <c r="R45" s="27">
+      <c r="T45" s="27">
         <f t="shared" si="29"/>
         <v>0.59168383592433038</v>
       </c>
-      <c r="S45" s="4"/>
-      <c r="T45" s="4"/>
       <c r="U45" s="4"/>
       <c r="V45" s="4"/>
       <c r="W45" s="4"/>
@@ -5980,8 +6180,8 @@
       <c r="AT45" s="4"/>
       <c r="AU45" s="4"/>
       <c r="AV45" s="4"/>
-      <c r="AW45" s="3"/>
-      <c r="AX45" s="3"/>
+      <c r="AW45" s="4"/>
+      <c r="AX45" s="4"/>
       <c r="AY45" s="3"/>
       <c r="AZ45" s="3"/>
       <c r="BA45" s="3"/>
@@ -6012,8 +6212,10 @@
       <c r="BZ45" s="3"/>
       <c r="CA45" s="3"/>
       <c r="CB45" s="3"/>
-    </row>
-    <row r="46" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC45" s="3"/>
+      <c r="CD45" s="3"/>
+    </row>
+    <row r="46" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B46" s="2" t="s">
         <v>65</v>
       </c>
@@ -6043,34 +6245,37 @@
         <f t="shared" si="26"/>
         <v>-9.6763788839904219E-4</v>
       </c>
-      <c r="K46" s="4"/>
-      <c r="L46" s="4"/>
-      <c r="M46" s="27" t="e">
+      <c r="K46" s="27">
+        <f t="shared" si="26"/>
+        <v>-0.30309146924466168</v>
+      </c>
+      <c r="L46" s="27"/>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N46" s="27" t="e">
+      <c r="P46" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O46" s="27">
+      <c r="Q46" s="27">
         <f t="shared" si="27"/>
         <v>0.60007014262333414</v>
       </c>
-      <c r="P46" s="27">
+      <c r="R46" s="27">
         <f t="shared" si="27"/>
         <v>0.24241981442244476</v>
       </c>
-      <c r="Q46" s="27">
+      <c r="S46" s="27">
         <f t="shared" si="29"/>
         <v>7.2508085857100779E-2</v>
       </c>
-      <c r="R46" s="27">
+      <c r="T46" s="27">
         <f t="shared" si="29"/>
         <v>2.5605877837482138E-2</v>
       </c>
-      <c r="S46" s="4"/>
-      <c r="T46" s="4"/>
       <c r="U46" s="4"/>
       <c r="V46" s="4"/>
       <c r="W46" s="4"/>
@@ -6099,8 +6304,8 @@
       <c r="AT46" s="4"/>
       <c r="AU46" s="4"/>
       <c r="AV46" s="4"/>
-      <c r="AW46" s="3"/>
-      <c r="AX46" s="3"/>
+      <c r="AW46" s="4"/>
+      <c r="AX46" s="4"/>
       <c r="AY46" s="3"/>
       <c r="AZ46" s="3"/>
       <c r="BA46" s="3"/>
@@ -6131,8 +6336,10 @@
       <c r="BZ46" s="3"/>
       <c r="CA46" s="3"/>
       <c r="CB46" s="3"/>
-    </row>
-    <row r="47" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC46" s="3"/>
+      <c r="CD46" s="3"/>
+    </row>
+    <row r="47" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B47" s="2" t="s">
         <v>66</v>
       </c>
@@ -6162,34 +6369,37 @@
         <f t="shared" si="26"/>
         <v>4.8924898722343402E-2</v>
       </c>
-      <c r="K47" s="4"/>
-      <c r="L47" s="4"/>
-      <c r="M47" s="27" t="e">
+      <c r="K47" s="27">
+        <f t="shared" si="26"/>
+        <v>0.1334203229489479</v>
+      </c>
+      <c r="L47" s="27"/>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N47" s="27" t="e">
+      <c r="P47" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O47" s="27">
+      <c r="Q47" s="27">
         <f t="shared" si="27"/>
         <v>5.5467704658800576E-2</v>
       </c>
-      <c r="P47" s="27">
+      <c r="R47" s="27">
         <f t="shared" si="27"/>
         <v>0.14451999539011173</v>
       </c>
-      <c r="Q47" s="27">
+      <c r="S47" s="27">
         <f t="shared" si="29"/>
         <v>0.2068271070385661</v>
       </c>
-      <c r="R47" s="27">
+      <c r="T47" s="27">
         <f t="shared" si="29"/>
         <v>7.3258239465999075E-2</v>
       </c>
-      <c r="S47" s="4"/>
-      <c r="T47" s="4"/>
       <c r="U47" s="4"/>
       <c r="V47" s="4"/>
       <c r="W47" s="4"/>
@@ -6218,8 +6428,8 @@
       <c r="AT47" s="4"/>
       <c r="AU47" s="4"/>
       <c r="AV47" s="4"/>
-      <c r="AW47" s="3"/>
-      <c r="AX47" s="3"/>
+      <c r="AW47" s="4"/>
+      <c r="AX47" s="4"/>
       <c r="AY47" s="3"/>
       <c r="AZ47" s="3"/>
       <c r="BA47" s="3"/>
@@ -6250,8 +6460,10 @@
       <c r="BZ47" s="3"/>
       <c r="CA47" s="3"/>
       <c r="CB47" s="3"/>
-    </row>
-    <row r="48" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC47" s="3"/>
+      <c r="CD47" s="3"/>
+    </row>
+    <row r="48" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B48" s="2" t="s">
         <v>67</v>
       </c>
@@ -6281,34 +6493,37 @@
         <f t="shared" si="26"/>
         <v>3.1286210892236488E-2</v>
       </c>
-      <c r="K48" s="4"/>
-      <c r="L48" s="4"/>
-      <c r="M48" s="27" t="e">
+      <c r="K48" s="27">
+        <f t="shared" si="26"/>
+        <v>2.0312944523470837</v>
+      </c>
+      <c r="L48" s="27"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N48" s="27" t="e">
+      <c r="P48" s="27" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O48" s="27">
+      <c r="Q48" s="27">
         <f t="shared" si="27"/>
         <v>-0.39767859610335776</v>
       </c>
-      <c r="P48" s="27">
+      <c r="R48" s="27">
         <f t="shared" si="27"/>
         <v>-0.22688690066529016</v>
       </c>
-      <c r="Q48" s="27">
+      <c r="S48" s="27">
         <f t="shared" si="29"/>
         <v>-2.1068249258160199E-2</v>
       </c>
-      <c r="R48" s="27">
+      <c r="T48" s="27">
         <f t="shared" si="29"/>
         <v>-3.4252803879963656E-2</v>
       </c>
-      <c r="S48" s="4"/>
-      <c r="T48" s="4"/>
       <c r="U48" s="4"/>
       <c r="V48" s="4"/>
       <c r="W48" s="4"/>
@@ -6337,8 +6552,8 @@
       <c r="AT48" s="4"/>
       <c r="AU48" s="4"/>
       <c r="AV48" s="4"/>
-      <c r="AW48" s="3"/>
-      <c r="AX48" s="3"/>
+      <c r="AW48" s="4"/>
+      <c r="AX48" s="4"/>
       <c r="AY48" s="3"/>
       <c r="AZ48" s="3"/>
       <c r="BA48" s="3"/>
@@ -6369,8 +6584,10 @@
       <c r="BZ48" s="3"/>
       <c r="CA48" s="3"/>
       <c r="CB48" s="3"/>
-    </row>
-    <row r="49" spans="2:80" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="CC48" s="3"/>
+      <c r="CD48" s="3"/>
+    </row>
+    <row r="49" spans="2:82" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="1" t="s">
         <v>68</v>
       </c>
@@ -6400,34 +6617,37 @@
         <f t="shared" si="26"/>
         <v>0.12358793238251864</v>
       </c>
-      <c r="K49" s="25"/>
-      <c r="L49" s="25"/>
-      <c r="M49" s="28" t="e">
+      <c r="K49" s="28">
+        <f t="shared" si="26"/>
+        <v>0.12876193441261941</v>
+      </c>
+      <c r="L49" s="28"/>
+      <c r="M49" s="25"/>
+      <c r="N49" s="25"/>
+      <c r="O49" s="28" t="e">
         <f t="shared" si="27"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="N49" s="28">
+      <c r="P49" s="28">
         <f t="shared" si="27"/>
         <v>0.38905158819553964</v>
       </c>
-      <c r="O49" s="28">
+      <c r="Q49" s="28">
         <f t="shared" si="27"/>
         <v>8.7637852740836797E-2</v>
       </c>
-      <c r="P49" s="28">
+      <c r="R49" s="28">
         <f t="shared" si="27"/>
         <v>0.16225233453244114</v>
       </c>
-      <c r="Q49" s="28">
+      <c r="S49" s="28">
         <f t="shared" si="29"/>
         <v>0.13583295913785354</v>
       </c>
-      <c r="R49" s="28">
+      <c r="T49" s="28">
         <f t="shared" si="29"/>
         <v>0.13262078897579976</v>
       </c>
-      <c r="S49" s="25"/>
-      <c r="T49" s="25"/>
       <c r="U49" s="25"/>
       <c r="V49" s="25"/>
       <c r="W49" s="25"/>
@@ -6456,8 +6676,8 @@
       <c r="AT49" s="25"/>
       <c r="AU49" s="25"/>
       <c r="AV49" s="25"/>
-      <c r="AW49" s="24"/>
-      <c r="AX49" s="24"/>
+      <c r="AW49" s="25"/>
+      <c r="AX49" s="25"/>
       <c r="AY49" s="24"/>
       <c r="AZ49" s="24"/>
       <c r="BA49" s="24"/>
@@ -6488,8 +6708,10 @@
       <c r="BZ49" s="24"/>
       <c r="CA49" s="24"/>
       <c r="CB49" s="24"/>
-    </row>
-    <row r="50" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC49" s="24"/>
+      <c r="CD49" s="24"/>
+    </row>
+    <row r="50" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B50" s="2" t="s">
         <v>69</v>
       </c>
@@ -6522,37 +6744,40 @@
         <v>0.63369136571191365</v>
       </c>
       <c r="J50" s="27">
-        <f t="shared" ref="J50" si="32">+J22/J20</f>
+        <f t="shared" ref="J50:K50" si="32">+J22/J20</f>
         <v>0.6072945410917816</v>
       </c>
-      <c r="K50" s="4"/>
-      <c r="L50" s="4"/>
-      <c r="M50" s="27">
-        <f t="shared" ref="M50:P50" si="33">+M22/M20</f>
+      <c r="K50" s="27">
+        <f t="shared" si="32"/>
+        <v>0.6387937573264072</v>
+      </c>
+      <c r="L50" s="27"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="27">
+        <f t="shared" ref="O50:R50" si="33">+O22/O20</f>
         <v>1</v>
       </c>
-      <c r="N50" s="27">
+      <c r="P50" s="27">
         <f t="shared" si="33"/>
         <v>0.61636393123580924</v>
       </c>
-      <c r="O50" s="27">
+      <c r="Q50" s="27">
         <f t="shared" si="33"/>
         <v>0.6023746062515144</v>
       </c>
-      <c r="P50" s="27">
+      <c r="R50" s="27">
         <f t="shared" si="33"/>
         <v>0.62589005067675929</v>
       </c>
-      <c r="Q50" s="27">
-        <f t="shared" ref="Q50:R50" si="34">+Q22/Q20</f>
+      <c r="S50" s="27">
+        <f t="shared" ref="S50:T50" si="34">+S22/S20</f>
         <v>0.62169259876316607</v>
       </c>
-      <c r="R50" s="27">
+      <c r="T50" s="27">
         <f t="shared" si="34"/>
         <v>0.61997781074309077</v>
       </c>
-      <c r="S50" s="4"/>
-      <c r="T50" s="4"/>
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
       <c r="W50" s="4"/>
@@ -6581,8 +6806,8 @@
       <c r="AT50" s="4"/>
       <c r="AU50" s="4"/>
       <c r="AV50" s="4"/>
-      <c r="AW50" s="3"/>
-      <c r="AX50" s="3"/>
+      <c r="AW50" s="4"/>
+      <c r="AX50" s="4"/>
       <c r="AY50" s="3"/>
       <c r="AZ50" s="3"/>
       <c r="BA50" s="3"/>
@@ -6613,8 +6838,10 @@
       <c r="BZ50" s="3"/>
       <c r="CA50" s="3"/>
       <c r="CB50" s="3"/>
-    </row>
-    <row r="51" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC50" s="3"/>
+      <c r="CD50" s="3"/>
+    </row>
+    <row r="51" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B51" s="2" t="s">
         <v>70</v>
       </c>
@@ -6647,37 +6874,40 @@
         <v>0.26284246575342468</v>
       </c>
       <c r="J51" s="27">
-        <f t="shared" ref="J51" si="37">+J26/J20</f>
+        <f t="shared" ref="J51:K51" si="37">+J26/J20</f>
         <v>0.21499700059988003</v>
       </c>
-      <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="27">
-        <f t="shared" ref="M51:P51" si="38">+M26/M20</f>
+      <c r="K51" s="27">
+        <f t="shared" si="37"/>
+        <v>0.27030133082032776</v>
+      </c>
+      <c r="L51" s="27"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="27">
+        <f t="shared" ref="O51:R51" si="38">+O26/O20</f>
         <v>1</v>
       </c>
-      <c r="N51" s="27">
+      <c r="P51" s="27">
         <f t="shared" si="38"/>
         <v>0.22277408368472268</v>
       </c>
-      <c r="O51" s="27">
+      <c r="Q51" s="27">
         <f t="shared" si="38"/>
         <v>0.2093157629867104</v>
       </c>
-      <c r="P51" s="27">
+      <c r="R51" s="27">
         <f t="shared" si="38"/>
         <v>0.24643979729296298</v>
       </c>
-      <c r="Q51" s="27">
-        <f t="shared" ref="Q51:R51" si="39">+Q26/Q20</f>
+      <c r="S51" s="27">
+        <f t="shared" ref="S51:T51" si="39">+S26/S20</f>
         <v>0.23430661056674101</v>
       </c>
-      <c r="R51" s="27">
+      <c r="T51" s="27">
         <f t="shared" si="39"/>
         <v>0.2379860132886224</v>
       </c>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
       <c r="W51" s="4"/>
@@ -6706,8 +6936,8 @@
       <c r="AT51" s="4"/>
       <c r="AU51" s="4"/>
       <c r="AV51" s="4"/>
-      <c r="AW51" s="3"/>
-      <c r="AX51" s="3"/>
+      <c r="AW51" s="4"/>
+      <c r="AX51" s="4"/>
       <c r="AY51" s="3"/>
       <c r="AZ51" s="3"/>
       <c r="BA51" s="3"/>
@@ -6738,8 +6968,10 @@
       <c r="BZ51" s="3"/>
       <c r="CA51" s="3"/>
       <c r="CB51" s="3"/>
-    </row>
-    <row r="52" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC51" s="3"/>
+      <c r="CD51" s="3"/>
+    </row>
+    <row r="52" spans="2:82" x14ac:dyDescent="0.2">
       <c r="B52" s="2" t="s">
         <v>71</v>
       </c>
@@ -6772,37 +7004,40 @@
         <v>0.27327300421109219</v>
       </c>
       <c r="J52" s="27">
-        <f t="shared" ref="J52" si="42">+J31/J30</f>
+        <f t="shared" ref="J52:K52" si="42">+J31/J30</f>
         <v>0.26582401555663587</v>
       </c>
-      <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="27">
-        <f t="shared" ref="M52:P52" si="43">+M31/M30</f>
+      <c r="K52" s="27">
+        <f t="shared" si="42"/>
+        <v>0.24820985954282568</v>
+      </c>
+      <c r="L52" s="27"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="27">
+        <f t="shared" ref="O52:R52" si="43">+O31/O30</f>
         <v>0</v>
       </c>
-      <c r="N52" s="27">
+      <c r="P52" s="27">
         <f t="shared" si="43"/>
         <v>0.26877224199288258</v>
       </c>
-      <c r="O52" s="27">
+      <c r="Q52" s="27">
         <f t="shared" si="43"/>
         <v>0.27388815499779834</v>
       </c>
-      <c r="P52" s="27">
+      <c r="R52" s="27">
         <f t="shared" si="43"/>
         <v>0.27896419437340153</v>
       </c>
-      <c r="Q52" s="27">
-        <f t="shared" ref="Q52:R52" si="44">+Q31/Q30</f>
+      <c r="S52" s="27">
+        <f t="shared" ref="S52:T52" si="44">+S31/S30</f>
         <v>0.22367940047523305</v>
       </c>
-      <c r="R52" s="27">
+      <c r="T52" s="27">
         <f t="shared" si="44"/>
         <v>0.26970064347663902</v>
       </c>
-      <c r="S52" s="4"/>
-      <c r="T52" s="4"/>
       <c r="U52" s="4"/>
       <c r="V52" s="4"/>
       <c r="W52" s="4"/>
@@ -6831,8 +7066,8 @@
       <c r="AT52" s="4"/>
       <c r="AU52" s="4"/>
       <c r="AV52" s="4"/>
-      <c r="AW52" s="3"/>
-      <c r="AX52" s="3"/>
+      <c r="AW52" s="4"/>
+      <c r="AX52" s="4"/>
       <c r="AY52" s="3"/>
       <c r="AZ52" s="3"/>
       <c r="BA52" s="3"/>
@@ -6863,8 +7098,10 @@
       <c r="BZ52" s="3"/>
       <c r="CA52" s="3"/>
       <c r="CB52" s="3"/>
-    </row>
-    <row r="53" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC52" s="3"/>
+      <c r="CD52" s="3"/>
+    </row>
+    <row r="53" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="4"/>
@@ -6911,8 +7148,8 @@
       <c r="AT53" s="4"/>
       <c r="AU53" s="4"/>
       <c r="AV53" s="4"/>
-      <c r="AW53" s="3"/>
-      <c r="AX53" s="3"/>
+      <c r="AW53" s="4"/>
+      <c r="AX53" s="4"/>
       <c r="AY53" s="3"/>
       <c r="AZ53" s="3"/>
       <c r="BA53" s="3"/>
@@ -6943,8 +7180,10 @@
       <c r="BZ53" s="3"/>
       <c r="CA53" s="3"/>
       <c r="CB53" s="3"/>
-    </row>
-    <row r="54" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC53" s="3"/>
+      <c r="CD53" s="3"/>
+    </row>
+    <row r="54" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="4"/>
@@ -6991,8 +7230,8 @@
       <c r="AT54" s="4"/>
       <c r="AU54" s="4"/>
       <c r="AV54" s="4"/>
-      <c r="AW54" s="3"/>
-      <c r="AX54" s="3"/>
+      <c r="AW54" s="4"/>
+      <c r="AX54" s="4"/>
       <c r="AY54" s="3"/>
       <c r="AZ54" s="3"/>
       <c r="BA54" s="3"/>
@@ -7023,8 +7262,10 @@
       <c r="BZ54" s="3"/>
       <c r="CA54" s="3"/>
       <c r="CB54" s="3"/>
-    </row>
-    <row r="55" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC54" s="3"/>
+      <c r="CD54" s="3"/>
+    </row>
+    <row r="55" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="4"/>
@@ -7071,8 +7312,8 @@
       <c r="AT55" s="4"/>
       <c r="AU55" s="4"/>
       <c r="AV55" s="4"/>
-      <c r="AW55" s="3"/>
-      <c r="AX55" s="3"/>
+      <c r="AW55" s="4"/>
+      <c r="AX55" s="4"/>
       <c r="AY55" s="3"/>
       <c r="AZ55" s="3"/>
       <c r="BA55" s="3"/>
@@ -7103,8 +7344,10 @@
       <c r="BZ55" s="3"/>
       <c r="CA55" s="3"/>
       <c r="CB55" s="3"/>
-    </row>
-    <row r="56" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC55" s="3"/>
+      <c r="CD55" s="3"/>
+    </row>
+    <row r="56" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="4"/>
@@ -7151,8 +7394,8 @@
       <c r="AT56" s="4"/>
       <c r="AU56" s="4"/>
       <c r="AV56" s="4"/>
-      <c r="AW56" s="3"/>
-      <c r="AX56" s="3"/>
+      <c r="AW56" s="4"/>
+      <c r="AX56" s="4"/>
       <c r="AY56" s="3"/>
       <c r="AZ56" s="3"/>
       <c r="BA56" s="3"/>
@@ -7183,8 +7426,10 @@
       <c r="BZ56" s="3"/>
       <c r="CA56" s="3"/>
       <c r="CB56" s="3"/>
-    </row>
-    <row r="57" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC56" s="3"/>
+      <c r="CD56" s="3"/>
+    </row>
+    <row r="57" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="4"/>
@@ -7231,8 +7476,8 @@
       <c r="AT57" s="4"/>
       <c r="AU57" s="4"/>
       <c r="AV57" s="4"/>
-      <c r="AW57" s="3"/>
-      <c r="AX57" s="3"/>
+      <c r="AW57" s="4"/>
+      <c r="AX57" s="4"/>
       <c r="AY57" s="3"/>
       <c r="AZ57" s="3"/>
       <c r="BA57" s="3"/>
@@ -7263,8 +7508,10 @@
       <c r="BZ57" s="3"/>
       <c r="CA57" s="3"/>
       <c r="CB57" s="3"/>
-    </row>
-    <row r="58" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC57" s="3"/>
+      <c r="CD57" s="3"/>
+    </row>
+    <row r="58" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="4"/>
@@ -7311,8 +7558,8 @@
       <c r="AT58" s="4"/>
       <c r="AU58" s="4"/>
       <c r="AV58" s="4"/>
-      <c r="AW58" s="3"/>
-      <c r="AX58" s="3"/>
+      <c r="AW58" s="4"/>
+      <c r="AX58" s="4"/>
       <c r="AY58" s="3"/>
       <c r="AZ58" s="3"/>
       <c r="BA58" s="3"/>
@@ -7343,8 +7590,10 @@
       <c r="BZ58" s="3"/>
       <c r="CA58" s="3"/>
       <c r="CB58" s="3"/>
-    </row>
-    <row r="59" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC58" s="3"/>
+      <c r="CD58" s="3"/>
+    </row>
+    <row r="59" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="4"/>
@@ -7391,8 +7640,8 @@
       <c r="AT59" s="4"/>
       <c r="AU59" s="4"/>
       <c r="AV59" s="4"/>
-      <c r="AW59" s="3"/>
-      <c r="AX59" s="3"/>
+      <c r="AW59" s="4"/>
+      <c r="AX59" s="4"/>
       <c r="AY59" s="3"/>
       <c r="AZ59" s="3"/>
       <c r="BA59" s="3"/>
@@ -7423,8 +7672,10 @@
       <c r="BZ59" s="3"/>
       <c r="CA59" s="3"/>
       <c r="CB59" s="3"/>
-    </row>
-    <row r="60" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC59" s="3"/>
+      <c r="CD59" s="3"/>
+    </row>
+    <row r="60" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="4"/>
@@ -7471,8 +7722,8 @@
       <c r="AT60" s="4"/>
       <c r="AU60" s="4"/>
       <c r="AV60" s="4"/>
-      <c r="AW60" s="3"/>
-      <c r="AX60" s="3"/>
+      <c r="AW60" s="4"/>
+      <c r="AX60" s="4"/>
       <c r="AY60" s="3"/>
       <c r="AZ60" s="3"/>
       <c r="BA60" s="3"/>
@@ -7503,8 +7754,10 @@
       <c r="BZ60" s="3"/>
       <c r="CA60" s="3"/>
       <c r="CB60" s="3"/>
-    </row>
-    <row r="61" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC60" s="3"/>
+      <c r="CD60" s="3"/>
+    </row>
+    <row r="61" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="4"/>
@@ -7551,8 +7804,8 @@
       <c r="AT61" s="4"/>
       <c r="AU61" s="4"/>
       <c r="AV61" s="4"/>
-      <c r="AW61" s="3"/>
-      <c r="AX61" s="3"/>
+      <c r="AW61" s="4"/>
+      <c r="AX61" s="4"/>
       <c r="AY61" s="3"/>
       <c r="AZ61" s="3"/>
       <c r="BA61" s="3"/>
@@ -7583,8 +7836,10 @@
       <c r="BZ61" s="3"/>
       <c r="CA61" s="3"/>
       <c r="CB61" s="3"/>
-    </row>
-    <row r="62" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC61" s="3"/>
+      <c r="CD61" s="3"/>
+    </row>
+    <row r="62" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="4"/>
@@ -7631,8 +7886,8 @@
       <c r="AT62" s="4"/>
       <c r="AU62" s="4"/>
       <c r="AV62" s="4"/>
-      <c r="AW62" s="3"/>
-      <c r="AX62" s="3"/>
+      <c r="AW62" s="4"/>
+      <c r="AX62" s="4"/>
       <c r="AY62" s="3"/>
       <c r="AZ62" s="3"/>
       <c r="BA62" s="3"/>
@@ -7663,8 +7918,10 @@
       <c r="BZ62" s="3"/>
       <c r="CA62" s="3"/>
       <c r="CB62" s="3"/>
-    </row>
-    <row r="63" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC62" s="3"/>
+      <c r="CD62" s="3"/>
+    </row>
+    <row r="63" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="4"/>
@@ -7711,8 +7968,8 @@
       <c r="AT63" s="4"/>
       <c r="AU63" s="4"/>
       <c r="AV63" s="4"/>
-      <c r="AW63" s="3"/>
-      <c r="AX63" s="3"/>
+      <c r="AW63" s="4"/>
+      <c r="AX63" s="4"/>
       <c r="AY63" s="3"/>
       <c r="AZ63" s="3"/>
       <c r="BA63" s="3"/>
@@ -7743,8 +8000,10 @@
       <c r="BZ63" s="3"/>
       <c r="CA63" s="3"/>
       <c r="CB63" s="3"/>
-    </row>
-    <row r="64" spans="2:80" x14ac:dyDescent="0.2">
+      <c r="CC63" s="3"/>
+      <c r="CD63" s="3"/>
+    </row>
+    <row r="64" spans="2:82" x14ac:dyDescent="0.2">
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="4"/>
@@ -7791,8 +8050,8 @@
       <c r="AT64" s="4"/>
       <c r="AU64" s="4"/>
       <c r="AV64" s="4"/>
-      <c r="AW64" s="3"/>
-      <c r="AX64" s="3"/>
+      <c r="AW64" s="4"/>
+      <c r="AX64" s="4"/>
       <c r="AY64" s="3"/>
       <c r="AZ64" s="3"/>
       <c r="BA64" s="3"/>
@@ -7823,8 +8082,10 @@
       <c r="BZ64" s="3"/>
       <c r="CA64" s="3"/>
       <c r="CB64" s="3"/>
-    </row>
-    <row r="65" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC64" s="3"/>
+      <c r="CD64" s="3"/>
+    </row>
+    <row r="65" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="4"/>
@@ -7871,8 +8132,8 @@
       <c r="AT65" s="4"/>
       <c r="AU65" s="4"/>
       <c r="AV65" s="4"/>
-      <c r="AW65" s="3"/>
-      <c r="AX65" s="3"/>
+      <c r="AW65" s="4"/>
+      <c r="AX65" s="4"/>
       <c r="AY65" s="3"/>
       <c r="AZ65" s="3"/>
       <c r="BA65" s="3"/>
@@ -7903,8 +8164,10 @@
       <c r="BZ65" s="3"/>
       <c r="CA65" s="3"/>
       <c r="CB65" s="3"/>
-    </row>
-    <row r="66" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC65" s="3"/>
+      <c r="CD65" s="3"/>
+    </row>
+    <row r="66" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="4"/>
@@ -7951,8 +8214,8 @@
       <c r="AT66" s="4"/>
       <c r="AU66" s="4"/>
       <c r="AV66" s="4"/>
-      <c r="AW66" s="3"/>
-      <c r="AX66" s="3"/>
+      <c r="AW66" s="4"/>
+      <c r="AX66" s="4"/>
       <c r="AY66" s="3"/>
       <c r="AZ66" s="3"/>
       <c r="BA66" s="3"/>
@@ -7983,8 +8246,10 @@
       <c r="BZ66" s="3"/>
       <c r="CA66" s="3"/>
       <c r="CB66" s="3"/>
-    </row>
-    <row r="67" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC66" s="3"/>
+      <c r="CD66" s="3"/>
+    </row>
+    <row r="67" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="4"/>
@@ -8031,8 +8296,8 @@
       <c r="AT67" s="4"/>
       <c r="AU67" s="4"/>
       <c r="AV67" s="4"/>
-      <c r="AW67" s="3"/>
-      <c r="AX67" s="3"/>
+      <c r="AW67" s="4"/>
+      <c r="AX67" s="4"/>
       <c r="AY67" s="3"/>
       <c r="AZ67" s="3"/>
       <c r="BA67" s="3"/>
@@ -8063,8 +8328,10 @@
       <c r="BZ67" s="3"/>
       <c r="CA67" s="3"/>
       <c r="CB67" s="3"/>
-    </row>
-    <row r="68" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC67" s="3"/>
+      <c r="CD67" s="3"/>
+    </row>
+    <row r="68" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="4"/>
@@ -8111,8 +8378,8 @@
       <c r="AT68" s="4"/>
       <c r="AU68" s="4"/>
       <c r="AV68" s="4"/>
-      <c r="AW68" s="3"/>
-      <c r="AX68" s="3"/>
+      <c r="AW68" s="4"/>
+      <c r="AX68" s="4"/>
       <c r="AY68" s="3"/>
       <c r="AZ68" s="3"/>
       <c r="BA68" s="3"/>
@@ -8143,8 +8410,10 @@
       <c r="BZ68" s="3"/>
       <c r="CA68" s="3"/>
       <c r="CB68" s="3"/>
-    </row>
-    <row r="69" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC68" s="3"/>
+      <c r="CD68" s="3"/>
+    </row>
+    <row r="69" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="4"/>
@@ -8191,8 +8460,8 @@
       <c r="AT69" s="4"/>
       <c r="AU69" s="4"/>
       <c r="AV69" s="4"/>
-      <c r="AW69" s="3"/>
-      <c r="AX69" s="3"/>
+      <c r="AW69" s="4"/>
+      <c r="AX69" s="4"/>
       <c r="AY69" s="3"/>
       <c r="AZ69" s="3"/>
       <c r="BA69" s="3"/>
@@ -8223,8 +8492,10 @@
       <c r="BZ69" s="3"/>
       <c r="CA69" s="3"/>
       <c r="CB69" s="3"/>
-    </row>
-    <row r="70" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC69" s="3"/>
+      <c r="CD69" s="3"/>
+    </row>
+    <row r="70" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="4"/>
@@ -8271,8 +8542,8 @@
       <c r="AT70" s="4"/>
       <c r="AU70" s="4"/>
       <c r="AV70" s="4"/>
-      <c r="AW70" s="3"/>
-      <c r="AX70" s="3"/>
+      <c r="AW70" s="4"/>
+      <c r="AX70" s="4"/>
       <c r="AY70" s="3"/>
       <c r="AZ70" s="3"/>
       <c r="BA70" s="3"/>
@@ -8303,8 +8574,10 @@
       <c r="BZ70" s="3"/>
       <c r="CA70" s="3"/>
       <c r="CB70" s="3"/>
-    </row>
-    <row r="71" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC70" s="3"/>
+      <c r="CD70" s="3"/>
+    </row>
+    <row r="71" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="4"/>
@@ -8351,8 +8624,8 @@
       <c r="AT71" s="4"/>
       <c r="AU71" s="4"/>
       <c r="AV71" s="4"/>
-      <c r="AW71" s="3"/>
-      <c r="AX71" s="3"/>
+      <c r="AW71" s="4"/>
+      <c r="AX71" s="4"/>
       <c r="AY71" s="3"/>
       <c r="AZ71" s="3"/>
       <c r="BA71" s="3"/>
@@ -8383,8 +8656,10 @@
       <c r="BZ71" s="3"/>
       <c r="CA71" s="3"/>
       <c r="CB71" s="3"/>
-    </row>
-    <row r="72" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC71" s="3"/>
+      <c r="CD71" s="3"/>
+    </row>
+    <row r="72" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="4"/>
@@ -8431,8 +8706,8 @@
       <c r="AT72" s="4"/>
       <c r="AU72" s="4"/>
       <c r="AV72" s="4"/>
-      <c r="AW72" s="3"/>
-      <c r="AX72" s="3"/>
+      <c r="AW72" s="4"/>
+      <c r="AX72" s="4"/>
       <c r="AY72" s="3"/>
       <c r="AZ72" s="3"/>
       <c r="BA72" s="3"/>
@@ -8463,8 +8738,10 @@
       <c r="BZ72" s="3"/>
       <c r="CA72" s="3"/>
       <c r="CB72" s="3"/>
-    </row>
-    <row r="73" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC72" s="3"/>
+      <c r="CD72" s="3"/>
+    </row>
+    <row r="73" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="4"/>
@@ -8511,8 +8788,8 @@
       <c r="AT73" s="4"/>
       <c r="AU73" s="4"/>
       <c r="AV73" s="4"/>
-      <c r="AW73" s="3"/>
-      <c r="AX73" s="3"/>
+      <c r="AW73" s="4"/>
+      <c r="AX73" s="4"/>
       <c r="AY73" s="3"/>
       <c r="AZ73" s="3"/>
       <c r="BA73" s="3"/>
@@ -8543,8 +8820,10 @@
       <c r="BZ73" s="3"/>
       <c r="CA73" s="3"/>
       <c r="CB73" s="3"/>
-    </row>
-    <row r="74" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC73" s="3"/>
+      <c r="CD73" s="3"/>
+    </row>
+    <row r="74" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="4"/>
@@ -8591,8 +8870,8 @@
       <c r="AT74" s="4"/>
       <c r="AU74" s="4"/>
       <c r="AV74" s="4"/>
-      <c r="AW74" s="3"/>
-      <c r="AX74" s="3"/>
+      <c r="AW74" s="4"/>
+      <c r="AX74" s="4"/>
       <c r="AY74" s="3"/>
       <c r="AZ74" s="3"/>
       <c r="BA74" s="3"/>
@@ -8623,8 +8902,10 @@
       <c r="BZ74" s="3"/>
       <c r="CA74" s="3"/>
       <c r="CB74" s="3"/>
-    </row>
-    <row r="75" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC74" s="3"/>
+      <c r="CD74" s="3"/>
+    </row>
+    <row r="75" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="4"/>
@@ -8671,8 +8952,8 @@
       <c r="AT75" s="4"/>
       <c r="AU75" s="4"/>
       <c r="AV75" s="4"/>
-      <c r="AW75" s="3"/>
-      <c r="AX75" s="3"/>
+      <c r="AW75" s="4"/>
+      <c r="AX75" s="4"/>
       <c r="AY75" s="3"/>
       <c r="AZ75" s="3"/>
       <c r="BA75" s="3"/>
@@ -8703,8 +8984,10 @@
       <c r="BZ75" s="3"/>
       <c r="CA75" s="3"/>
       <c r="CB75" s="3"/>
-    </row>
-    <row r="76" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC75" s="3"/>
+      <c r="CD75" s="3"/>
+    </row>
+    <row r="76" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="4"/>
@@ -8751,8 +9034,8 @@
       <c r="AT76" s="4"/>
       <c r="AU76" s="4"/>
       <c r="AV76" s="4"/>
-      <c r="AW76" s="3"/>
-      <c r="AX76" s="3"/>
+      <c r="AW76" s="4"/>
+      <c r="AX76" s="4"/>
       <c r="AY76" s="3"/>
       <c r="AZ76" s="3"/>
       <c r="BA76" s="3"/>
@@ -8783,8 +9066,10 @@
       <c r="BZ76" s="3"/>
       <c r="CA76" s="3"/>
       <c r="CB76" s="3"/>
-    </row>
-    <row r="77" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC76" s="3"/>
+      <c r="CD76" s="3"/>
+    </row>
+    <row r="77" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="4"/>
@@ -8831,8 +9116,8 @@
       <c r="AT77" s="4"/>
       <c r="AU77" s="4"/>
       <c r="AV77" s="4"/>
-      <c r="AW77" s="3"/>
-      <c r="AX77" s="3"/>
+      <c r="AW77" s="4"/>
+      <c r="AX77" s="4"/>
       <c r="AY77" s="3"/>
       <c r="AZ77" s="3"/>
       <c r="BA77" s="3"/>
@@ -8863,8 +9148,10 @@
       <c r="BZ77" s="3"/>
       <c r="CA77" s="3"/>
       <c r="CB77" s="3"/>
-    </row>
-    <row r="78" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC77" s="3"/>
+      <c r="CD77" s="3"/>
+    </row>
+    <row r="78" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="4"/>
@@ -8911,8 +9198,8 @@
       <c r="AT78" s="4"/>
       <c r="AU78" s="4"/>
       <c r="AV78" s="4"/>
-      <c r="AW78" s="3"/>
-      <c r="AX78" s="3"/>
+      <c r="AW78" s="4"/>
+      <c r="AX78" s="4"/>
       <c r="AY78" s="3"/>
       <c r="AZ78" s="3"/>
       <c r="BA78" s="3"/>
@@ -8943,8 +9230,10 @@
       <c r="BZ78" s="3"/>
       <c r="CA78" s="3"/>
       <c r="CB78" s="3"/>
-    </row>
-    <row r="79" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC78" s="3"/>
+      <c r="CD78" s="3"/>
+    </row>
+    <row r="79" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="4"/>
@@ -8991,8 +9280,8 @@
       <c r="AT79" s="4"/>
       <c r="AU79" s="4"/>
       <c r="AV79" s="4"/>
-      <c r="AW79" s="3"/>
-      <c r="AX79" s="3"/>
+      <c r="AW79" s="4"/>
+      <c r="AX79" s="4"/>
       <c r="AY79" s="3"/>
       <c r="AZ79" s="3"/>
       <c r="BA79" s="3"/>
@@ -9023,8 +9312,10 @@
       <c r="BZ79" s="3"/>
       <c r="CA79" s="3"/>
       <c r="CB79" s="3"/>
-    </row>
-    <row r="80" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC79" s="3"/>
+      <c r="CD79" s="3"/>
+    </row>
+    <row r="80" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="4"/>
@@ -9071,8 +9362,8 @@
       <c r="AT80" s="4"/>
       <c r="AU80" s="4"/>
       <c r="AV80" s="4"/>
-      <c r="AW80" s="3"/>
-      <c r="AX80" s="3"/>
+      <c r="AW80" s="4"/>
+      <c r="AX80" s="4"/>
       <c r="AY80" s="3"/>
       <c r="AZ80" s="3"/>
       <c r="BA80" s="3"/>
@@ -9103,8 +9394,10 @@
       <c r="BZ80" s="3"/>
       <c r="CA80" s="3"/>
       <c r="CB80" s="3"/>
-    </row>
-    <row r="81" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC80" s="3"/>
+      <c r="CD80" s="3"/>
+    </row>
+    <row r="81" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="4"/>
@@ -9151,8 +9444,8 @@
       <c r="AT81" s="4"/>
       <c r="AU81" s="4"/>
       <c r="AV81" s="4"/>
-      <c r="AW81" s="3"/>
-      <c r="AX81" s="3"/>
+      <c r="AW81" s="4"/>
+      <c r="AX81" s="4"/>
       <c r="AY81" s="3"/>
       <c r="AZ81" s="3"/>
       <c r="BA81" s="3"/>
@@ -9183,8 +9476,10 @@
       <c r="BZ81" s="3"/>
       <c r="CA81" s="3"/>
       <c r="CB81" s="3"/>
-    </row>
-    <row r="82" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC81" s="3"/>
+      <c r="CD81" s="3"/>
+    </row>
+    <row r="82" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="4"/>
@@ -9231,8 +9526,8 @@
       <c r="AT82" s="4"/>
       <c r="AU82" s="4"/>
       <c r="AV82" s="4"/>
-      <c r="AW82" s="3"/>
-      <c r="AX82" s="3"/>
+      <c r="AW82" s="4"/>
+      <c r="AX82" s="4"/>
       <c r="AY82" s="3"/>
       <c r="AZ82" s="3"/>
       <c r="BA82" s="3"/>
@@ -9263,8 +9558,10 @@
       <c r="BZ82" s="3"/>
       <c r="CA82" s="3"/>
       <c r="CB82" s="3"/>
-    </row>
-    <row r="83" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC82" s="3"/>
+      <c r="CD82" s="3"/>
+    </row>
+    <row r="83" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="4"/>
@@ -9311,8 +9608,8 @@
       <c r="AT83" s="4"/>
       <c r="AU83" s="4"/>
       <c r="AV83" s="4"/>
-      <c r="AW83" s="3"/>
-      <c r="AX83" s="3"/>
+      <c r="AW83" s="4"/>
+      <c r="AX83" s="4"/>
       <c r="AY83" s="3"/>
       <c r="AZ83" s="3"/>
       <c r="BA83" s="3"/>
@@ -9343,8 +9640,10 @@
       <c r="BZ83" s="3"/>
       <c r="CA83" s="3"/>
       <c r="CB83" s="3"/>
-    </row>
-    <row r="84" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC83" s="3"/>
+      <c r="CD83" s="3"/>
+    </row>
+    <row r="84" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="4"/>
@@ -9391,8 +9690,8 @@
       <c r="AT84" s="4"/>
       <c r="AU84" s="4"/>
       <c r="AV84" s="4"/>
-      <c r="AW84" s="3"/>
-      <c r="AX84" s="3"/>
+      <c r="AW84" s="4"/>
+      <c r="AX84" s="4"/>
       <c r="AY84" s="3"/>
       <c r="AZ84" s="3"/>
       <c r="BA84" s="3"/>
@@ -9423,8 +9722,10 @@
       <c r="BZ84" s="3"/>
       <c r="CA84" s="3"/>
       <c r="CB84" s="3"/>
-    </row>
-    <row r="85" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC84" s="3"/>
+      <c r="CD84" s="3"/>
+    </row>
+    <row r="85" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="4"/>
@@ -9471,8 +9772,8 @@
       <c r="AT85" s="4"/>
       <c r="AU85" s="4"/>
       <c r="AV85" s="4"/>
-      <c r="AW85" s="3"/>
-      <c r="AX85" s="3"/>
+      <c r="AW85" s="4"/>
+      <c r="AX85" s="4"/>
       <c r="AY85" s="3"/>
       <c r="AZ85" s="3"/>
       <c r="BA85" s="3"/>
@@ -9503,8 +9804,10 @@
       <c r="BZ85" s="3"/>
       <c r="CA85" s="3"/>
       <c r="CB85" s="3"/>
-    </row>
-    <row r="86" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC85" s="3"/>
+      <c r="CD85" s="3"/>
+    </row>
+    <row r="86" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="4"/>
@@ -9551,8 +9854,8 @@
       <c r="AT86" s="4"/>
       <c r="AU86" s="4"/>
       <c r="AV86" s="4"/>
-      <c r="AW86" s="3"/>
-      <c r="AX86" s="3"/>
+      <c r="AW86" s="4"/>
+      <c r="AX86" s="4"/>
       <c r="AY86" s="3"/>
       <c r="AZ86" s="3"/>
       <c r="BA86" s="3"/>
@@ -9583,8 +9886,10 @@
       <c r="BZ86" s="3"/>
       <c r="CA86" s="3"/>
       <c r="CB86" s="3"/>
-    </row>
-    <row r="87" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC86" s="3"/>
+      <c r="CD86" s="3"/>
+    </row>
+    <row r="87" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="4"/>
@@ -9631,8 +9936,8 @@
       <c r="AT87" s="4"/>
       <c r="AU87" s="4"/>
       <c r="AV87" s="4"/>
-      <c r="AW87" s="3"/>
-      <c r="AX87" s="3"/>
+      <c r="AW87" s="4"/>
+      <c r="AX87" s="4"/>
       <c r="AY87" s="3"/>
       <c r="AZ87" s="3"/>
       <c r="BA87" s="3"/>
@@ -9663,8 +9968,10 @@
       <c r="BZ87" s="3"/>
       <c r="CA87" s="3"/>
       <c r="CB87" s="3"/>
-    </row>
-    <row r="88" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC87" s="3"/>
+      <c r="CD87" s="3"/>
+    </row>
+    <row r="88" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="4"/>
@@ -9711,8 +10018,8 @@
       <c r="AT88" s="4"/>
       <c r="AU88" s="4"/>
       <c r="AV88" s="4"/>
-      <c r="AW88" s="3"/>
-      <c r="AX88" s="3"/>
+      <c r="AW88" s="4"/>
+      <c r="AX88" s="4"/>
       <c r="AY88" s="3"/>
       <c r="AZ88" s="3"/>
       <c r="BA88" s="3"/>
@@ -9743,8 +10050,10 @@
       <c r="BZ88" s="3"/>
       <c r="CA88" s="3"/>
       <c r="CB88" s="3"/>
-    </row>
-    <row r="89" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC88" s="3"/>
+      <c r="CD88" s="3"/>
+    </row>
+    <row r="89" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="4"/>
@@ -9791,8 +10100,8 @@
       <c r="AT89" s="4"/>
       <c r="AU89" s="4"/>
       <c r="AV89" s="4"/>
-      <c r="AW89" s="3"/>
-      <c r="AX89" s="3"/>
+      <c r="AW89" s="4"/>
+      <c r="AX89" s="4"/>
       <c r="AY89" s="3"/>
       <c r="AZ89" s="3"/>
       <c r="BA89" s="3"/>
@@ -9823,8 +10132,10 @@
       <c r="BZ89" s="3"/>
       <c r="CA89" s="3"/>
       <c r="CB89" s="3"/>
-    </row>
-    <row r="90" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC89" s="3"/>
+      <c r="CD89" s="3"/>
+    </row>
+    <row r="90" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="4"/>
@@ -9871,8 +10182,8 @@
       <c r="AT90" s="4"/>
       <c r="AU90" s="4"/>
       <c r="AV90" s="4"/>
-      <c r="AW90" s="3"/>
-      <c r="AX90" s="3"/>
+      <c r="AW90" s="4"/>
+      <c r="AX90" s="4"/>
       <c r="AY90" s="3"/>
       <c r="AZ90" s="3"/>
       <c r="BA90" s="3"/>
@@ -9903,8 +10214,10 @@
       <c r="BZ90" s="3"/>
       <c r="CA90" s="3"/>
       <c r="CB90" s="3"/>
-    </row>
-    <row r="91" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC90" s="3"/>
+      <c r="CD90" s="3"/>
+    </row>
+    <row r="91" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="4"/>
@@ -9951,8 +10264,8 @@
       <c r="AT91" s="4"/>
       <c r="AU91" s="4"/>
       <c r="AV91" s="4"/>
-      <c r="AW91" s="3"/>
-      <c r="AX91" s="3"/>
+      <c r="AW91" s="4"/>
+      <c r="AX91" s="4"/>
       <c r="AY91" s="3"/>
       <c r="AZ91" s="3"/>
       <c r="BA91" s="3"/>
@@ -9983,8 +10296,10 @@
       <c r="BZ91" s="3"/>
       <c r="CA91" s="3"/>
       <c r="CB91" s="3"/>
-    </row>
-    <row r="92" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC91" s="3"/>
+      <c r="CD91" s="3"/>
+    </row>
+    <row r="92" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="4"/>
@@ -10031,8 +10346,8 @@
       <c r="AT92" s="4"/>
       <c r="AU92" s="4"/>
       <c r="AV92" s="4"/>
-      <c r="AW92" s="3"/>
-      <c r="AX92" s="3"/>
+      <c r="AW92" s="4"/>
+      <c r="AX92" s="4"/>
       <c r="AY92" s="3"/>
       <c r="AZ92" s="3"/>
       <c r="BA92" s="3"/>
@@ -10063,8 +10378,10 @@
       <c r="BZ92" s="3"/>
       <c r="CA92" s="3"/>
       <c r="CB92" s="3"/>
-    </row>
-    <row r="93" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC92" s="3"/>
+      <c r="CD92" s="3"/>
+    </row>
+    <row r="93" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="4"/>
@@ -10111,8 +10428,8 @@
       <c r="AT93" s="4"/>
       <c r="AU93" s="4"/>
       <c r="AV93" s="4"/>
-      <c r="AW93" s="3"/>
-      <c r="AX93" s="3"/>
+      <c r="AW93" s="4"/>
+      <c r="AX93" s="4"/>
       <c r="AY93" s="3"/>
       <c r="AZ93" s="3"/>
       <c r="BA93" s="3"/>
@@ -10143,8 +10460,10 @@
       <c r="BZ93" s="3"/>
       <c r="CA93" s="3"/>
       <c r="CB93" s="3"/>
-    </row>
-    <row r="94" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC93" s="3"/>
+      <c r="CD93" s="3"/>
+    </row>
+    <row r="94" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="4"/>
@@ -10191,8 +10510,8 @@
       <c r="AT94" s="4"/>
       <c r="AU94" s="4"/>
       <c r="AV94" s="4"/>
-      <c r="AW94" s="3"/>
-      <c r="AX94" s="3"/>
+      <c r="AW94" s="4"/>
+      <c r="AX94" s="4"/>
       <c r="AY94" s="3"/>
       <c r="AZ94" s="3"/>
       <c r="BA94" s="3"/>
@@ -10223,8 +10542,10 @@
       <c r="BZ94" s="3"/>
       <c r="CA94" s="3"/>
       <c r="CB94" s="3"/>
-    </row>
-    <row r="95" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC94" s="3"/>
+      <c r="CD94" s="3"/>
+    </row>
+    <row r="95" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="4"/>
@@ -10271,8 +10592,8 @@
       <c r="AT95" s="4"/>
       <c r="AU95" s="4"/>
       <c r="AV95" s="4"/>
-      <c r="AW95" s="3"/>
-      <c r="AX95" s="3"/>
+      <c r="AW95" s="4"/>
+      <c r="AX95" s="4"/>
       <c r="AY95" s="3"/>
       <c r="AZ95" s="3"/>
       <c r="BA95" s="3"/>
@@ -10303,8 +10624,10 @@
       <c r="BZ95" s="3"/>
       <c r="CA95" s="3"/>
       <c r="CB95" s="3"/>
-    </row>
-    <row r="96" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC95" s="3"/>
+      <c r="CD95" s="3"/>
+    </row>
+    <row r="96" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="4"/>
@@ -10351,8 +10674,8 @@
       <c r="AT96" s="4"/>
       <c r="AU96" s="4"/>
       <c r="AV96" s="4"/>
-      <c r="AW96" s="3"/>
-      <c r="AX96" s="3"/>
+      <c r="AW96" s="4"/>
+      <c r="AX96" s="4"/>
       <c r="AY96" s="3"/>
       <c r="AZ96" s="3"/>
       <c r="BA96" s="3"/>
@@ -10383,8 +10706,10 @@
       <c r="BZ96" s="3"/>
       <c r="CA96" s="3"/>
       <c r="CB96" s="3"/>
-    </row>
-    <row r="97" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC96" s="3"/>
+      <c r="CD96" s="3"/>
+    </row>
+    <row r="97" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="4"/>
@@ -10431,8 +10756,8 @@
       <c r="AT97" s="4"/>
       <c r="AU97" s="4"/>
       <c r="AV97" s="4"/>
-      <c r="AW97" s="3"/>
-      <c r="AX97" s="3"/>
+      <c r="AW97" s="4"/>
+      <c r="AX97" s="4"/>
       <c r="AY97" s="3"/>
       <c r="AZ97" s="3"/>
       <c r="BA97" s="3"/>
@@ -10463,8 +10788,10 @@
       <c r="BZ97" s="3"/>
       <c r="CA97" s="3"/>
       <c r="CB97" s="3"/>
-    </row>
-    <row r="98" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC97" s="3"/>
+      <c r="CD97" s="3"/>
+    </row>
+    <row r="98" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="4"/>
@@ -10511,8 +10838,8 @@
       <c r="AT98" s="4"/>
       <c r="AU98" s="4"/>
       <c r="AV98" s="4"/>
-      <c r="AW98" s="3"/>
-      <c r="AX98" s="3"/>
+      <c r="AW98" s="4"/>
+      <c r="AX98" s="4"/>
       <c r="AY98" s="3"/>
       <c r="AZ98" s="3"/>
       <c r="BA98" s="3"/>
@@ -10543,8 +10870,10 @@
       <c r="BZ98" s="3"/>
       <c r="CA98" s="3"/>
       <c r="CB98" s="3"/>
-    </row>
-    <row r="99" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC98" s="3"/>
+      <c r="CD98" s="3"/>
+    </row>
+    <row r="99" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="4"/>
@@ -10591,8 +10920,8 @@
       <c r="AT99" s="4"/>
       <c r="AU99" s="4"/>
       <c r="AV99" s="4"/>
-      <c r="AW99" s="3"/>
-      <c r="AX99" s="3"/>
+      <c r="AW99" s="4"/>
+      <c r="AX99" s="4"/>
       <c r="AY99" s="3"/>
       <c r="AZ99" s="3"/>
       <c r="BA99" s="3"/>
@@ -10623,8 +10952,10 @@
       <c r="BZ99" s="3"/>
       <c r="CA99" s="3"/>
       <c r="CB99" s="3"/>
-    </row>
-    <row r="100" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC99" s="3"/>
+      <c r="CD99" s="3"/>
+    </row>
+    <row r="100" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="4"/>
@@ -10671,8 +11002,8 @@
       <c r="AT100" s="4"/>
       <c r="AU100" s="4"/>
       <c r="AV100" s="4"/>
-      <c r="AW100" s="3"/>
-      <c r="AX100" s="3"/>
+      <c r="AW100" s="4"/>
+      <c r="AX100" s="4"/>
       <c r="AY100" s="3"/>
       <c r="AZ100" s="3"/>
       <c r="BA100" s="3"/>
@@ -10703,8 +11034,10 @@
       <c r="BZ100" s="3"/>
       <c r="CA100" s="3"/>
       <c r="CB100" s="3"/>
-    </row>
-    <row r="101" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC100" s="3"/>
+      <c r="CD100" s="3"/>
+    </row>
+    <row r="101" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="4"/>
@@ -10751,8 +11084,8 @@
       <c r="AT101" s="4"/>
       <c r="AU101" s="4"/>
       <c r="AV101" s="4"/>
-      <c r="AW101" s="3"/>
-      <c r="AX101" s="3"/>
+      <c r="AW101" s="4"/>
+      <c r="AX101" s="4"/>
       <c r="AY101" s="3"/>
       <c r="AZ101" s="3"/>
       <c r="BA101" s="3"/>
@@ -10783,8 +11116,10 @@
       <c r="BZ101" s="3"/>
       <c r="CA101" s="3"/>
       <c r="CB101" s="3"/>
-    </row>
-    <row r="102" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC101" s="3"/>
+      <c r="CD101" s="3"/>
+    </row>
+    <row r="102" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="4"/>
@@ -10831,8 +11166,8 @@
       <c r="AT102" s="4"/>
       <c r="AU102" s="4"/>
       <c r="AV102" s="4"/>
-      <c r="AW102" s="3"/>
-      <c r="AX102" s="3"/>
+      <c r="AW102" s="4"/>
+      <c r="AX102" s="4"/>
       <c r="AY102" s="3"/>
       <c r="AZ102" s="3"/>
       <c r="BA102" s="3"/>
@@ -10863,8 +11198,10 @@
       <c r="BZ102" s="3"/>
       <c r="CA102" s="3"/>
       <c r="CB102" s="3"/>
-    </row>
-    <row r="103" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC102" s="3"/>
+      <c r="CD102" s="3"/>
+    </row>
+    <row r="103" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="4"/>
@@ -10911,8 +11248,8 @@
       <c r="AT103" s="4"/>
       <c r="AU103" s="4"/>
       <c r="AV103" s="4"/>
-      <c r="AW103" s="3"/>
-      <c r="AX103" s="3"/>
+      <c r="AW103" s="4"/>
+      <c r="AX103" s="4"/>
       <c r="AY103" s="3"/>
       <c r="AZ103" s="3"/>
       <c r="BA103" s="3"/>
@@ -10943,8 +11280,10 @@
       <c r="BZ103" s="3"/>
       <c r="CA103" s="3"/>
       <c r="CB103" s="3"/>
-    </row>
-    <row r="104" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC103" s="3"/>
+      <c r="CD103" s="3"/>
+    </row>
+    <row r="104" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="4"/>
@@ -10991,8 +11330,8 @@
       <c r="AT104" s="4"/>
       <c r="AU104" s="4"/>
       <c r="AV104" s="4"/>
-      <c r="AW104" s="3"/>
-      <c r="AX104" s="3"/>
+      <c r="AW104" s="4"/>
+      <c r="AX104" s="4"/>
       <c r="AY104" s="3"/>
       <c r="AZ104" s="3"/>
       <c r="BA104" s="3"/>
@@ -11023,8 +11362,10 @@
       <c r="BZ104" s="3"/>
       <c r="CA104" s="3"/>
       <c r="CB104" s="3"/>
-    </row>
-    <row r="105" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC104" s="3"/>
+      <c r="CD104" s="3"/>
+    </row>
+    <row r="105" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="4"/>
@@ -11071,8 +11412,8 @@
       <c r="AT105" s="4"/>
       <c r="AU105" s="4"/>
       <c r="AV105" s="4"/>
-      <c r="AW105" s="3"/>
-      <c r="AX105" s="3"/>
+      <c r="AW105" s="4"/>
+      <c r="AX105" s="4"/>
       <c r="AY105" s="3"/>
       <c r="AZ105" s="3"/>
       <c r="BA105" s="3"/>
@@ -11103,8 +11444,10 @@
       <c r="BZ105" s="3"/>
       <c r="CA105" s="3"/>
       <c r="CB105" s="3"/>
-    </row>
-    <row r="106" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC105" s="3"/>
+      <c r="CD105" s="3"/>
+    </row>
+    <row r="106" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="4"/>
@@ -11151,8 +11494,8 @@
       <c r="AT106" s="4"/>
       <c r="AU106" s="4"/>
       <c r="AV106" s="4"/>
-      <c r="AW106" s="3"/>
-      <c r="AX106" s="3"/>
+      <c r="AW106" s="4"/>
+      <c r="AX106" s="4"/>
       <c r="AY106" s="3"/>
       <c r="AZ106" s="3"/>
       <c r="BA106" s="3"/>
@@ -11183,8 +11526,10 @@
       <c r="BZ106" s="3"/>
       <c r="CA106" s="3"/>
       <c r="CB106" s="3"/>
-    </row>
-    <row r="107" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC106" s="3"/>
+      <c r="CD106" s="3"/>
+    </row>
+    <row r="107" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="4"/>
@@ -11231,8 +11576,8 @@
       <c r="AT107" s="4"/>
       <c r="AU107" s="4"/>
       <c r="AV107" s="4"/>
-      <c r="AW107" s="3"/>
-      <c r="AX107" s="3"/>
+      <c r="AW107" s="4"/>
+      <c r="AX107" s="4"/>
       <c r="AY107" s="3"/>
       <c r="AZ107" s="3"/>
       <c r="BA107" s="3"/>
@@ -11263,8 +11608,10 @@
       <c r="BZ107" s="3"/>
       <c r="CA107" s="3"/>
       <c r="CB107" s="3"/>
-    </row>
-    <row r="108" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC107" s="3"/>
+      <c r="CD107" s="3"/>
+    </row>
+    <row r="108" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="4"/>
@@ -11311,8 +11658,8 @@
       <c r="AT108" s="4"/>
       <c r="AU108" s="4"/>
       <c r="AV108" s="4"/>
-      <c r="AW108" s="3"/>
-      <c r="AX108" s="3"/>
+      <c r="AW108" s="4"/>
+      <c r="AX108" s="4"/>
       <c r="AY108" s="3"/>
       <c r="AZ108" s="3"/>
       <c r="BA108" s="3"/>
@@ -11343,8 +11690,10 @@
       <c r="BZ108" s="3"/>
       <c r="CA108" s="3"/>
       <c r="CB108" s="3"/>
-    </row>
-    <row r="109" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC108" s="3"/>
+      <c r="CD108" s="3"/>
+    </row>
+    <row r="109" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="4"/>
@@ -11391,8 +11740,8 @@
       <c r="AT109" s="4"/>
       <c r="AU109" s="4"/>
       <c r="AV109" s="4"/>
-      <c r="AW109" s="3"/>
-      <c r="AX109" s="3"/>
+      <c r="AW109" s="4"/>
+      <c r="AX109" s="4"/>
       <c r="AY109" s="3"/>
       <c r="AZ109" s="3"/>
       <c r="BA109" s="3"/>
@@ -11423,8 +11772,10 @@
       <c r="BZ109" s="3"/>
       <c r="CA109" s="3"/>
       <c r="CB109" s="3"/>
-    </row>
-    <row r="110" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC109" s="3"/>
+      <c r="CD109" s="3"/>
+    </row>
+    <row r="110" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="4"/>
@@ -11471,8 +11822,8 @@
       <c r="AT110" s="4"/>
       <c r="AU110" s="4"/>
       <c r="AV110" s="4"/>
-      <c r="AW110" s="3"/>
-      <c r="AX110" s="3"/>
+      <c r="AW110" s="4"/>
+      <c r="AX110" s="4"/>
       <c r="AY110" s="3"/>
       <c r="AZ110" s="3"/>
       <c r="BA110" s="3"/>
@@ -11503,8 +11854,10 @@
       <c r="BZ110" s="3"/>
       <c r="CA110" s="3"/>
       <c r="CB110" s="3"/>
-    </row>
-    <row r="111" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC110" s="3"/>
+      <c r="CD110" s="3"/>
+    </row>
+    <row r="111" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="4"/>
@@ -11551,8 +11904,8 @@
       <c r="AT111" s="4"/>
       <c r="AU111" s="4"/>
       <c r="AV111" s="4"/>
-      <c r="AW111" s="3"/>
-      <c r="AX111" s="3"/>
+      <c r="AW111" s="4"/>
+      <c r="AX111" s="4"/>
       <c r="AY111" s="3"/>
       <c r="AZ111" s="3"/>
       <c r="BA111" s="3"/>
@@ -11583,8 +11936,10 @@
       <c r="BZ111" s="3"/>
       <c r="CA111" s="3"/>
       <c r="CB111" s="3"/>
-    </row>
-    <row r="112" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC111" s="3"/>
+      <c r="CD111" s="3"/>
+    </row>
+    <row r="112" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="4"/>
@@ -11631,8 +11986,8 @@
       <c r="AT112" s="4"/>
       <c r="AU112" s="4"/>
       <c r="AV112" s="4"/>
-      <c r="AW112" s="3"/>
-      <c r="AX112" s="3"/>
+      <c r="AW112" s="4"/>
+      <c r="AX112" s="4"/>
       <c r="AY112" s="3"/>
       <c r="AZ112" s="3"/>
       <c r="BA112" s="3"/>
@@ -11663,8 +12018,10 @@
       <c r="BZ112" s="3"/>
       <c r="CA112" s="3"/>
       <c r="CB112" s="3"/>
-    </row>
-    <row r="113" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC112" s="3"/>
+      <c r="CD112" s="3"/>
+    </row>
+    <row r="113" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="4"/>
@@ -11711,8 +12068,8 @@
       <c r="AT113" s="4"/>
       <c r="AU113" s="4"/>
       <c r="AV113" s="4"/>
-      <c r="AW113" s="3"/>
-      <c r="AX113" s="3"/>
+      <c r="AW113" s="4"/>
+      <c r="AX113" s="4"/>
       <c r="AY113" s="3"/>
       <c r="AZ113" s="3"/>
       <c r="BA113" s="3"/>
@@ -11743,8 +12100,10 @@
       <c r="BZ113" s="3"/>
       <c r="CA113" s="3"/>
       <c r="CB113" s="3"/>
-    </row>
-    <row r="114" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC113" s="3"/>
+      <c r="CD113" s="3"/>
+    </row>
+    <row r="114" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="4"/>
@@ -11791,8 +12150,8 @@
       <c r="AT114" s="4"/>
       <c r="AU114" s="4"/>
       <c r="AV114" s="4"/>
-      <c r="AW114" s="3"/>
-      <c r="AX114" s="3"/>
+      <c r="AW114" s="4"/>
+      <c r="AX114" s="4"/>
       <c r="AY114" s="3"/>
       <c r="AZ114" s="3"/>
       <c r="BA114" s="3"/>
@@ -11823,8 +12182,10 @@
       <c r="BZ114" s="3"/>
       <c r="CA114" s="3"/>
       <c r="CB114" s="3"/>
-    </row>
-    <row r="115" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC114" s="3"/>
+      <c r="CD114" s="3"/>
+    </row>
+    <row r="115" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="4"/>
@@ -11871,8 +12232,8 @@
       <c r="AT115" s="4"/>
       <c r="AU115" s="4"/>
       <c r="AV115" s="4"/>
-      <c r="AW115" s="3"/>
-      <c r="AX115" s="3"/>
+      <c r="AW115" s="4"/>
+      <c r="AX115" s="4"/>
       <c r="AY115" s="3"/>
       <c r="AZ115" s="3"/>
       <c r="BA115" s="3"/>
@@ -11903,8 +12264,10 @@
       <c r="BZ115" s="3"/>
       <c r="CA115" s="3"/>
       <c r="CB115" s="3"/>
-    </row>
-    <row r="116" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC115" s="3"/>
+      <c r="CD115" s="3"/>
+    </row>
+    <row r="116" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="4"/>
@@ -11951,8 +12314,8 @@
       <c r="AT116" s="4"/>
       <c r="AU116" s="4"/>
       <c r="AV116" s="4"/>
-      <c r="AW116" s="3"/>
-      <c r="AX116" s="3"/>
+      <c r="AW116" s="4"/>
+      <c r="AX116" s="4"/>
       <c r="AY116" s="3"/>
       <c r="AZ116" s="3"/>
       <c r="BA116" s="3"/>
@@ -11983,8 +12346,10 @@
       <c r="BZ116" s="3"/>
       <c r="CA116" s="3"/>
       <c r="CB116" s="3"/>
-    </row>
-    <row r="117" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC116" s="3"/>
+      <c r="CD116" s="3"/>
+    </row>
+    <row r="117" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="4"/>
@@ -12031,8 +12396,8 @@
       <c r="AT117" s="4"/>
       <c r="AU117" s="4"/>
       <c r="AV117" s="4"/>
-      <c r="AW117" s="3"/>
-      <c r="AX117" s="3"/>
+      <c r="AW117" s="4"/>
+      <c r="AX117" s="4"/>
       <c r="AY117" s="3"/>
       <c r="AZ117" s="3"/>
       <c r="BA117" s="3"/>
@@ -12063,8 +12428,10 @@
       <c r="BZ117" s="3"/>
       <c r="CA117" s="3"/>
       <c r="CB117" s="3"/>
-    </row>
-    <row r="118" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC117" s="3"/>
+      <c r="CD117" s="3"/>
+    </row>
+    <row r="118" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="4"/>
@@ -12111,8 +12478,8 @@
       <c r="AT118" s="4"/>
       <c r="AU118" s="4"/>
       <c r="AV118" s="4"/>
-      <c r="AW118" s="3"/>
-      <c r="AX118" s="3"/>
+      <c r="AW118" s="4"/>
+      <c r="AX118" s="4"/>
       <c r="AY118" s="3"/>
       <c r="AZ118" s="3"/>
       <c r="BA118" s="3"/>
@@ -12143,8 +12510,10 @@
       <c r="BZ118" s="3"/>
       <c r="CA118" s="3"/>
       <c r="CB118" s="3"/>
-    </row>
-    <row r="119" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC118" s="3"/>
+      <c r="CD118" s="3"/>
+    </row>
+    <row r="119" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="4"/>
@@ -12191,8 +12560,8 @@
       <c r="AT119" s="4"/>
       <c r="AU119" s="4"/>
       <c r="AV119" s="4"/>
-      <c r="AW119" s="3"/>
-      <c r="AX119" s="3"/>
+      <c r="AW119" s="4"/>
+      <c r="AX119" s="4"/>
       <c r="AY119" s="3"/>
       <c r="AZ119" s="3"/>
       <c r="BA119" s="3"/>
@@ -12223,8 +12592,10 @@
       <c r="BZ119" s="3"/>
       <c r="CA119" s="3"/>
       <c r="CB119" s="3"/>
-    </row>
-    <row r="120" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC119" s="3"/>
+      <c r="CD119" s="3"/>
+    </row>
+    <row r="120" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="4"/>
@@ -12271,8 +12642,8 @@
       <c r="AT120" s="4"/>
       <c r="AU120" s="4"/>
       <c r="AV120" s="4"/>
-      <c r="AW120" s="3"/>
-      <c r="AX120" s="3"/>
+      <c r="AW120" s="4"/>
+      <c r="AX120" s="4"/>
       <c r="AY120" s="3"/>
       <c r="AZ120" s="3"/>
       <c r="BA120" s="3"/>
@@ -12303,8 +12674,10 @@
       <c r="BZ120" s="3"/>
       <c r="CA120" s="3"/>
       <c r="CB120" s="3"/>
-    </row>
-    <row r="121" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC120" s="3"/>
+      <c r="CD120" s="3"/>
+    </row>
+    <row r="121" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="4"/>
@@ -12351,8 +12724,8 @@
       <c r="AT121" s="4"/>
       <c r="AU121" s="4"/>
       <c r="AV121" s="4"/>
-      <c r="AW121" s="3"/>
-      <c r="AX121" s="3"/>
+      <c r="AW121" s="4"/>
+      <c r="AX121" s="4"/>
       <c r="AY121" s="3"/>
       <c r="AZ121" s="3"/>
       <c r="BA121" s="3"/>
@@ -12383,8 +12756,10 @@
       <c r="BZ121" s="3"/>
       <c r="CA121" s="3"/>
       <c r="CB121" s="3"/>
-    </row>
-    <row r="122" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC121" s="3"/>
+      <c r="CD121" s="3"/>
+    </row>
+    <row r="122" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="4"/>
@@ -12431,8 +12806,8 @@
       <c r="AT122" s="4"/>
       <c r="AU122" s="4"/>
       <c r="AV122" s="4"/>
-      <c r="AW122" s="3"/>
-      <c r="AX122" s="3"/>
+      <c r="AW122" s="4"/>
+      <c r="AX122" s="4"/>
       <c r="AY122" s="3"/>
       <c r="AZ122" s="3"/>
       <c r="BA122" s="3"/>
@@ -12463,8 +12838,10 @@
       <c r="BZ122" s="3"/>
       <c r="CA122" s="3"/>
       <c r="CB122" s="3"/>
-    </row>
-    <row r="123" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC122" s="3"/>
+      <c r="CD122" s="3"/>
+    </row>
+    <row r="123" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="4"/>
@@ -12511,8 +12888,8 @@
       <c r="AT123" s="4"/>
       <c r="AU123" s="4"/>
       <c r="AV123" s="4"/>
-      <c r="AW123" s="3"/>
-      <c r="AX123" s="3"/>
+      <c r="AW123" s="4"/>
+      <c r="AX123" s="4"/>
       <c r="AY123" s="3"/>
       <c r="AZ123" s="3"/>
       <c r="BA123" s="3"/>
@@ -12543,8 +12920,10 @@
       <c r="BZ123" s="3"/>
       <c r="CA123" s="3"/>
       <c r="CB123" s="3"/>
-    </row>
-    <row r="124" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC123" s="3"/>
+      <c r="CD123" s="3"/>
+    </row>
+    <row r="124" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="4"/>
@@ -12591,8 +12970,8 @@
       <c r="AT124" s="4"/>
       <c r="AU124" s="4"/>
       <c r="AV124" s="4"/>
-      <c r="AW124" s="3"/>
-      <c r="AX124" s="3"/>
+      <c r="AW124" s="4"/>
+      <c r="AX124" s="4"/>
       <c r="AY124" s="3"/>
       <c r="AZ124" s="3"/>
       <c r="BA124" s="3"/>
@@ -12623,8 +13002,10 @@
       <c r="BZ124" s="3"/>
       <c r="CA124" s="3"/>
       <c r="CB124" s="3"/>
-    </row>
-    <row r="125" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC124" s="3"/>
+      <c r="CD124" s="3"/>
+    </row>
+    <row r="125" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="4"/>
@@ -12671,8 +13052,8 @@
       <c r="AT125" s="4"/>
       <c r="AU125" s="4"/>
       <c r="AV125" s="4"/>
-      <c r="AW125" s="3"/>
-      <c r="AX125" s="3"/>
+      <c r="AW125" s="4"/>
+      <c r="AX125" s="4"/>
       <c r="AY125" s="3"/>
       <c r="AZ125" s="3"/>
       <c r="BA125" s="3"/>
@@ -12703,8 +13084,10 @@
       <c r="BZ125" s="3"/>
       <c r="CA125" s="3"/>
       <c r="CB125" s="3"/>
-    </row>
-    <row r="126" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC125" s="3"/>
+      <c r="CD125" s="3"/>
+    </row>
+    <row r="126" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="4"/>
@@ -12751,8 +13134,8 @@
       <c r="AT126" s="4"/>
       <c r="AU126" s="4"/>
       <c r="AV126" s="4"/>
-      <c r="AW126" s="3"/>
-      <c r="AX126" s="3"/>
+      <c r="AW126" s="4"/>
+      <c r="AX126" s="4"/>
       <c r="AY126" s="3"/>
       <c r="AZ126" s="3"/>
       <c r="BA126" s="3"/>
@@ -12783,8 +13166,10 @@
       <c r="BZ126" s="3"/>
       <c r="CA126" s="3"/>
       <c r="CB126" s="3"/>
-    </row>
-    <row r="127" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC126" s="3"/>
+      <c r="CD126" s="3"/>
+    </row>
+    <row r="127" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="4"/>
@@ -12831,8 +13216,8 @@
       <c r="AT127" s="4"/>
       <c r="AU127" s="4"/>
       <c r="AV127" s="4"/>
-      <c r="AW127" s="3"/>
-      <c r="AX127" s="3"/>
+      <c r="AW127" s="4"/>
+      <c r="AX127" s="4"/>
       <c r="AY127" s="3"/>
       <c r="AZ127" s="3"/>
       <c r="BA127" s="3"/>
@@ -12863,8 +13248,10 @@
       <c r="BZ127" s="3"/>
       <c r="CA127" s="3"/>
       <c r="CB127" s="3"/>
-    </row>
-    <row r="128" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC127" s="3"/>
+      <c r="CD127" s="3"/>
+    </row>
+    <row r="128" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="4"/>
@@ -12911,8 +13298,8 @@
       <c r="AT128" s="4"/>
       <c r="AU128" s="4"/>
       <c r="AV128" s="4"/>
-      <c r="AW128" s="3"/>
-      <c r="AX128" s="3"/>
+      <c r="AW128" s="4"/>
+      <c r="AX128" s="4"/>
       <c r="AY128" s="3"/>
       <c r="AZ128" s="3"/>
       <c r="BA128" s="3"/>
@@ -12943,8 +13330,10 @@
       <c r="BZ128" s="3"/>
       <c r="CA128" s="3"/>
       <c r="CB128" s="3"/>
-    </row>
-    <row r="129" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC128" s="3"/>
+      <c r="CD128" s="3"/>
+    </row>
+    <row r="129" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="4"/>
@@ -12991,8 +13380,8 @@
       <c r="AT129" s="4"/>
       <c r="AU129" s="4"/>
       <c r="AV129" s="4"/>
-      <c r="AW129" s="3"/>
-      <c r="AX129" s="3"/>
+      <c r="AW129" s="4"/>
+      <c r="AX129" s="4"/>
       <c r="AY129" s="3"/>
       <c r="AZ129" s="3"/>
       <c r="BA129" s="3"/>
@@ -13023,8 +13412,10 @@
       <c r="BZ129" s="3"/>
       <c r="CA129" s="3"/>
       <c r="CB129" s="3"/>
-    </row>
-    <row r="130" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC129" s="3"/>
+      <c r="CD129" s="3"/>
+    </row>
+    <row r="130" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="4"/>
@@ -13071,8 +13462,8 @@
       <c r="AT130" s="4"/>
       <c r="AU130" s="4"/>
       <c r="AV130" s="4"/>
-      <c r="AW130" s="3"/>
-      <c r="AX130" s="3"/>
+      <c r="AW130" s="4"/>
+      <c r="AX130" s="4"/>
       <c r="AY130" s="3"/>
       <c r="AZ130" s="3"/>
       <c r="BA130" s="3"/>
@@ -13103,8 +13494,10 @@
       <c r="BZ130" s="3"/>
       <c r="CA130" s="3"/>
       <c r="CB130" s="3"/>
-    </row>
-    <row r="131" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC130" s="3"/>
+      <c r="CD130" s="3"/>
+    </row>
+    <row r="131" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="4"/>
@@ -13151,8 +13544,8 @@
       <c r="AT131" s="4"/>
       <c r="AU131" s="4"/>
       <c r="AV131" s="4"/>
-      <c r="AW131" s="3"/>
-      <c r="AX131" s="3"/>
+      <c r="AW131" s="4"/>
+      <c r="AX131" s="4"/>
       <c r="AY131" s="3"/>
       <c r="AZ131" s="3"/>
       <c r="BA131" s="3"/>
@@ -13183,8 +13576,10 @@
       <c r="BZ131" s="3"/>
       <c r="CA131" s="3"/>
       <c r="CB131" s="3"/>
-    </row>
-    <row r="132" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC131" s="3"/>
+      <c r="CD131" s="3"/>
+    </row>
+    <row r="132" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="4"/>
@@ -13231,8 +13626,8 @@
       <c r="AT132" s="4"/>
       <c r="AU132" s="4"/>
       <c r="AV132" s="4"/>
-      <c r="AW132" s="3"/>
-      <c r="AX132" s="3"/>
+      <c r="AW132" s="4"/>
+      <c r="AX132" s="4"/>
       <c r="AY132" s="3"/>
       <c r="AZ132" s="3"/>
       <c r="BA132" s="3"/>
@@ -13263,8 +13658,10 @@
       <c r="BZ132" s="3"/>
       <c r="CA132" s="3"/>
       <c r="CB132" s="3"/>
-    </row>
-    <row r="133" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC132" s="3"/>
+      <c r="CD132" s="3"/>
+    </row>
+    <row r="133" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="4"/>
@@ -13311,8 +13708,8 @@
       <c r="AT133" s="4"/>
       <c r="AU133" s="4"/>
       <c r="AV133" s="4"/>
-      <c r="AW133" s="3"/>
-      <c r="AX133" s="3"/>
+      <c r="AW133" s="4"/>
+      <c r="AX133" s="4"/>
       <c r="AY133" s="3"/>
       <c r="AZ133" s="3"/>
       <c r="BA133" s="3"/>
@@ -13343,8 +13740,10 @@
       <c r="BZ133" s="3"/>
       <c r="CA133" s="3"/>
       <c r="CB133" s="3"/>
-    </row>
-    <row r="134" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC133" s="3"/>
+      <c r="CD133" s="3"/>
+    </row>
+    <row r="134" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="4"/>
@@ -13391,8 +13790,8 @@
       <c r="AT134" s="4"/>
       <c r="AU134" s="4"/>
       <c r="AV134" s="4"/>
-      <c r="AW134" s="3"/>
-      <c r="AX134" s="3"/>
+      <c r="AW134" s="4"/>
+      <c r="AX134" s="4"/>
       <c r="AY134" s="3"/>
       <c r="AZ134" s="3"/>
       <c r="BA134" s="3"/>
@@ -13423,8 +13822,10 @@
       <c r="BZ134" s="3"/>
       <c r="CA134" s="3"/>
       <c r="CB134" s="3"/>
-    </row>
-    <row r="135" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC134" s="3"/>
+      <c r="CD134" s="3"/>
+    </row>
+    <row r="135" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="4"/>
@@ -13471,8 +13872,8 @@
       <c r="AT135" s="4"/>
       <c r="AU135" s="4"/>
       <c r="AV135" s="4"/>
-      <c r="AW135" s="3"/>
-      <c r="AX135" s="3"/>
+      <c r="AW135" s="4"/>
+      <c r="AX135" s="4"/>
       <c r="AY135" s="3"/>
       <c r="AZ135" s="3"/>
       <c r="BA135" s="3"/>
@@ -13503,8 +13904,10 @@
       <c r="BZ135" s="3"/>
       <c r="CA135" s="3"/>
       <c r="CB135" s="3"/>
-    </row>
-    <row r="136" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC135" s="3"/>
+      <c r="CD135" s="3"/>
+    </row>
+    <row r="136" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="4"/>
@@ -13551,8 +13954,8 @@
       <c r="AT136" s="4"/>
       <c r="AU136" s="4"/>
       <c r="AV136" s="4"/>
-      <c r="AW136" s="3"/>
-      <c r="AX136" s="3"/>
+      <c r="AW136" s="4"/>
+      <c r="AX136" s="4"/>
       <c r="AY136" s="3"/>
       <c r="AZ136" s="3"/>
       <c r="BA136" s="3"/>
@@ -13583,8 +13986,10 @@
       <c r="BZ136" s="3"/>
       <c r="CA136" s="3"/>
       <c r="CB136" s="3"/>
-    </row>
-    <row r="137" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC136" s="3"/>
+      <c r="CD136" s="3"/>
+    </row>
+    <row r="137" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="4"/>
@@ -13631,8 +14036,8 @@
       <c r="AT137" s="4"/>
       <c r="AU137" s="4"/>
       <c r="AV137" s="4"/>
-      <c r="AW137" s="3"/>
-      <c r="AX137" s="3"/>
+      <c r="AW137" s="4"/>
+      <c r="AX137" s="4"/>
       <c r="AY137" s="3"/>
       <c r="AZ137" s="3"/>
       <c r="BA137" s="3"/>
@@ -13663,8 +14068,10 @@
       <c r="BZ137" s="3"/>
       <c r="CA137" s="3"/>
       <c r="CB137" s="3"/>
-    </row>
-    <row r="138" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC137" s="3"/>
+      <c r="CD137" s="3"/>
+    </row>
+    <row r="138" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="4"/>
@@ -13711,8 +14118,8 @@
       <c r="AT138" s="4"/>
       <c r="AU138" s="4"/>
       <c r="AV138" s="4"/>
-      <c r="AW138" s="3"/>
-      <c r="AX138" s="3"/>
+      <c r="AW138" s="4"/>
+      <c r="AX138" s="4"/>
       <c r="AY138" s="3"/>
       <c r="AZ138" s="3"/>
       <c r="BA138" s="3"/>
@@ -13743,8 +14150,10 @@
       <c r="BZ138" s="3"/>
       <c r="CA138" s="3"/>
       <c r="CB138" s="3"/>
-    </row>
-    <row r="139" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC138" s="3"/>
+      <c r="CD138" s="3"/>
+    </row>
+    <row r="139" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="4"/>
@@ -13791,8 +14200,8 @@
       <c r="AT139" s="4"/>
       <c r="AU139" s="4"/>
       <c r="AV139" s="4"/>
-      <c r="AW139" s="3"/>
-      <c r="AX139" s="3"/>
+      <c r="AW139" s="4"/>
+      <c r="AX139" s="4"/>
       <c r="AY139" s="3"/>
       <c r="AZ139" s="3"/>
       <c r="BA139" s="3"/>
@@ -13823,8 +14232,10 @@
       <c r="BZ139" s="3"/>
       <c r="CA139" s="3"/>
       <c r="CB139" s="3"/>
-    </row>
-    <row r="140" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC139" s="3"/>
+      <c r="CD139" s="3"/>
+    </row>
+    <row r="140" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="4"/>
@@ -13871,8 +14282,8 @@
       <c r="AT140" s="4"/>
       <c r="AU140" s="4"/>
       <c r="AV140" s="4"/>
-      <c r="AW140" s="3"/>
-      <c r="AX140" s="3"/>
+      <c r="AW140" s="4"/>
+      <c r="AX140" s="4"/>
       <c r="AY140" s="3"/>
       <c r="AZ140" s="3"/>
       <c r="BA140" s="3"/>
@@ -13903,8 +14314,10 @@
       <c r="BZ140" s="3"/>
       <c r="CA140" s="3"/>
       <c r="CB140" s="3"/>
-    </row>
-    <row r="141" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC140" s="3"/>
+      <c r="CD140" s="3"/>
+    </row>
+    <row r="141" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="4"/>
@@ -13951,8 +14364,8 @@
       <c r="AT141" s="4"/>
       <c r="AU141" s="4"/>
       <c r="AV141" s="4"/>
-      <c r="AW141" s="3"/>
-      <c r="AX141" s="3"/>
+      <c r="AW141" s="4"/>
+      <c r="AX141" s="4"/>
       <c r="AY141" s="3"/>
       <c r="AZ141" s="3"/>
       <c r="BA141" s="3"/>
@@ -13983,8 +14396,10 @@
       <c r="BZ141" s="3"/>
       <c r="CA141" s="3"/>
       <c r="CB141" s="3"/>
-    </row>
-    <row r="142" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC141" s="3"/>
+      <c r="CD141" s="3"/>
+    </row>
+    <row r="142" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="4"/>
@@ -14031,8 +14446,8 @@
       <c r="AT142" s="4"/>
       <c r="AU142" s="4"/>
       <c r="AV142" s="4"/>
-      <c r="AW142" s="3"/>
-      <c r="AX142" s="3"/>
+      <c r="AW142" s="4"/>
+      <c r="AX142" s="4"/>
       <c r="AY142" s="3"/>
       <c r="AZ142" s="3"/>
       <c r="BA142" s="3"/>
@@ -14063,8 +14478,10 @@
       <c r="BZ142" s="3"/>
       <c r="CA142" s="3"/>
       <c r="CB142" s="3"/>
-    </row>
-    <row r="143" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC142" s="3"/>
+      <c r="CD142" s="3"/>
+    </row>
+    <row r="143" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="4"/>
@@ -14111,8 +14528,8 @@
       <c r="AT143" s="4"/>
       <c r="AU143" s="4"/>
       <c r="AV143" s="4"/>
-      <c r="AW143" s="3"/>
-      <c r="AX143" s="3"/>
+      <c r="AW143" s="4"/>
+      <c r="AX143" s="4"/>
       <c r="AY143" s="3"/>
       <c r="AZ143" s="3"/>
       <c r="BA143" s="3"/>
@@ -14143,8 +14560,10 @@
       <c r="BZ143" s="3"/>
       <c r="CA143" s="3"/>
       <c r="CB143" s="3"/>
-    </row>
-    <row r="144" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC143" s="3"/>
+      <c r="CD143" s="3"/>
+    </row>
+    <row r="144" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="4"/>
@@ -14191,8 +14610,8 @@
       <c r="AT144" s="4"/>
       <c r="AU144" s="4"/>
       <c r="AV144" s="4"/>
-      <c r="AW144" s="3"/>
-      <c r="AX144" s="3"/>
+      <c r="AW144" s="4"/>
+      <c r="AX144" s="4"/>
       <c r="AY144" s="3"/>
       <c r="AZ144" s="3"/>
       <c r="BA144" s="3"/>
@@ -14223,8 +14642,10 @@
       <c r="BZ144" s="3"/>
       <c r="CA144" s="3"/>
       <c r="CB144" s="3"/>
-    </row>
-    <row r="145" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC144" s="3"/>
+      <c r="CD144" s="3"/>
+    </row>
+    <row r="145" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="4"/>
@@ -14271,8 +14692,8 @@
       <c r="AT145" s="4"/>
       <c r="AU145" s="4"/>
       <c r="AV145" s="4"/>
-      <c r="AW145" s="3"/>
-      <c r="AX145" s="3"/>
+      <c r="AW145" s="4"/>
+      <c r="AX145" s="4"/>
       <c r="AY145" s="3"/>
       <c r="AZ145" s="3"/>
       <c r="BA145" s="3"/>
@@ -14303,8 +14724,10 @@
       <c r="BZ145" s="3"/>
       <c r="CA145" s="3"/>
       <c r="CB145" s="3"/>
-    </row>
-    <row r="146" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC145" s="3"/>
+      <c r="CD145" s="3"/>
+    </row>
+    <row r="146" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="4"/>
@@ -14351,8 +14774,8 @@
       <c r="AT146" s="4"/>
       <c r="AU146" s="4"/>
       <c r="AV146" s="4"/>
-      <c r="AW146" s="3"/>
-      <c r="AX146" s="3"/>
+      <c r="AW146" s="4"/>
+      <c r="AX146" s="4"/>
       <c r="AY146" s="3"/>
       <c r="AZ146" s="3"/>
       <c r="BA146" s="3"/>
@@ -14383,8 +14806,10 @@
       <c r="BZ146" s="3"/>
       <c r="CA146" s="3"/>
       <c r="CB146" s="3"/>
-    </row>
-    <row r="147" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC146" s="3"/>
+      <c r="CD146" s="3"/>
+    </row>
+    <row r="147" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="4"/>
@@ -14431,8 +14856,8 @@
       <c r="AT147" s="4"/>
       <c r="AU147" s="4"/>
       <c r="AV147" s="4"/>
-      <c r="AW147" s="3"/>
-      <c r="AX147" s="3"/>
+      <c r="AW147" s="4"/>
+      <c r="AX147" s="4"/>
       <c r="AY147" s="3"/>
       <c r="AZ147" s="3"/>
       <c r="BA147" s="3"/>
@@ -14463,8 +14888,10 @@
       <c r="BZ147" s="3"/>
       <c r="CA147" s="3"/>
       <c r="CB147" s="3"/>
-    </row>
-    <row r="148" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC147" s="3"/>
+      <c r="CD147" s="3"/>
+    </row>
+    <row r="148" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="4"/>
@@ -14511,8 +14938,8 @@
       <c r="AT148" s="4"/>
       <c r="AU148" s="4"/>
       <c r="AV148" s="4"/>
-      <c r="AW148" s="3"/>
-      <c r="AX148" s="3"/>
+      <c r="AW148" s="4"/>
+      <c r="AX148" s="4"/>
       <c r="AY148" s="3"/>
       <c r="AZ148" s="3"/>
       <c r="BA148" s="3"/>
@@ -14543,8 +14970,10 @@
       <c r="BZ148" s="3"/>
       <c r="CA148" s="3"/>
       <c r="CB148" s="3"/>
-    </row>
-    <row r="149" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC148" s="3"/>
+      <c r="CD148" s="3"/>
+    </row>
+    <row r="149" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -14623,8 +15052,10 @@
       <c r="BZ149" s="3"/>
       <c r="CA149" s="3"/>
       <c r="CB149" s="3"/>
-    </row>
-    <row r="150" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC149" s="3"/>
+      <c r="CD149" s="3"/>
+    </row>
+    <row r="150" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -14703,8 +15134,10 @@
       <c r="BZ150" s="3"/>
       <c r="CA150" s="3"/>
       <c r="CB150" s="3"/>
-    </row>
-    <row r="151" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC150" s="3"/>
+      <c r="CD150" s="3"/>
+    </row>
+    <row r="151" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -14783,8 +15216,10 @@
       <c r="BZ151" s="3"/>
       <c r="CA151" s="3"/>
       <c r="CB151" s="3"/>
-    </row>
-    <row r="152" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC151" s="3"/>
+      <c r="CD151" s="3"/>
+    </row>
+    <row r="152" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -14863,8 +15298,10 @@
       <c r="BZ152" s="3"/>
       <c r="CA152" s="3"/>
       <c r="CB152" s="3"/>
-    </row>
-    <row r="153" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC152" s="3"/>
+      <c r="CD152" s="3"/>
+    </row>
+    <row r="153" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -14943,8 +15380,10 @@
       <c r="BZ153" s="3"/>
       <c r="CA153" s="3"/>
       <c r="CB153" s="3"/>
-    </row>
-    <row r="154" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC153" s="3"/>
+      <c r="CD153" s="3"/>
+    </row>
+    <row r="154" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -15023,8 +15462,10 @@
       <c r="BZ154" s="3"/>
       <c r="CA154" s="3"/>
       <c r="CB154" s="3"/>
-    </row>
-    <row r="155" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC154" s="3"/>
+      <c r="CD154" s="3"/>
+    </row>
+    <row r="155" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -15103,8 +15544,10 @@
       <c r="BZ155" s="3"/>
       <c r="CA155" s="3"/>
       <c r="CB155" s="3"/>
-    </row>
-    <row r="156" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC155" s="3"/>
+      <c r="CD155" s="3"/>
+    </row>
+    <row r="156" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -15183,8 +15626,10 @@
       <c r="BZ156" s="3"/>
       <c r="CA156" s="3"/>
       <c r="CB156" s="3"/>
-    </row>
-    <row r="157" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC156" s="3"/>
+      <c r="CD156" s="3"/>
+    </row>
+    <row r="157" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -15263,8 +15708,10 @@
       <c r="BZ157" s="3"/>
       <c r="CA157" s="3"/>
       <c r="CB157" s="3"/>
-    </row>
-    <row r="158" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC157" s="3"/>
+      <c r="CD157" s="3"/>
+    </row>
+    <row r="158" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -15343,8 +15790,10 @@
       <c r="BZ158" s="3"/>
       <c r="CA158" s="3"/>
       <c r="CB158" s="3"/>
-    </row>
-    <row r="159" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC158" s="3"/>
+      <c r="CD158" s="3"/>
+    </row>
+    <row r="159" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -15423,8 +15872,10 @@
       <c r="BZ159" s="3"/>
       <c r="CA159" s="3"/>
       <c r="CB159" s="3"/>
-    </row>
-    <row r="160" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC159" s="3"/>
+      <c r="CD159" s="3"/>
+    </row>
+    <row r="160" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -15503,8 +15954,10 @@
       <c r="BZ160" s="3"/>
       <c r="CA160" s="3"/>
       <c r="CB160" s="3"/>
-    </row>
-    <row r="161" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC160" s="3"/>
+      <c r="CD160" s="3"/>
+    </row>
+    <row r="161" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -15583,8 +16036,10 @@
       <c r="BZ161" s="3"/>
       <c r="CA161" s="3"/>
       <c r="CB161" s="3"/>
-    </row>
-    <row r="162" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC161" s="3"/>
+      <c r="CD161" s="3"/>
+    </row>
+    <row r="162" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -15663,8 +16118,10 @@
       <c r="BZ162" s="3"/>
       <c r="CA162" s="3"/>
       <c r="CB162" s="3"/>
-    </row>
-    <row r="163" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC162" s="3"/>
+      <c r="CD162" s="3"/>
+    </row>
+    <row r="163" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -15743,8 +16200,10 @@
       <c r="BZ163" s="3"/>
       <c r="CA163" s="3"/>
       <c r="CB163" s="3"/>
-    </row>
-    <row r="164" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC163" s="3"/>
+      <c r="CD163" s="3"/>
+    </row>
+    <row r="164" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -15823,8 +16282,10 @@
       <c r="BZ164" s="3"/>
       <c r="CA164" s="3"/>
       <c r="CB164" s="3"/>
-    </row>
-    <row r="165" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC164" s="3"/>
+      <c r="CD164" s="3"/>
+    </row>
+    <row r="165" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -15903,8 +16364,10 @@
       <c r="BZ165" s="3"/>
       <c r="CA165" s="3"/>
       <c r="CB165" s="3"/>
-    </row>
-    <row r="166" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC165" s="3"/>
+      <c r="CD165" s="3"/>
+    </row>
+    <row r="166" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -15983,8 +16446,10 @@
       <c r="BZ166" s="3"/>
       <c r="CA166" s="3"/>
       <c r="CB166" s="3"/>
-    </row>
-    <row r="167" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC166" s="3"/>
+      <c r="CD166" s="3"/>
+    </row>
+    <row r="167" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -16063,8 +16528,10 @@
       <c r="BZ167" s="3"/>
       <c r="CA167" s="3"/>
       <c r="CB167" s="3"/>
-    </row>
-    <row r="168" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC167" s="3"/>
+      <c r="CD167" s="3"/>
+    </row>
+    <row r="168" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -16143,8 +16610,10 @@
       <c r="BZ168" s="3"/>
       <c r="CA168" s="3"/>
       <c r="CB168" s="3"/>
-    </row>
-    <row r="169" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC168" s="3"/>
+      <c r="CD168" s="3"/>
+    </row>
+    <row r="169" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -16223,8 +16692,10 @@
       <c r="BZ169" s="3"/>
       <c r="CA169" s="3"/>
       <c r="CB169" s="3"/>
-    </row>
-    <row r="170" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC169" s="3"/>
+      <c r="CD169" s="3"/>
+    </row>
+    <row r="170" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -16303,8 +16774,10 @@
       <c r="BZ170" s="3"/>
       <c r="CA170" s="3"/>
       <c r="CB170" s="3"/>
-    </row>
-    <row r="171" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC170" s="3"/>
+      <c r="CD170" s="3"/>
+    </row>
+    <row r="171" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -16383,8 +16856,10 @@
       <c r="BZ171" s="3"/>
       <c r="CA171" s="3"/>
       <c r="CB171" s="3"/>
-    </row>
-    <row r="172" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC171" s="3"/>
+      <c r="CD171" s="3"/>
+    </row>
+    <row r="172" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -16463,8 +16938,10 @@
       <c r="BZ172" s="3"/>
       <c r="CA172" s="3"/>
       <c r="CB172" s="3"/>
-    </row>
-    <row r="173" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC172" s="3"/>
+      <c r="CD172" s="3"/>
+    </row>
+    <row r="173" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -16543,8 +17020,10 @@
       <c r="BZ173" s="3"/>
       <c r="CA173" s="3"/>
       <c r="CB173" s="3"/>
-    </row>
-    <row r="174" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC173" s="3"/>
+      <c r="CD173" s="3"/>
+    </row>
+    <row r="174" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -16623,8 +17102,10 @@
       <c r="BZ174" s="3"/>
       <c r="CA174" s="3"/>
       <c r="CB174" s="3"/>
-    </row>
-    <row r="175" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC174" s="3"/>
+      <c r="CD174" s="3"/>
+    </row>
+    <row r="175" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -16703,8 +17184,10 @@
       <c r="BZ175" s="3"/>
       <c r="CA175" s="3"/>
       <c r="CB175" s="3"/>
-    </row>
-    <row r="176" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC175" s="3"/>
+      <c r="CD175" s="3"/>
+    </row>
+    <row r="176" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -16783,8 +17266,10 @@
       <c r="BZ176" s="3"/>
       <c r="CA176" s="3"/>
       <c r="CB176" s="3"/>
-    </row>
-    <row r="177" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC176" s="3"/>
+      <c r="CD176" s="3"/>
+    </row>
+    <row r="177" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -16863,8 +17348,10 @@
       <c r="BZ177" s="3"/>
       <c r="CA177" s="3"/>
       <c r="CB177" s="3"/>
-    </row>
-    <row r="178" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC177" s="3"/>
+      <c r="CD177" s="3"/>
+    </row>
+    <row r="178" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -16943,8 +17430,10 @@
       <c r="BZ178" s="3"/>
       <c r="CA178" s="3"/>
       <c r="CB178" s="3"/>
-    </row>
-    <row r="179" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC178" s="3"/>
+      <c r="CD178" s="3"/>
+    </row>
+    <row r="179" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -17023,8 +17512,10 @@
       <c r="BZ179" s="3"/>
       <c r="CA179" s="3"/>
       <c r="CB179" s="3"/>
-    </row>
-    <row r="180" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC179" s="3"/>
+      <c r="CD179" s="3"/>
+    </row>
+    <row r="180" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -17103,8 +17594,10 @@
       <c r="BZ180" s="3"/>
       <c r="CA180" s="3"/>
       <c r="CB180" s="3"/>
-    </row>
-    <row r="181" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC180" s="3"/>
+      <c r="CD180" s="3"/>
+    </row>
+    <row r="181" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -17183,8 +17676,10 @@
       <c r="BZ181" s="3"/>
       <c r="CA181" s="3"/>
       <c r="CB181" s="3"/>
-    </row>
-    <row r="182" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC181" s="3"/>
+      <c r="CD181" s="3"/>
+    </row>
+    <row r="182" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -17263,8 +17758,10 @@
       <c r="BZ182" s="3"/>
       <c r="CA182" s="3"/>
       <c r="CB182" s="3"/>
-    </row>
-    <row r="183" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC182" s="3"/>
+      <c r="CD182" s="3"/>
+    </row>
+    <row r="183" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -17343,8 +17840,10 @@
       <c r="BZ183" s="3"/>
       <c r="CA183" s="3"/>
       <c r="CB183" s="3"/>
-    </row>
-    <row r="184" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC183" s="3"/>
+      <c r="CD183" s="3"/>
+    </row>
+    <row r="184" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -17423,8 +17922,10 @@
       <c r="BZ184" s="3"/>
       <c r="CA184" s="3"/>
       <c r="CB184" s="3"/>
-    </row>
-    <row r="185" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC184" s="3"/>
+      <c r="CD184" s="3"/>
+    </row>
+    <row r="185" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -17503,8 +18004,10 @@
       <c r="BZ185" s="3"/>
       <c r="CA185" s="3"/>
       <c r="CB185" s="3"/>
-    </row>
-    <row r="186" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC185" s="3"/>
+      <c r="CD185" s="3"/>
+    </row>
+    <row r="186" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -17583,8 +18086,10 @@
       <c r="BZ186" s="3"/>
       <c r="CA186" s="3"/>
       <c r="CB186" s="3"/>
-    </row>
-    <row r="187" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC186" s="3"/>
+      <c r="CD186" s="3"/>
+    </row>
+    <row r="187" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -17663,8 +18168,10 @@
       <c r="BZ187" s="3"/>
       <c r="CA187" s="3"/>
       <c r="CB187" s="3"/>
-    </row>
-    <row r="188" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC187" s="3"/>
+      <c r="CD187" s="3"/>
+    </row>
+    <row r="188" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -17743,8 +18250,10 @@
       <c r="BZ188" s="3"/>
       <c r="CA188" s="3"/>
       <c r="CB188" s="3"/>
-    </row>
-    <row r="189" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC188" s="3"/>
+      <c r="CD188" s="3"/>
+    </row>
+    <row r="189" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -17823,8 +18332,10 @@
       <c r="BZ189" s="3"/>
       <c r="CA189" s="3"/>
       <c r="CB189" s="3"/>
-    </row>
-    <row r="190" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC189" s="3"/>
+      <c r="CD189" s="3"/>
+    </row>
+    <row r="190" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -17903,8 +18414,10 @@
       <c r="BZ190" s="3"/>
       <c r="CA190" s="3"/>
       <c r="CB190" s="3"/>
-    </row>
-    <row r="191" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC190" s="3"/>
+      <c r="CD190" s="3"/>
+    </row>
+    <row r="191" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -17983,8 +18496,10 @@
       <c r="BZ191" s="3"/>
       <c r="CA191" s="3"/>
       <c r="CB191" s="3"/>
-    </row>
-    <row r="192" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC191" s="3"/>
+      <c r="CD191" s="3"/>
+    </row>
+    <row r="192" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -18063,8 +18578,10 @@
       <c r="BZ192" s="3"/>
       <c r="CA192" s="3"/>
       <c r="CB192" s="3"/>
-    </row>
-    <row r="193" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC192" s="3"/>
+      <c r="CD192" s="3"/>
+    </row>
+    <row r="193" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -18143,8 +18660,10 @@
       <c r="BZ193" s="3"/>
       <c r="CA193" s="3"/>
       <c r="CB193" s="3"/>
-    </row>
-    <row r="194" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC193" s="3"/>
+      <c r="CD193" s="3"/>
+    </row>
+    <row r="194" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -18223,8 +18742,10 @@
       <c r="BZ194" s="3"/>
       <c r="CA194" s="3"/>
       <c r="CB194" s="3"/>
-    </row>
-    <row r="195" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC194" s="3"/>
+      <c r="CD194" s="3"/>
+    </row>
+    <row r="195" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -18303,8 +18824,10 @@
       <c r="BZ195" s="3"/>
       <c r="CA195" s="3"/>
       <c r="CB195" s="3"/>
-    </row>
-    <row r="196" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC195" s="3"/>
+      <c r="CD195" s="3"/>
+    </row>
+    <row r="196" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -18383,8 +18906,10 @@
       <c r="BZ196" s="3"/>
       <c r="CA196" s="3"/>
       <c r="CB196" s="3"/>
-    </row>
-    <row r="197" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC196" s="3"/>
+      <c r="CD196" s="3"/>
+    </row>
+    <row r="197" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -18463,8 +18988,10 @@
       <c r="BZ197" s="3"/>
       <c r="CA197" s="3"/>
       <c r="CB197" s="3"/>
-    </row>
-    <row r="198" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC197" s="3"/>
+      <c r="CD197" s="3"/>
+    </row>
+    <row r="198" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -18543,8 +19070,10 @@
       <c r="BZ198" s="3"/>
       <c r="CA198" s="3"/>
       <c r="CB198" s="3"/>
-    </row>
-    <row r="199" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC198" s="3"/>
+      <c r="CD198" s="3"/>
+    </row>
+    <row r="199" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -18623,8 +19152,10 @@
       <c r="BZ199" s="3"/>
       <c r="CA199" s="3"/>
       <c r="CB199" s="3"/>
-    </row>
-    <row r="200" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC199" s="3"/>
+      <c r="CD199" s="3"/>
+    </row>
+    <row r="200" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -18703,8 +19234,10 @@
       <c r="BZ200" s="3"/>
       <c r="CA200" s="3"/>
       <c r="CB200" s="3"/>
-    </row>
-    <row r="201" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC200" s="3"/>
+      <c r="CD200" s="3"/>
+    </row>
+    <row r="201" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C201" s="3"/>
       <c r="D201" s="3"/>
       <c r="E201" s="3"/>
@@ -18783,8 +19316,10 @@
       <c r="BZ201" s="3"/>
       <c r="CA201" s="3"/>
       <c r="CB201" s="3"/>
-    </row>
-    <row r="202" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC201" s="3"/>
+      <c r="CD201" s="3"/>
+    </row>
+    <row r="202" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C202" s="3"/>
       <c r="D202" s="3"/>
       <c r="E202" s="3"/>
@@ -18863,8 +19398,10 @@
       <c r="BZ202" s="3"/>
       <c r="CA202" s="3"/>
       <c r="CB202" s="3"/>
-    </row>
-    <row r="203" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC202" s="3"/>
+      <c r="CD202" s="3"/>
+    </row>
+    <row r="203" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C203" s="3"/>
       <c r="D203" s="3"/>
       <c r="E203" s="3"/>
@@ -18943,8 +19480,10 @@
       <c r="BZ203" s="3"/>
       <c r="CA203" s="3"/>
       <c r="CB203" s="3"/>
-    </row>
-    <row r="204" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC203" s="3"/>
+      <c r="CD203" s="3"/>
+    </row>
+    <row r="204" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C204" s="3"/>
       <c r="D204" s="3"/>
       <c r="E204" s="3"/>
@@ -19023,8 +19562,10 @@
       <c r="BZ204" s="3"/>
       <c r="CA204" s="3"/>
       <c r="CB204" s="3"/>
-    </row>
-    <row r="205" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC204" s="3"/>
+      <c r="CD204" s="3"/>
+    </row>
+    <row r="205" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C205" s="3"/>
       <c r="D205" s="3"/>
       <c r="E205" s="3"/>
@@ -19103,8 +19644,10 @@
       <c r="BZ205" s="3"/>
       <c r="CA205" s="3"/>
       <c r="CB205" s="3"/>
-    </row>
-    <row r="206" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC205" s="3"/>
+      <c r="CD205" s="3"/>
+    </row>
+    <row r="206" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C206" s="3"/>
       <c r="D206" s="3"/>
       <c r="E206" s="3"/>
@@ -19183,8 +19726,10 @@
       <c r="BZ206" s="3"/>
       <c r="CA206" s="3"/>
       <c r="CB206" s="3"/>
-    </row>
-    <row r="207" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC206" s="3"/>
+      <c r="CD206" s="3"/>
+    </row>
+    <row r="207" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3"/>
@@ -19263,8 +19808,10 @@
       <c r="BZ207" s="3"/>
       <c r="CA207" s="3"/>
       <c r="CB207" s="3"/>
-    </row>
-    <row r="208" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC207" s="3"/>
+      <c r="CD207" s="3"/>
+    </row>
+    <row r="208" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C208" s="3"/>
       <c r="D208" s="3"/>
       <c r="E208" s="3"/>
@@ -19343,8 +19890,10 @@
       <c r="BZ208" s="3"/>
       <c r="CA208" s="3"/>
       <c r="CB208" s="3"/>
-    </row>
-    <row r="209" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC208" s="3"/>
+      <c r="CD208" s="3"/>
+    </row>
+    <row r="209" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3"/>
@@ -19423,8 +19972,10 @@
       <c r="BZ209" s="3"/>
       <c r="CA209" s="3"/>
       <c r="CB209" s="3"/>
-    </row>
-    <row r="210" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC209" s="3"/>
+      <c r="CD209" s="3"/>
+    </row>
+    <row r="210" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C210" s="3"/>
       <c r="D210" s="3"/>
       <c r="E210" s="3"/>
@@ -19503,8 +20054,10 @@
       <c r="BZ210" s="3"/>
       <c r="CA210" s="3"/>
       <c r="CB210" s="3"/>
-    </row>
-    <row r="211" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC210" s="3"/>
+      <c r="CD210" s="3"/>
+    </row>
+    <row r="211" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C211" s="3"/>
       <c r="D211" s="3"/>
       <c r="E211" s="3"/>
@@ -19583,8 +20136,10 @@
       <c r="BZ211" s="3"/>
       <c r="CA211" s="3"/>
       <c r="CB211" s="3"/>
-    </row>
-    <row r="212" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC211" s="3"/>
+      <c r="CD211" s="3"/>
+    </row>
+    <row r="212" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C212" s="3"/>
       <c r="D212" s="3"/>
       <c r="E212" s="3"/>
@@ -19663,8 +20218,10 @@
       <c r="BZ212" s="3"/>
       <c r="CA212" s="3"/>
       <c r="CB212" s="3"/>
-    </row>
-    <row r="213" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC212" s="3"/>
+      <c r="CD212" s="3"/>
+    </row>
+    <row r="213" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C213" s="3"/>
       <c r="D213" s="3"/>
       <c r="E213" s="3"/>
@@ -19743,8 +20300,10 @@
       <c r="BZ213" s="3"/>
       <c r="CA213" s="3"/>
       <c r="CB213" s="3"/>
-    </row>
-    <row r="214" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC213" s="3"/>
+      <c r="CD213" s="3"/>
+    </row>
+    <row r="214" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C214" s="3"/>
       <c r="D214" s="3"/>
       <c r="E214" s="3"/>
@@ -19823,8 +20382,10 @@
       <c r="BZ214" s="3"/>
       <c r="CA214" s="3"/>
       <c r="CB214" s="3"/>
-    </row>
-    <row r="215" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC214" s="3"/>
+      <c r="CD214" s="3"/>
+    </row>
+    <row r="215" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C215" s="3"/>
       <c r="D215" s="3"/>
       <c r="E215" s="3"/>
@@ -19903,8 +20464,10 @@
       <c r="BZ215" s="3"/>
       <c r="CA215" s="3"/>
       <c r="CB215" s="3"/>
-    </row>
-    <row r="216" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC215" s="3"/>
+      <c r="CD215" s="3"/>
+    </row>
+    <row r="216" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C216" s="3"/>
       <c r="D216" s="3"/>
       <c r="E216" s="3"/>
@@ -19983,8 +20546,10 @@
       <c r="BZ216" s="3"/>
       <c r="CA216" s="3"/>
       <c r="CB216" s="3"/>
-    </row>
-    <row r="217" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC216" s="3"/>
+      <c r="CD216" s="3"/>
+    </row>
+    <row r="217" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3"/>
@@ -20063,8 +20628,10 @@
       <c r="BZ217" s="3"/>
       <c r="CA217" s="3"/>
       <c r="CB217" s="3"/>
-    </row>
-    <row r="218" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC217" s="3"/>
+      <c r="CD217" s="3"/>
+    </row>
+    <row r="218" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3"/>
@@ -20143,8 +20710,10 @@
       <c r="BZ218" s="3"/>
       <c r="CA218" s="3"/>
       <c r="CB218" s="3"/>
-    </row>
-    <row r="219" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC218" s="3"/>
+      <c r="CD218" s="3"/>
+    </row>
+    <row r="219" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C219" s="3"/>
       <c r="D219" s="3"/>
       <c r="E219" s="3"/>
@@ -20223,8 +20792,10 @@
       <c r="BZ219" s="3"/>
       <c r="CA219" s="3"/>
       <c r="CB219" s="3"/>
-    </row>
-    <row r="220" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC219" s="3"/>
+      <c r="CD219" s="3"/>
+    </row>
+    <row r="220" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C220" s="3"/>
       <c r="D220" s="3"/>
       <c r="E220" s="3"/>
@@ -20303,8 +20874,10 @@
       <c r="BZ220" s="3"/>
       <c r="CA220" s="3"/>
       <c r="CB220" s="3"/>
-    </row>
-    <row r="221" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC220" s="3"/>
+      <c r="CD220" s="3"/>
+    </row>
+    <row r="221" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C221" s="3"/>
       <c r="D221" s="3"/>
       <c r="E221" s="3"/>
@@ -20383,8 +20956,10 @@
       <c r="BZ221" s="3"/>
       <c r="CA221" s="3"/>
       <c r="CB221" s="3"/>
-    </row>
-    <row r="222" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC221" s="3"/>
+      <c r="CD221" s="3"/>
+    </row>
+    <row r="222" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C222" s="3"/>
       <c r="D222" s="3"/>
       <c r="E222" s="3"/>
@@ -20463,8 +21038,10 @@
       <c r="BZ222" s="3"/>
       <c r="CA222" s="3"/>
       <c r="CB222" s="3"/>
-    </row>
-    <row r="223" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC222" s="3"/>
+      <c r="CD222" s="3"/>
+    </row>
+    <row r="223" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C223" s="3"/>
       <c r="D223" s="3"/>
       <c r="E223" s="3"/>
@@ -20543,8 +21120,10 @@
       <c r="BZ223" s="3"/>
       <c r="CA223" s="3"/>
       <c r="CB223" s="3"/>
-    </row>
-    <row r="224" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC223" s="3"/>
+      <c r="CD223" s="3"/>
+    </row>
+    <row r="224" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C224" s="3"/>
       <c r="D224" s="3"/>
       <c r="E224" s="3"/>
@@ -20623,8 +21202,10 @@
       <c r="BZ224" s="3"/>
       <c r="CA224" s="3"/>
       <c r="CB224" s="3"/>
-    </row>
-    <row r="225" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC224" s="3"/>
+      <c r="CD224" s="3"/>
+    </row>
+    <row r="225" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C225" s="3"/>
       <c r="D225" s="3"/>
       <c r="E225" s="3"/>
@@ -20703,8 +21284,10 @@
       <c r="BZ225" s="3"/>
       <c r="CA225" s="3"/>
       <c r="CB225" s="3"/>
-    </row>
-    <row r="226" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC225" s="3"/>
+      <c r="CD225" s="3"/>
+    </row>
+    <row r="226" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C226" s="3"/>
       <c r="D226" s="3"/>
       <c r="E226" s="3"/>
@@ -20783,8 +21366,10 @@
       <c r="BZ226" s="3"/>
       <c r="CA226" s="3"/>
       <c r="CB226" s="3"/>
-    </row>
-    <row r="227" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC226" s="3"/>
+      <c r="CD226" s="3"/>
+    </row>
+    <row r="227" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C227" s="3"/>
       <c r="D227" s="3"/>
       <c r="E227" s="3"/>
@@ -20863,8 +21448,10 @@
       <c r="BZ227" s="3"/>
       <c r="CA227" s="3"/>
       <c r="CB227" s="3"/>
-    </row>
-    <row r="228" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC227" s="3"/>
+      <c r="CD227" s="3"/>
+    </row>
+    <row r="228" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C228" s="3"/>
       <c r="D228" s="3"/>
       <c r="E228" s="3"/>
@@ -20943,8 +21530,10 @@
       <c r="BZ228" s="3"/>
       <c r="CA228" s="3"/>
       <c r="CB228" s="3"/>
-    </row>
-    <row r="229" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC228" s="3"/>
+      <c r="CD228" s="3"/>
+    </row>
+    <row r="229" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3"/>
@@ -21023,8 +21612,10 @@
       <c r="BZ229" s="3"/>
       <c r="CA229" s="3"/>
       <c r="CB229" s="3"/>
-    </row>
-    <row r="230" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC229" s="3"/>
+      <c r="CD229" s="3"/>
+    </row>
+    <row r="230" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3"/>
@@ -21103,8 +21694,10 @@
       <c r="BZ230" s="3"/>
       <c r="CA230" s="3"/>
       <c r="CB230" s="3"/>
-    </row>
-    <row r="231" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC230" s="3"/>
+      <c r="CD230" s="3"/>
+    </row>
+    <row r="231" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C231" s="3"/>
       <c r="D231" s="3"/>
       <c r="E231" s="3"/>
@@ -21183,8 +21776,10 @@
       <c r="BZ231" s="3"/>
       <c r="CA231" s="3"/>
       <c r="CB231" s="3"/>
-    </row>
-    <row r="232" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC231" s="3"/>
+      <c r="CD231" s="3"/>
+    </row>
+    <row r="232" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C232" s="3"/>
       <c r="D232" s="3"/>
       <c r="E232" s="3"/>
@@ -21263,8 +21858,10 @@
       <c r="BZ232" s="3"/>
       <c r="CA232" s="3"/>
       <c r="CB232" s="3"/>
-    </row>
-    <row r="233" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC232" s="3"/>
+      <c r="CD232" s="3"/>
+    </row>
+    <row r="233" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C233" s="3"/>
       <c r="D233" s="3"/>
       <c r="E233" s="3"/>
@@ -21343,8 +21940,10 @@
       <c r="BZ233" s="3"/>
       <c r="CA233" s="3"/>
       <c r="CB233" s="3"/>
-    </row>
-    <row r="234" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC233" s="3"/>
+      <c r="CD233" s="3"/>
+    </row>
+    <row r="234" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C234" s="3"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3"/>
@@ -21423,8 +22022,10 @@
       <c r="BZ234" s="3"/>
       <c r="CA234" s="3"/>
       <c r="CB234" s="3"/>
-    </row>
-    <row r="235" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC234" s="3"/>
+      <c r="CD234" s="3"/>
+    </row>
+    <row r="235" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C235" s="3"/>
       <c r="D235" s="3"/>
       <c r="E235" s="3"/>
@@ -21503,8 +22104,10 @@
       <c r="BZ235" s="3"/>
       <c r="CA235" s="3"/>
       <c r="CB235" s="3"/>
-    </row>
-    <row r="236" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC235" s="3"/>
+      <c r="CD235" s="3"/>
+    </row>
+    <row r="236" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C236" s="3"/>
       <c r="D236" s="3"/>
       <c r="E236" s="3"/>
@@ -21583,8 +22186,10 @@
       <c r="BZ236" s="3"/>
       <c r="CA236" s="3"/>
       <c r="CB236" s="3"/>
-    </row>
-    <row r="237" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC236" s="3"/>
+      <c r="CD236" s="3"/>
+    </row>
+    <row r="237" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C237" s="3"/>
       <c r="D237" s="3"/>
       <c r="E237" s="3"/>
@@ -21663,8 +22268,10 @@
       <c r="BZ237" s="3"/>
       <c r="CA237" s="3"/>
       <c r="CB237" s="3"/>
-    </row>
-    <row r="238" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC237" s="3"/>
+      <c r="CD237" s="3"/>
+    </row>
+    <row r="238" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C238" s="3"/>
       <c r="D238" s="3"/>
       <c r="E238" s="3"/>
@@ -21743,8 +22350,10 @@
       <c r="BZ238" s="3"/>
       <c r="CA238" s="3"/>
       <c r="CB238" s="3"/>
-    </row>
-    <row r="239" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC238" s="3"/>
+      <c r="CD238" s="3"/>
+    </row>
+    <row r="239" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C239" s="3"/>
       <c r="D239" s="3"/>
       <c r="E239" s="3"/>
@@ -21823,8 +22432,10 @@
       <c r="BZ239" s="3"/>
       <c r="CA239" s="3"/>
       <c r="CB239" s="3"/>
-    </row>
-    <row r="240" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC239" s="3"/>
+      <c r="CD239" s="3"/>
+    </row>
+    <row r="240" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C240" s="3"/>
       <c r="D240" s="3"/>
       <c r="E240" s="3"/>
@@ -21903,8 +22514,10 @@
       <c r="BZ240" s="3"/>
       <c r="CA240" s="3"/>
       <c r="CB240" s="3"/>
-    </row>
-    <row r="241" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC240" s="3"/>
+      <c r="CD240" s="3"/>
+    </row>
+    <row r="241" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C241" s="3"/>
       <c r="D241" s="3"/>
       <c r="E241" s="3"/>
@@ -21983,8 +22596,10 @@
       <c r="BZ241" s="3"/>
       <c r="CA241" s="3"/>
       <c r="CB241" s="3"/>
-    </row>
-    <row r="242" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC241" s="3"/>
+      <c r="CD241" s="3"/>
+    </row>
+    <row r="242" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C242" s="3"/>
       <c r="D242" s="3"/>
       <c r="E242" s="3"/>
@@ -22063,8 +22678,10 @@
       <c r="BZ242" s="3"/>
       <c r="CA242" s="3"/>
       <c r="CB242" s="3"/>
-    </row>
-    <row r="243" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC242" s="3"/>
+      <c r="CD242" s="3"/>
+    </row>
+    <row r="243" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C243" s="3"/>
       <c r="D243" s="3"/>
       <c r="E243" s="3"/>
@@ -22143,8 +22760,10 @@
       <c r="BZ243" s="3"/>
       <c r="CA243" s="3"/>
       <c r="CB243" s="3"/>
-    </row>
-    <row r="244" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC243" s="3"/>
+      <c r="CD243" s="3"/>
+    </row>
+    <row r="244" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C244" s="3"/>
       <c r="D244" s="3"/>
       <c r="E244" s="3"/>
@@ -22223,8 +22842,10 @@
       <c r="BZ244" s="3"/>
       <c r="CA244" s="3"/>
       <c r="CB244" s="3"/>
-    </row>
-    <row r="245" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC244" s="3"/>
+      <c r="CD244" s="3"/>
+    </row>
+    <row r="245" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C245" s="3"/>
       <c r="D245" s="3"/>
       <c r="E245" s="3"/>
@@ -22303,8 +22924,10 @@
       <c r="BZ245" s="3"/>
       <c r="CA245" s="3"/>
       <c r="CB245" s="3"/>
-    </row>
-    <row r="246" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC245" s="3"/>
+      <c r="CD245" s="3"/>
+    </row>
+    <row r="246" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C246" s="3"/>
       <c r="D246" s="3"/>
       <c r="E246" s="3"/>
@@ -22383,8 +23006,10 @@
       <c r="BZ246" s="3"/>
       <c r="CA246" s="3"/>
       <c r="CB246" s="3"/>
-    </row>
-    <row r="247" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC246" s="3"/>
+      <c r="CD246" s="3"/>
+    </row>
+    <row r="247" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C247" s="3"/>
       <c r="D247" s="3"/>
       <c r="E247" s="3"/>
@@ -22463,8 +23088,10 @@
       <c r="BZ247" s="3"/>
       <c r="CA247" s="3"/>
       <c r="CB247" s="3"/>
-    </row>
-    <row r="248" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC247" s="3"/>
+      <c r="CD247" s="3"/>
+    </row>
+    <row r="248" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C248" s="3"/>
       <c r="D248" s="3"/>
       <c r="E248" s="3"/>
@@ -22543,8 +23170,10 @@
       <c r="BZ248" s="3"/>
       <c r="CA248" s="3"/>
       <c r="CB248" s="3"/>
-    </row>
-    <row r="249" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC248" s="3"/>
+      <c r="CD248" s="3"/>
+    </row>
+    <row r="249" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C249" s="3"/>
       <c r="D249" s="3"/>
       <c r="E249" s="3"/>
@@ -22623,8 +23252,10 @@
       <c r="BZ249" s="3"/>
       <c r="CA249" s="3"/>
       <c r="CB249" s="3"/>
-    </row>
-    <row r="250" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC249" s="3"/>
+      <c r="CD249" s="3"/>
+    </row>
+    <row r="250" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C250" s="3"/>
       <c r="D250" s="3"/>
       <c r="E250" s="3"/>
@@ -22703,8 +23334,10 @@
       <c r="BZ250" s="3"/>
       <c r="CA250" s="3"/>
       <c r="CB250" s="3"/>
-    </row>
-    <row r="251" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC250" s="3"/>
+      <c r="CD250" s="3"/>
+    </row>
+    <row r="251" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C251" s="3"/>
       <c r="D251" s="3"/>
       <c r="E251" s="3"/>
@@ -22783,8 +23416,10 @@
       <c r="BZ251" s="3"/>
       <c r="CA251" s="3"/>
       <c r="CB251" s="3"/>
-    </row>
-    <row r="252" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC251" s="3"/>
+      <c r="CD251" s="3"/>
+    </row>
+    <row r="252" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C252" s="3"/>
       <c r="D252" s="3"/>
       <c r="E252" s="3"/>
@@ -22863,8 +23498,10 @@
       <c r="BZ252" s="3"/>
       <c r="CA252" s="3"/>
       <c r="CB252" s="3"/>
-    </row>
-    <row r="253" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC252" s="3"/>
+      <c r="CD252" s="3"/>
+    </row>
+    <row r="253" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C253" s="3"/>
       <c r="D253" s="3"/>
       <c r="E253" s="3"/>
@@ -22943,8 +23580,10 @@
       <c r="BZ253" s="3"/>
       <c r="CA253" s="3"/>
       <c r="CB253" s="3"/>
-    </row>
-    <row r="254" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC253" s="3"/>
+      <c r="CD253" s="3"/>
+    </row>
+    <row r="254" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C254" s="3"/>
       <c r="D254" s="3"/>
       <c r="E254" s="3"/>
@@ -23023,8 +23662,10 @@
       <c r="BZ254" s="3"/>
       <c r="CA254" s="3"/>
       <c r="CB254" s="3"/>
-    </row>
-    <row r="255" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC254" s="3"/>
+      <c r="CD254" s="3"/>
+    </row>
+    <row r="255" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C255" s="3"/>
       <c r="D255" s="3"/>
       <c r="E255" s="3"/>
@@ -23103,8 +23744,10 @@
       <c r="BZ255" s="3"/>
       <c r="CA255" s="3"/>
       <c r="CB255" s="3"/>
-    </row>
-    <row r="256" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC255" s="3"/>
+      <c r="CD255" s="3"/>
+    </row>
+    <row r="256" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="3"/>
@@ -23183,8 +23826,10 @@
       <c r="BZ256" s="3"/>
       <c r="CA256" s="3"/>
       <c r="CB256" s="3"/>
-    </row>
-    <row r="257" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC256" s="3"/>
+      <c r="CD256" s="3"/>
+    </row>
+    <row r="257" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C257" s="3"/>
       <c r="D257" s="3"/>
       <c r="E257" s="3"/>
@@ -23263,8 +23908,10 @@
       <c r="BZ257" s="3"/>
       <c r="CA257" s="3"/>
       <c r="CB257" s="3"/>
-    </row>
-    <row r="258" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC257" s="3"/>
+      <c r="CD257" s="3"/>
+    </row>
+    <row r="258" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C258" s="3"/>
       <c r="D258" s="3"/>
       <c r="E258" s="3"/>
@@ -23343,8 +23990,10 @@
       <c r="BZ258" s="3"/>
       <c r="CA258" s="3"/>
       <c r="CB258" s="3"/>
-    </row>
-    <row r="259" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC258" s="3"/>
+      <c r="CD258" s="3"/>
+    </row>
+    <row r="259" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C259" s="3"/>
       <c r="D259" s="3"/>
       <c r="E259" s="3"/>
@@ -23423,8 +24072,10 @@
       <c r="BZ259" s="3"/>
       <c r="CA259" s="3"/>
       <c r="CB259" s="3"/>
-    </row>
-    <row r="260" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC259" s="3"/>
+      <c r="CD259" s="3"/>
+    </row>
+    <row r="260" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C260" s="3"/>
       <c r="D260" s="3"/>
       <c r="E260" s="3"/>
@@ -23503,8 +24154,10 @@
       <c r="BZ260" s="3"/>
       <c r="CA260" s="3"/>
       <c r="CB260" s="3"/>
-    </row>
-    <row r="261" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC260" s="3"/>
+      <c r="CD260" s="3"/>
+    </row>
+    <row r="261" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C261" s="3"/>
       <c r="D261" s="3"/>
       <c r="E261" s="3"/>
@@ -23583,8 +24236,10 @@
       <c r="BZ261" s="3"/>
       <c r="CA261" s="3"/>
       <c r="CB261" s="3"/>
-    </row>
-    <row r="262" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC261" s="3"/>
+      <c r="CD261" s="3"/>
+    </row>
+    <row r="262" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C262" s="3"/>
       <c r="D262" s="3"/>
       <c r="E262" s="3"/>
@@ -23663,8 +24318,10 @@
       <c r="BZ262" s="3"/>
       <c r="CA262" s="3"/>
       <c r="CB262" s="3"/>
-    </row>
-    <row r="263" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC262" s="3"/>
+      <c r="CD262" s="3"/>
+    </row>
+    <row r="263" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C263" s="3"/>
       <c r="D263" s="3"/>
       <c r="E263" s="3"/>
@@ -23743,8 +24400,10 @@
       <c r="BZ263" s="3"/>
       <c r="CA263" s="3"/>
       <c r="CB263" s="3"/>
-    </row>
-    <row r="264" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC263" s="3"/>
+      <c r="CD263" s="3"/>
+    </row>
+    <row r="264" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C264" s="3"/>
       <c r="D264" s="3"/>
       <c r="E264" s="3"/>
@@ -23823,8 +24482,10 @@
       <c r="BZ264" s="3"/>
       <c r="CA264" s="3"/>
       <c r="CB264" s="3"/>
-    </row>
-    <row r="265" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC264" s="3"/>
+      <c r="CD264" s="3"/>
+    </row>
+    <row r="265" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C265" s="3"/>
       <c r="D265" s="3"/>
       <c r="E265" s="3"/>
@@ -23903,8 +24564,10 @@
       <c r="BZ265" s="3"/>
       <c r="CA265" s="3"/>
       <c r="CB265" s="3"/>
-    </row>
-    <row r="266" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC265" s="3"/>
+      <c r="CD265" s="3"/>
+    </row>
+    <row r="266" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C266" s="3"/>
       <c r="D266" s="3"/>
       <c r="E266" s="3"/>
@@ -23983,8 +24646,10 @@
       <c r="BZ266" s="3"/>
       <c r="CA266" s="3"/>
       <c r="CB266" s="3"/>
-    </row>
-    <row r="267" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC266" s="3"/>
+      <c r="CD266" s="3"/>
+    </row>
+    <row r="267" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C267" s="3"/>
       <c r="D267" s="3"/>
       <c r="E267" s="3"/>
@@ -24063,8 +24728,10 @@
       <c r="BZ267" s="3"/>
       <c r="CA267" s="3"/>
       <c r="CB267" s="3"/>
-    </row>
-    <row r="268" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC267" s="3"/>
+      <c r="CD267" s="3"/>
+    </row>
+    <row r="268" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3"/>
@@ -24143,8 +24810,10 @@
       <c r="BZ268" s="3"/>
       <c r="CA268" s="3"/>
       <c r="CB268" s="3"/>
-    </row>
-    <row r="269" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC268" s="3"/>
+      <c r="CD268" s="3"/>
+    </row>
+    <row r="269" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3"/>
@@ -24223,8 +24892,10 @@
       <c r="BZ269" s="3"/>
       <c r="CA269" s="3"/>
       <c r="CB269" s="3"/>
-    </row>
-    <row r="270" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC269" s="3"/>
+      <c r="CD269" s="3"/>
+    </row>
+    <row r="270" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C270" s="3"/>
       <c r="D270" s="3"/>
       <c r="E270" s="3"/>
@@ -24303,8 +24974,10 @@
       <c r="BZ270" s="3"/>
       <c r="CA270" s="3"/>
       <c r="CB270" s="3"/>
-    </row>
-    <row r="271" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC270" s="3"/>
+      <c r="CD270" s="3"/>
+    </row>
+    <row r="271" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C271" s="3"/>
       <c r="D271" s="3"/>
       <c r="E271" s="3"/>
@@ -24383,8 +25056,10 @@
       <c r="BZ271" s="3"/>
       <c r="CA271" s="3"/>
       <c r="CB271" s="3"/>
-    </row>
-    <row r="272" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC271" s="3"/>
+      <c r="CD271" s="3"/>
+    </row>
+    <row r="272" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C272" s="3"/>
       <c r="D272" s="3"/>
       <c r="E272" s="3"/>
@@ -24463,8 +25138,10 @@
       <c r="BZ272" s="3"/>
       <c r="CA272" s="3"/>
       <c r="CB272" s="3"/>
-    </row>
-    <row r="273" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC272" s="3"/>
+      <c r="CD272" s="3"/>
+    </row>
+    <row r="273" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C273" s="3"/>
       <c r="D273" s="3"/>
       <c r="E273" s="3"/>
@@ -24543,8 +25220,10 @@
       <c r="BZ273" s="3"/>
       <c r="CA273" s="3"/>
       <c r="CB273" s="3"/>
-    </row>
-    <row r="274" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC273" s="3"/>
+      <c r="CD273" s="3"/>
+    </row>
+    <row r="274" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3"/>
@@ -24623,8 +25302,10 @@
       <c r="BZ274" s="3"/>
       <c r="CA274" s="3"/>
       <c r="CB274" s="3"/>
-    </row>
-    <row r="275" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC274" s="3"/>
+      <c r="CD274" s="3"/>
+    </row>
+    <row r="275" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3"/>
@@ -24703,8 +25384,10 @@
       <c r="BZ275" s="3"/>
       <c r="CA275" s="3"/>
       <c r="CB275" s="3"/>
-    </row>
-    <row r="276" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC275" s="3"/>
+      <c r="CD275" s="3"/>
+    </row>
+    <row r="276" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C276" s="3"/>
       <c r="D276" s="3"/>
       <c r="E276" s="3"/>
@@ -24783,8 +25466,10 @@
       <c r="BZ276" s="3"/>
       <c r="CA276" s="3"/>
       <c r="CB276" s="3"/>
-    </row>
-    <row r="277" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC276" s="3"/>
+      <c r="CD276" s="3"/>
+    </row>
+    <row r="277" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C277" s="3"/>
       <c r="D277" s="3"/>
       <c r="E277" s="3"/>
@@ -24863,8 +25548,10 @@
       <c r="BZ277" s="3"/>
       <c r="CA277" s="3"/>
       <c r="CB277" s="3"/>
-    </row>
-    <row r="278" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC277" s="3"/>
+      <c r="CD277" s="3"/>
+    </row>
+    <row r="278" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C278" s="3"/>
       <c r="D278" s="3"/>
       <c r="E278" s="3"/>
@@ -24943,8 +25630,10 @@
       <c r="BZ278" s="3"/>
       <c r="CA278" s="3"/>
       <c r="CB278" s="3"/>
-    </row>
-    <row r="279" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC278" s="3"/>
+      <c r="CD278" s="3"/>
+    </row>
+    <row r="279" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C279" s="3"/>
       <c r="D279" s="3"/>
       <c r="E279" s="3"/>
@@ -25023,8 +25712,10 @@
       <c r="BZ279" s="3"/>
       <c r="CA279" s="3"/>
       <c r="CB279" s="3"/>
-    </row>
-    <row r="280" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC279" s="3"/>
+      <c r="CD279" s="3"/>
+    </row>
+    <row r="280" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C280" s="3"/>
       <c r="D280" s="3"/>
       <c r="E280" s="3"/>
@@ -25103,8 +25794,10 @@
       <c r="BZ280" s="3"/>
       <c r="CA280" s="3"/>
       <c r="CB280" s="3"/>
-    </row>
-    <row r="281" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC280" s="3"/>
+      <c r="CD280" s="3"/>
+    </row>
+    <row r="281" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C281" s="3"/>
       <c r="D281" s="3"/>
       <c r="E281" s="3"/>
@@ -25183,8 +25876,10 @@
       <c r="BZ281" s="3"/>
       <c r="CA281" s="3"/>
       <c r="CB281" s="3"/>
-    </row>
-    <row r="282" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC281" s="3"/>
+      <c r="CD281" s="3"/>
+    </row>
+    <row r="282" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C282" s="3"/>
       <c r="D282" s="3"/>
       <c r="E282" s="3"/>
@@ -25263,8 +25958,10 @@
       <c r="BZ282" s="3"/>
       <c r="CA282" s="3"/>
       <c r="CB282" s="3"/>
-    </row>
-    <row r="283" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC282" s="3"/>
+      <c r="CD282" s="3"/>
+    </row>
+    <row r="283" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C283" s="3"/>
       <c r="D283" s="3"/>
       <c r="E283" s="3"/>
@@ -25343,8 +26040,10 @@
       <c r="BZ283" s="3"/>
       <c r="CA283" s="3"/>
       <c r="CB283" s="3"/>
-    </row>
-    <row r="284" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC283" s="3"/>
+      <c r="CD283" s="3"/>
+    </row>
+    <row r="284" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C284" s="3"/>
       <c r="D284" s="3"/>
       <c r="E284" s="3"/>
@@ -25423,8 +26122,10 @@
       <c r="BZ284" s="3"/>
       <c r="CA284" s="3"/>
       <c r="CB284" s="3"/>
-    </row>
-    <row r="285" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC284" s="3"/>
+      <c r="CD284" s="3"/>
+    </row>
+    <row r="285" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C285" s="3"/>
       <c r="D285" s="3"/>
       <c r="E285" s="3"/>
@@ -25503,8 +26204,10 @@
       <c r="BZ285" s="3"/>
       <c r="CA285" s="3"/>
       <c r="CB285" s="3"/>
-    </row>
-    <row r="286" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC285" s="3"/>
+      <c r="CD285" s="3"/>
+    </row>
+    <row r="286" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C286" s="3"/>
       <c r="D286" s="3"/>
       <c r="E286" s="3"/>
@@ -25583,8 +26286,10 @@
       <c r="BZ286" s="3"/>
       <c r="CA286" s="3"/>
       <c r="CB286" s="3"/>
-    </row>
-    <row r="287" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC286" s="3"/>
+      <c r="CD286" s="3"/>
+    </row>
+    <row r="287" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C287" s="3"/>
       <c r="D287" s="3"/>
       <c r="E287" s="3"/>
@@ -25663,8 +26368,10 @@
       <c r="BZ287" s="3"/>
       <c r="CA287" s="3"/>
       <c r="CB287" s="3"/>
-    </row>
-    <row r="288" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC287" s="3"/>
+      <c r="CD287" s="3"/>
+    </row>
+    <row r="288" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C288" s="3"/>
       <c r="D288" s="3"/>
       <c r="E288" s="3"/>
@@ -25743,8 +26450,10 @@
       <c r="BZ288" s="3"/>
       <c r="CA288" s="3"/>
       <c r="CB288" s="3"/>
-    </row>
-    <row r="289" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC288" s="3"/>
+      <c r="CD288" s="3"/>
+    </row>
+    <row r="289" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C289" s="3"/>
       <c r="D289" s="3"/>
       <c r="E289" s="3"/>
@@ -25823,8 +26532,10 @@
       <c r="BZ289" s="3"/>
       <c r="CA289" s="3"/>
       <c r="CB289" s="3"/>
-    </row>
-    <row r="290" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC289" s="3"/>
+      <c r="CD289" s="3"/>
+    </row>
+    <row r="290" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C290" s="3"/>
       <c r="D290" s="3"/>
       <c r="E290" s="3"/>
@@ -25903,8 +26614,10 @@
       <c r="BZ290" s="3"/>
       <c r="CA290" s="3"/>
       <c r="CB290" s="3"/>
-    </row>
-    <row r="291" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC290" s="3"/>
+      <c r="CD290" s="3"/>
+    </row>
+    <row r="291" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C291" s="3"/>
       <c r="D291" s="3"/>
       <c r="E291" s="3"/>
@@ -25983,8 +26696,10 @@
       <c r="BZ291" s="3"/>
       <c r="CA291" s="3"/>
       <c r="CB291" s="3"/>
-    </row>
-    <row r="292" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC291" s="3"/>
+      <c r="CD291" s="3"/>
+    </row>
+    <row r="292" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C292" s="3"/>
       <c r="D292" s="3"/>
       <c r="E292" s="3"/>
@@ -26063,8 +26778,10 @@
       <c r="BZ292" s="3"/>
       <c r="CA292" s="3"/>
       <c r="CB292" s="3"/>
-    </row>
-    <row r="293" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC292" s="3"/>
+      <c r="CD292" s="3"/>
+    </row>
+    <row r="293" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C293" s="3"/>
       <c r="D293" s="3"/>
       <c r="E293" s="3"/>
@@ -26143,8 +26860,10 @@
       <c r="BZ293" s="3"/>
       <c r="CA293" s="3"/>
       <c r="CB293" s="3"/>
-    </row>
-    <row r="294" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC293" s="3"/>
+      <c r="CD293" s="3"/>
+    </row>
+    <row r="294" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C294" s="3"/>
       <c r="D294" s="3"/>
       <c r="E294" s="3"/>
@@ -26223,8 +26942,10 @@
       <c r="BZ294" s="3"/>
       <c r="CA294" s="3"/>
       <c r="CB294" s="3"/>
-    </row>
-    <row r="295" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC294" s="3"/>
+      <c r="CD294" s="3"/>
+    </row>
+    <row r="295" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C295" s="3"/>
       <c r="D295" s="3"/>
       <c r="E295" s="3"/>
@@ -26303,8 +27024,10 @@
       <c r="BZ295" s="3"/>
       <c r="CA295" s="3"/>
       <c r="CB295" s="3"/>
-    </row>
-    <row r="296" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC295" s="3"/>
+      <c r="CD295" s="3"/>
+    </row>
+    <row r="296" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C296" s="3"/>
       <c r="D296" s="3"/>
       <c r="E296" s="3"/>
@@ -26383,8 +27106,10 @@
       <c r="BZ296" s="3"/>
       <c r="CA296" s="3"/>
       <c r="CB296" s="3"/>
-    </row>
-    <row r="297" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC296" s="3"/>
+      <c r="CD296" s="3"/>
+    </row>
+    <row r="297" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C297" s="3"/>
       <c r="D297" s="3"/>
       <c r="E297" s="3"/>
@@ -26463,8 +27188,10 @@
       <c r="BZ297" s="3"/>
       <c r="CA297" s="3"/>
       <c r="CB297" s="3"/>
-    </row>
-    <row r="298" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC297" s="3"/>
+      <c r="CD297" s="3"/>
+    </row>
+    <row r="298" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C298" s="3"/>
       <c r="D298" s="3"/>
       <c r="E298" s="3"/>
@@ -26543,8 +27270,10 @@
       <c r="BZ298" s="3"/>
       <c r="CA298" s="3"/>
       <c r="CB298" s="3"/>
-    </row>
-    <row r="299" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC298" s="3"/>
+      <c r="CD298" s="3"/>
+    </row>
+    <row r="299" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C299" s="3"/>
       <c r="D299" s="3"/>
       <c r="E299" s="3"/>
@@ -26623,8 +27352,10 @@
       <c r="BZ299" s="3"/>
       <c r="CA299" s="3"/>
       <c r="CB299" s="3"/>
-    </row>
-    <row r="300" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC299" s="3"/>
+      <c r="CD299" s="3"/>
+    </row>
+    <row r="300" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C300" s="3"/>
       <c r="D300" s="3"/>
       <c r="E300" s="3"/>
@@ -26703,8 +27434,10 @@
       <c r="BZ300" s="3"/>
       <c r="CA300" s="3"/>
       <c r="CB300" s="3"/>
-    </row>
-    <row r="301" spans="3:80" x14ac:dyDescent="0.2">
+      <c r="CC300" s="3"/>
+      <c r="CD300" s="3"/>
+    </row>
+    <row r="301" spans="3:82" x14ac:dyDescent="0.2">
       <c r="C301" s="3"/>
       <c r="D301" s="3"/>
       <c r="E301" s="3"/>
@@ -26783,6 +27516,8 @@
       <c r="BZ301" s="3"/>
       <c r="CA301" s="3"/>
       <c r="CB301" s="3"/>
+      <c r="CC301" s="3"/>
+      <c r="CD301" s="3"/>
     </row>
   </sheetData>
   <hyperlinks>
